--- a/docs/ideas.xlsx
+++ b/docs/ideas.xlsx
@@ -18,7 +18,7 @@
     <sheet name="Palette" sheetId="8" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">'Image prompts'!$A$1:$M$52</definedName>
+    <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">'Image prompts'!$A$1:$M$57</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="677" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="725" uniqueCount="385">
   <si>
     <t xml:space="preserve">Intro:</t>
   </si>
@@ -413,7 +413,7 @@
     <t xml:space="preserve">Order</t>
   </si>
   <si>
-    <t xml:space="preserve">Batch "Now" (2026-10-16): the flat — new background without the bed, the wake-up sheet and the flat props. Everything else is already in the game.</t>
+    <t xml:space="preserve">Batch "Now" (2026-10-16): the metro station in layers — back wall, platform front layer (magenta = see-through), train cars, station props, debris. Make metro_back and metro_platform in the same ChatGPT chat so they match. Everything else is already in the game.</t>
   </si>
   <si>
     <t xml:space="preserve">Batch 1 first: player_ok.png is the reference for every other bunny image. Batch 2 needs player_ok.png attached. Everything else can be done in parallel.</t>
@@ -488,82 +488,122 @@
     <t xml:space="preserve">Now</t>
   </si>
   <si>
-    <t xml:space="preserve">Flat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">player_wake.png</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intro — wake-up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 × 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112×72</t>
+    <t xml:space="preserve">Metro station</t>
+  </si>
+  <si>
+    <t xml:space="preserve">metro_back.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metro — back layer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">full scene</t>
+  </si>
+  <si>
+    <t xml:space="preserve">320×180</t>
   </si>
   <si>
     <t xml:space="preserve">Wide landscape image, 1536×1024</t>
   </si>
   <si>
-    <t xml:space="preserve">Attach player_ok.png and add: "Keep the character identical to the attached sprite sheet." The futon must stay in the same place in every cell.</t>
+    <t xml:space="preserve">Back layer: the train drives in front of it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Art style: retro 8-bit pixel art, like a Japanese console game from around 1990, set in a 1990s Japanese office. Chunky square pixels with hard edges: no anti-aliasing, no blur, no soft shading, no gradients, no painterly or paper texture. Every character and object has a 1-pixel dark ink outline. Flat colours from one small palette only: ink black, night indigo, slate blue, paper cream, warm grey, vermilion red, deep red, gold, ochre, wood brown, celadon green, moss green, sakura pink, peach. Subtle Japanese touches where they fit (seigaiha wave patterns, shoji paper screens, paper lanterns, hanko stamps, maneki-neko, daruma, bonsai). Satirical anthropomorphic animals. Clean, readable game asset. No text, letters, numbers, watermark, signature or frame.
+Camera: plain side view of a 2D side-scrolling game stage, horizon level, no characters in the scene.
+Subject: The far side of a 1990s Tokyo metro station seen from the platform, plain side view: the opposite tunnel wall with white tiles, a red stripe, a few framed advertisement posters (pictures only, no text), round wall lamps and dark tunnel shadows; below it the dark track bed with two shiny rails running straight across the whole picture at about two thirds of the image height. NO train, NO platform in the foreground, NO pillars, NO people — just the wall and the empty tracks.
+Draw it as low-resolution pixel art, as if the whole picture were only 320×180 pixels scaled up, so each pixel is a big visible square block.
+The picture must tile seamlessly from left to right: the left edge must continue exactly into the right edge (same horizon, same floor and ceiling lines, nothing cut in half at the edges). No characters.
+Output: the scene fills the whole image edge to edge, no border, no vignette, no text. Wide landscape image, 1536×1024 (it will be cropped to 16:9, so keep important things away from the top and bottom edges).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To do</t>
+  </si>
+  <si>
+    <t xml:space="preserve">metro_platform.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metro — platform front layer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Front layer: pillars and platform go in front of the train. Magenta = see-through.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Art style: retro 8-bit pixel art, like a Japanese console game from around 1990, set in a 1990s Japanese office. Chunky square pixels with hard edges: no anti-aliasing, no blur, no soft shading, no gradients, no painterly or paper texture. Every character and object has a 1-pixel dark ink outline. Flat colours from one small palette only: ink black, night indigo, slate blue, paper cream, warm grey, vermilion red, deep red, gold, ochre, wood brown, celadon green, moss green, sakura pink, peach. Subtle Japanese touches where they fit (seigaiha wave patterns, shoji paper screens, paper lanterns, hanko stamps, maneki-neko, daruma, bonsai). Satirical anthropomorphic animals. Clean, readable game asset. No text, letters, numbers, watermark, signature or frame.
+Camera: plain side view of a 2D side-scrolling game stage, horizon level, no characters in the scene.
+Subject: The FRONT layer of a 1990s Tokyo metro platform, plain side view: the platform floor with grey tiles across the bottom quarter of the picture, its front edge with a bright yellow tactile safety strip, two thick white-tiled pillars with a red band (one at about one quarter and one at about three quarters of the width) reaching from the floor to the top edge, a dark ceiling beam along the very top with hanging fluorescent lights and a hanging station sign with arrows (no letters). Everything between the pillars above the platform floor is magenta (it will show the tracks and passing trains).
+Draw it as low-resolution pixel art, as if the whole picture were only 320×180 pixels scaled up, so each pixel is a big visible square block.
+Layout: everything that is NOT part of this layer is a solid flat magenta background (#FF00FF, one single pure colour, no shading, no checkerboard) — that area will become see-through in the game. The picture must tile seamlessly from left to right: the left edge must continue exactly into the right edge (same heights, same floor line, same ceiling line, nothing cut in half at the edges). No characters, no train.
+Output: PNG, Wide landscape image, 1536×1024 (it will be cropped to 16:9, so keep important things away from the top and bottom edges).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">metro_train.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metro — train cars</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 × 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">400×100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Each car is long and low (about 4 times wider than tall). The code chains them into trains.</t>
   </si>
   <si>
     <t xml:space="preserve">Art style: retro 8-bit pixel art, like a Japanese console game from around 1990, set in a 1990s Japanese office. Chunky square pixels with hard edges: no anti-aliasing, no blur, no soft shading, no gradients, no painterly or paper texture. Every character and object has a 1-pixel dark ink outline. Flat colours from one small palette only: ink black, night indigo, slate blue, paper cream, warm grey, vermilion red, deep red, gold, ochre, wood brown, celadon green, moss green, sakura pink, peach. Subtle Japanese touches where they fit (seigaiha wave patterns, shoji paper screens, paper lanterns, hanko stamps, maneki-neko, daruma, bonsai). Satirical anthropomorphic animals. Clean, readable game asset. No text, letters, numbers, watermark, signature or frame.
 Camera: plain side view, like a 2D side-scrolling game; every figure stands on the bottom edge of its cell.
-Subject: The main character in his tiny apartment, plain side view: a burnt-out white rabbit office worker with long upright ears (soft pink inside), tired half-closed eyes with red rims, a navy-blue suit, white shirt, vermilion tie and brown shoes, carrying a brown leather briefcase. He fell asleep in his crumpled suit after overtime (tie loosened, his briefcase lying on the floor at the RIGHT end of the futon in every cell). A thin red-and-cream Japanese futon with a cherry-blossom blanket and a small pillow lies on the floor on the LEFT side of every cell, always at exactly the same place and size.
-Layout: a sprite sheet on a solid flat magenta background (#FF00FF, one single pure colour, no shading, no checkerboard). An evenly spaced grid of 4 columns and 2 rows of equal-sized cells with wide plain magenta gaps between the cells. Every cell shows the same little scene drawn at about 112×72 pixel-art resolution (each pixel a big visible square block): the futon is in EXACTLY the same place and size in every cell, touching the left and bottom edges of the cell area; only the character changes. Same character design and size in every cell. No grid lines, borders, labels or numbers. Never use magenta or purple on the subjects themselves.
+Subject: A 1990s Tokyo metro train car in plain side view, silver body with a red stripe along the windows, sliding doors, bright windows with the silhouettes of tired standing commuters (dark simple shapes, no faces), wheels on the bogies at the bottom.
+Layout: a sprite sheet on a solid flat magenta background (#FF00FF, one single pure colour, no shading, no checkerboard). An evenly spaced grid of 1 column and 2 rows of equal-sized cells with wide plain magenta gaps between the cells. Every cell shows the exact same character (same design, same colours, same size), centred in its cell, feet on the same baseline. Draw each cell at about 400×100 pixel-art resolution, so each pixel is a big visible square block. No grid lines, borders, labels or numbers. Never use magenta or purple on the subjects themselves.
 Cells, left to right, top to bottom:
-- Row 1: asleep under the blanket, only the head and ears showing on the pillow | the same, little 'z' shapes above the head | eyes snapped wide open in panic, still under the blanket | sitting up on the futon, blanket slid down to the waist
-- Row 2: kneeling beside the futon, getting up | standing right next to the futon, stretching both arms up with a huge yawn | standing next to the futon, shaking himself awake, ears flapping | ONLY the empty futon, blanket thrown back, no bunny
+- Row 1: the front (driver) car, facing LEFT: rounded driver cab with a headlight on the left end, the rest of the car to the right
+- Row 2: a middle car: the same body without a cab, flat ends on both sides so cars can be chained one after another
 Output: PNG, Wide landscape image, 1536×1024.</t>
   </si>
   <si>
-    <t xml:space="preserve">To do</t>
-  </si>
-  <si>
-    <t xml:space="preserve">flat_props.png</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intro — interactive props (mirror, plant, cat)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48×72</t>
+    <t xml:space="preserve">metro_props.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metro — station props</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 × 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72×72</t>
   </si>
   <si>
     <t xml:space="preserve">Art style: retro 8-bit pixel art, like a Japanese console game from around 1990, set in a 1990s Japanese office. Chunky square pixels with hard edges: no anti-aliasing, no blur, no soft shading, no gradients, no painterly or paper texture. Every character and object has a 1-pixel dark ink outline. Flat colours from one small palette only: ink black, night indigo, slate blue, paper cream, warm grey, vermilion red, deep red, gold, ochre, wood brown, celadon green, moss green, sakura pink, peach. Subtle Japanese touches where they fit (seigaiha wave patterns, shoji paper screens, paper lanterns, hanko stamps, maneki-neko, daruma, bonsai). Satirical anthropomorphic animals. Clean, readable game asset. No text, letters, numbers, watermark, signature or frame.
 Camera: plain side view, like a 2D side-scrolling game; every figure stands on the bottom edge of its cell.
-Subject: Objects in a tiny Tokyo apartment, plain side view, all at the same scale (a standing rabbit character would be about as tall as the mirror).
-Layout: a sprite sheet on a solid flat magenta background (#FF00FF, one single pure colour, no shading, no checkerboard). An evenly spaced grid of 4 columns and 2 rows of equal-sized cells with wide plain magenta gaps between the cells. Every cell shows the exact same character (same design, same colours, same size), centred in its cell, feet on the same baseline. Draw each cell at about 48×72 pixel-art resolution, so each pixel is a big visible square block. No grid lines, borders, labels or numbers. Never use magenta or purple on the subjects themselves.
+Subject: Objects on a 1990s Tokyo metro platform, plain side view, all at the same scale (a standing person would be about as tall as the ticket gates are wide).
+Layout: a sprite sheet on a solid flat magenta background (#FF00FF, one single pure colour, no shading, no checkerboard). An evenly spaced grid of 3 columns and 2 rows of equal-sized cells with wide plain magenta gaps between the cells. Each cell shows a different object, all drawn at the same scale as if standing on the same office floor (a person would be about 32 pixels tall), each centred in its cell and resting on the bottom of the cell. Each pixel is a big visible square block. No grid lines, borders, labels or numbers. Never use magenta or purple on the subjects themselves.
 Cells, left to right, top to bottom:
-- Row 1: tall standing mirror in a wooden frame | the same mirror with a bright sparkle on the glass | a droopy, thirsty potted plant in a ceramic pot with a wave pattern | the same plant perky and green again, with a few water drops and a little sparkle
-- Row 2: a fat ginger house cat asleep, curled up on a round cushion | the same cat sitting up on the cushion, looking up | the same cat purring with eyes closed and little pink hearts around it | the same cat stretching on the cushion
+- Row 1: a row of three grey automatic ticket gates with small green arrows | a red drinks vending machine | a station rubbish bin with three openings for separate waste
+- Row 2: a plain wooden station bench | a timetable board on a pole (lines and dots, no readable text) | a big advertisement billboard on legs showing a smiling salaryman holding coffee (no text)
 Output: PNG, Wide landscape image, 1536×1024.</t>
   </si>
   <si>
-    <t xml:space="preserve">Full-screen backgrounds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">intro_flat.png</t>
-  </si>
-  <si>
-    <t xml:space="preserve">full scene</t>
-  </si>
-  <si>
-    <t xml:space="preserve">320×180</t>
+    <t xml:space="preserve">metro_debris.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metro — debris blown by the draft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 × 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16×16</t>
   </si>
   <si>
     <t xml:space="preserve">Art style: retro 8-bit pixel art, like a Japanese console game from around 1990, set in a 1990s Japanese office. Chunky square pixels with hard edges: no anti-aliasing, no blur, no soft shading, no gradients, no painterly or paper texture. Every character and object has a 1-pixel dark ink outline. Flat colours from one small palette only: ink black, night indigo, slate blue, paper cream, warm grey, vermilion red, deep red, gold, ochre, wood brown, celadon green, moss green, sakura pink, peach. Subtle Japanese touches where they fit (seigaiha wave patterns, shoji paper screens, paper lanterns, hanko stamps, maneki-neko, daruma, bonsai). Satirical anthropomorphic animals. Clean, readable game asset. No text, letters, numbers, watermark, signature or frame.
-Camera: plain side view of a 2D side-scrolling game stage, horizon level, no characters in the scene.
-Subject: The inside of a tiny, cosy Tokyo apartment at dawn: wooden floor, a big window in the middle with the sun rising over the city and Mount Fuji, a bookshelf and a hanging scroll on the left wall, a small kitchenette corner, the front door on the right with a little genkan step and shoes. IMPORTANT: NO bed, NO futon, NO mirror, NO potted plants and NO animals anywhere (they are added separately). Keep the left third of the floor completely empty (a futon will be placed there) and the bottom sixth of the image as plain floor.
-Draw it as low-resolution pixel art, as if the whole picture were only 320×180 pixels scaled up, so each pixel is a big visible square block.
-Output: the scene fills the whole image edge to edge, no border, no vignette, no text. Wide landscape image, 1536×1024 (it will be cropped to 16:9, so keep important things away from the top and bottom edges).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs redo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Redo: no bed / mirror / plants in the background (they are separate sprites now).</t>
+Camera: plain side view, like a 2D side-scrolling game; every figure stands on the bottom edge of its cell.
+Subject: Small light things that the draft in a metro tunnel blows along the platform.
+Layout: a sprite sheet on a solid flat magenta background (#FF00FF, one single pure colour, no shading, no checkerboard). An evenly spaced grid of 4 columns and 2 rows of equal-sized cells with wide plain magenta gaps between the cells. Each cell shows one small item, centred, drawn at about 16×16 pixel-art resolution so each pixel is a big visible square block. No grid lines, borders, labels or numbers. Never use magenta or purple on the subjects themselves.
+Cells, left to right, top to bottom:
+- Row 1: dry orange maple leaf | the same leaf flipped over, tumbling | a sheet of newspaper (scribbles, no readable text) | the same newspaper crumpled, flapping
+- Row 2: an empty white plastic shopping bag, puffed | the same bag flattened, fluttering | a crushed drink can | a paper coffee cup lying on its side
+Output: PNG, Wide landscape image, 1536×1024.</t>
   </si>
   <si>
     <t xml:space="preserve">1</t>
@@ -686,7 +726,51 @@
 Output: PNG, Wide landscape image, 1536×1024.</t>
   </si>
   <si>
+    <t xml:space="preserve">Flat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">player_wake.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intro — wake-up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112×72</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Attach player_ok.png and add: "Keep the character identical to the attached sprite sheet." The futon must stay in the same place in every cell.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Art style: retro 8-bit pixel art, like a Japanese console game from around 1990, set in a 1990s Japanese office. Chunky square pixels with hard edges: no anti-aliasing, no blur, no soft shading, no gradients, no painterly or paper texture. Every character and object has a 1-pixel dark ink outline. Flat colours from one small palette only: ink black, night indigo, slate blue, paper cream, warm grey, vermilion red, deep red, gold, ochre, wood brown, celadon green, moss green, sakura pink, peach. Subtle Japanese touches where they fit (seigaiha wave patterns, shoji paper screens, paper lanterns, hanko stamps, maneki-neko, daruma, bonsai). Satirical anthropomorphic animals. Clean, readable game asset. No text, letters, numbers, watermark, signature or frame.
+Camera: plain side view, like a 2D side-scrolling game; every figure stands on the bottom edge of its cell.
+Subject: The main character in his tiny apartment, plain side view: a burnt-out white rabbit office worker with long upright ears (soft pink inside), tired half-closed eyes with red rims, a navy-blue suit, white shirt, vermilion tie and brown shoes, carrying a brown leather briefcase. He fell asleep in his crumpled suit after overtime (tie loosened, his briefcase lying on the floor at the RIGHT end of the futon in every cell). A thin red-and-cream Japanese futon with a cherry-blossom blanket and a small pillow lies on the floor on the LEFT side of every cell, always at exactly the same place and size.
+Layout: a sprite sheet on a solid flat magenta background (#FF00FF, one single pure colour, no shading, no checkerboard). An evenly spaced grid of 4 columns and 2 rows of equal-sized cells with wide plain magenta gaps between the cells. Every cell shows the same little scene drawn at about 112×72 pixel-art resolution (each pixel a big visible square block): the futon is in EXACTLY the same place and size in every cell, touching the left and bottom edges of the cell area; only the character changes. Same character design and size in every cell. No grid lines, borders, labels or numbers. Never use magenta or purple on the subjects themselves.
+Cells, left to right, top to bottom:
+- Row 1: asleep under the blanket, only the head and ears showing on the pillow | the same, little 'z' shapes above the head | eyes snapped wide open in panic, still under the blanket | sitting up on the futon, blanket slid down to the waist
+- Row 2: kneeling beside the futon, getting up | standing right next to the futon, stretching both arms up with a huge yawn | standing next to the futon, shaking himself awake, ears flapping | ONLY the empty futon, blanket thrown back, no bunny
+Output: PNG, Wide landscape image, 1536×1024.</t>
+  </si>
+  <si>
     <t xml:space="preserve">3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">flat_props.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intro — interactive props (mirror, plant, cat)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48×72</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Art style: retro 8-bit pixel art, like a Japanese console game from around 1990, set in a 1990s Japanese office. Chunky square pixels with hard edges: no anti-aliasing, no blur, no soft shading, no gradients, no painterly or paper texture. Every character and object has a 1-pixel dark ink outline. Flat colours from one small palette only: ink black, night indigo, slate blue, paper cream, warm grey, vermilion red, deep red, gold, ochre, wood brown, celadon green, moss green, sakura pink, peach. Subtle Japanese touches where they fit (seigaiha wave patterns, shoji paper screens, paper lanterns, hanko stamps, maneki-neko, daruma, bonsai). Satirical anthropomorphic animals. Clean, readable game asset. No text, letters, numbers, watermark, signature or frame.
+Camera: plain side view, like a 2D side-scrolling game; every figure stands on the bottom edge of its cell.
+Subject: Objects in a tiny Tokyo apartment, plain side view, all at the same scale (a standing rabbit character would be about as tall as the mirror).
+Layout: a sprite sheet on a solid flat magenta background (#FF00FF, one single pure colour, no shading, no checkerboard). An evenly spaced grid of 4 columns and 2 rows of equal-sized cells with wide plain magenta gaps between the cells. Every cell shows the exact same character (same design, same colours, same size), centred in its cell, feet on the same baseline. Draw each cell at about 48×72 pixel-art resolution, so each pixel is a big visible square block. No grid lines, borders, labels or numbers. Never use magenta or purple on the subjects themselves.
+Cells, left to right, top to bottom:
+- Row 1: tall standing mirror in a wooden frame | the same mirror with a bright sparkle on the glass | a droopy, thirsty potted plant in a ceramic pot with a wave pattern | the same plant perky and green again, with a few water drops and a little sparkle
+- Row 2: a fat ginger house cat asleep, curled up on a round cushion | the same cat sitting up on the cushion, looking up | the same cat purring with eyes closed and little pink hearts around it | the same cat stretching on the cushion
+Output: PNG, Wide landscape image, 1536×1024.</t>
   </si>
   <si>
     <t xml:space="preserve">Bosses</t>
@@ -1112,9 +1196,6 @@
   </si>
   <si>
     <t xml:space="preserve">4 × 4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16×16</t>
   </si>
   <si>
     <t xml:space="preserve">Do all sheets of this group in the same ChatGPT chat.</t>
@@ -1153,9 +1234,6 @@
     <t xml:space="preserve">props_cubicles_a.png</t>
   </si>
   <si>
-    <t xml:space="preserve">3 × 2</t>
-  </si>
-  <si>
     <t xml:space="preserve">Art style: retro 8-bit pixel art, like a Japanese console game from around 1990, set in a 1990s Japanese office. Chunky square pixels with hard edges: no anti-aliasing, no blur, no soft shading, no gradients, no painterly or paper texture. Every character and object has a 1-pixel dark ink outline. Flat colours from one small palette only: ink black, night indigo, slate blue, paper cream, warm grey, vermilion red, deep red, gold, ochre, wood brown, celadon green, moss green, sakura pink, peach. Subtle Japanese touches where they fit (seigaiha wave patterns, shoji paper screens, paper lanterns, hanko stamps, maneki-neko, daruma, bonsai). Satirical anthropomorphic animals. Clean, readable game asset. No text, letters, numbers, watermark, signature or frame.
 Camera: classic Japanese top-down RPG view (three-quarter view from above and in front): you see the top and the front of things; characters show their face when they face down.
 Subject: Six different single office cubicles (desk, grey partition, rolling chair, beige CRT monitor), each with a distinct personality.
@@ -1273,6 +1351,9 @@
 Output: PNG, Wide landscape image, 1536×1024.</t>
   </si>
   <si>
+    <t xml:space="preserve">Full-screen backgrounds</t>
+  </si>
+  <si>
     <t xml:space="preserve">title_bg.png</t>
   </si>
   <si>
@@ -1283,14 +1364,27 @@
 Output: the scene fills the whole image edge to edge, no border, no vignette, no text. Wide landscape image, 1536×1024 (it will be cropped to 16:9, so keep important things away from the top and bottom edges).</t>
   </si>
   <si>
-    <t xml:space="preserve">intro_metro.png</t>
+    <t xml:space="preserve">intro_flat.png</t>
   </si>
   <si>
     <t xml:space="preserve">Art style: retro 8-bit pixel art, like a Japanese console game from around 1990, set in a 1990s Japanese office. Chunky square pixels with hard edges: no anti-aliasing, no blur, no soft shading, no gradients, no painterly or paper texture. Every character and object has a 1-pixel dark ink outline. Flat colours from one small palette only: ink black, night indigo, slate blue, paper cream, warm grey, vermilion red, deep red, gold, ochre, wood brown, celadon green, moss green, sakura pink, peach. Subtle Japanese touches where they fit (seigaiha wave patterns, shoji paper screens, paper lanterns, hanko stamps, maneki-neko, daruma, bonsai). Satirical anthropomorphic animals. Clean, readable game asset. No text, letters, numbers, watermark, signature or frame.
 Camera: plain side view of a 2D side-scrolling game stage, horizon level, no characters in the scene.
-Subject: A 1990s Tokyo metro station platform: tiled walls, pillars, a ticket turnstile, hanging station signs (symbols only). Keep the bottom sixth of the image as plain floor.
+Subject: The inside of a tiny, cosy Tokyo apartment at dawn: wooden floor, a big window in the middle with the sun rising over the city and Mount Fuji, a bookshelf and a hanging scroll on the left wall, a small kitchenette corner, the front door on the right with a little genkan step and shoes. IMPORTANT: NO bed, NO futon, NO mirror, NO potted plants and NO animals anywhere (they are added separately). Keep the left third of the floor completely empty (a futon will be placed there) and the bottom sixth of the image as plain floor.
 Draw it as low-resolution pixel art, as if the whole picture were only 320×180 pixels scaled up, so each pixel is a big visible square block.
 Output: the scene fills the whole image edge to edge, no border, no vignette, no text. Wide landscape image, 1536×1024 (it will be cropped to 16:9, so keep important things away from the top and bottom edges).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">intro_metro.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Art style: retro 8-bit pixel art, like a Japanese console game from around 1990, set in a 1990s Japanese office. Chunky square pixels with hard edges: no anti-aliasing, no blur, no soft shading, no gradients, no painterly or paper texture. Every character and object has a 1-pixel dark ink outline. Flat colours from one small palette only: ink black, night indigo, slate blue, paper cream, warm grey, vermilion red, deep red, gold, ochre, wood brown, celadon green, moss green, sakura pink, peach. Subtle Japanese touches where they fit (seigaiha wave patterns, shoji paper screens, paper lanterns, hanko stamps, maneki-neko, daruma, bonsai). Satirical anthropomorphic animals. Clean, readable game asset. No text, letters, numbers, watermark, signature or frame.
+Camera: plain side view of a 2D side-scrolling game stage, horizon level, no characters in the scene.
+Subject: OLD single-picture metro background, replaced by the metro_* layers above — only used until those exist. A 1990s Tokyo metro station platform: tiled walls, pillars, a ticket turnstile, hanging station signs (symbols only). Keep the bottom sixth of the image as plain floor.
+Draw it as low-resolution pixel art, as if the whole picture were only 320×180 pixels scaled up, so each pixel is a big visible square block.
+Output: the scene fills the whole image edge to edge, no border, no vignette, no text. Wide landscape image, 1536×1024 (it will be cropped to 16:9, so keep important things away from the top and bottom edges).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Only used until the metro_* layers exist.</t>
   </si>
   <si>
     <t xml:space="preserve">intro_entrance.png</t>
@@ -1344,6 +1438,9 @@
   </si>
   <si>
     <t xml:space="preserve">Delivered</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs redo</t>
   </si>
   <si>
     <t xml:space="preserve">Total</t>
@@ -1871,7 +1968,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="9">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1884,14 +1981,6 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -35876,7 +35965,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M52"/>
+  <dimension ref="A1:M57"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -35992,12 +36081,14 @@
         <v>153</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="H3" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="I3" s="9"/>
+      <c r="I3" s="9" t="s">
+        <v>161</v>
+      </c>
       <c r="J3" s="9" t="s">
         <v>162</v>
       </c>
@@ -36015,12 +36106,14 @@
         <v>149</v>
       </c>
       <c r="C4" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="D4" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="E4" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="E4" s="9"/>
       <c r="F4" s="9" t="s">
         <v>165</v>
       </c>
@@ -36030,50 +36123,50 @@
       <c r="H4" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="I4" s="9"/>
+      <c r="I4" s="9" t="s">
+        <v>167</v>
+      </c>
       <c r="J4" s="9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="K4" s="11"/>
       <c r="L4" s="11" t="s">
-        <v>168</v>
-      </c>
-      <c r="M4" s="11" t="s">
-        <v>169</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="M4" s="11"/>
     </row>
     <row r="5" customFormat="false" ht="229.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="n">
         <v>4</v>
       </c>
       <c r="B5" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="E5" s="9" t="s">
         <v>170</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="F5" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="G5" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9" t="s">
+      <c r="H5" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9" t="s">
         <v>173</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>174</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="I5" s="9" t="s">
-        <v>176</v>
-      </c>
-      <c r="J5" s="9" t="s">
-        <v>177</v>
       </c>
       <c r="K5" s="11"/>
       <c r="L5" s="11" t="s">
-        <v>178</v>
+        <v>158</v>
       </c>
       <c r="M5" s="11"/>
     </row>
@@ -36082,33 +36175,33 @@
         <v>5</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>179</v>
+        <v>149</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>171</v>
+        <v>150</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E6" s="9"/>
+        <v>174</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>175</v>
+      </c>
       <c r="F6" s="9" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="I6" s="9" t="s">
-        <v>181</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="I6" s="9"/>
       <c r="J6" s="9" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="K6" s="11"/>
       <c r="L6" s="11" t="s">
-        <v>178</v>
+        <v>158</v>
       </c>
       <c r="M6" s="11"/>
     </row>
@@ -36120,30 +36213,30 @@
         <v>179</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E7" s="9"/>
       <c r="F7" s="9" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="J7" s="9" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="K7" s="11"/>
       <c r="L7" s="11" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="M7" s="11"/>
     </row>
@@ -36152,33 +36245,33 @@
         <v>7</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E8" s="9"/>
       <c r="F8" s="9" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="K8" s="11"/>
       <c r="L8" s="11" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="M8" s="11"/>
     </row>
@@ -36187,33 +36280,33 @@
         <v>8</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="E9" s="9"/>
       <c r="F9" s="9" t="s">
-        <v>153</v>
+        <v>182</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>155</v>
+        <v>184</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="J9" s="9" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="K9" s="11"/>
       <c r="L9" s="11" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="M9" s="11"/>
     </row>
@@ -36222,33 +36315,33 @@
         <v>9</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="E10" s="9"/>
       <c r="F10" s="9" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>155</v>
+        <v>184</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="K10" s="11"/>
       <c r="L10" s="11" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="M10" s="11"/>
     </row>
@@ -36257,33 +36350,33 @@
         <v>10</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>196</v>
+        <v>180</v>
       </c>
       <c r="D11" s="10" t="s">
         <v>197</v>
       </c>
-      <c r="E11" s="9" t="s">
+      <c r="E11" s="9"/>
+      <c r="F11" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="G11" s="9" t="s">
         <v>198</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="G11" s="9" t="s">
-        <v>193</v>
       </c>
       <c r="H11" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="I11" s="9"/>
+      <c r="I11" s="9" t="s">
+        <v>195</v>
+      </c>
       <c r="J11" s="9" t="s">
         <v>199</v>
       </c>
       <c r="K11" s="11"/>
       <c r="L11" s="11" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="M11" s="11"/>
     </row>
@@ -36292,33 +36385,33 @@
         <v>11</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="C12" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="D12" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="E12" s="9"/>
+      <c r="F12" s="9" t="s">
         <v>201</v>
       </c>
-      <c r="E12" s="9" t="s">
+      <c r="G12" s="9" t="s">
         <v>202</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="G12" s="9" t="s">
-        <v>203</v>
       </c>
       <c r="H12" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="I12" s="9"/>
+      <c r="I12" s="9" t="s">
+        <v>195</v>
+      </c>
       <c r="J12" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="K12" s="11"/>
       <c r="L12" s="11" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="M12" s="11"/>
     </row>
@@ -36327,10 +36420,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="D13" s="10" t="s">
         <v>205</v>
@@ -36339,21 +36432,23 @@
         <v>206</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>153</v>
+        <v>176</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="H13" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="I13" s="9"/>
+      <c r="I13" s="9" t="s">
+        <v>208</v>
+      </c>
       <c r="J13" s="9" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="K13" s="11"/>
       <c r="L13" s="11" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="M13" s="11"/>
     </row>
@@ -36362,33 +36457,33 @@
         <v>13</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>153</v>
+        <v>176</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="H14" s="9" t="s">
         <v>155</v>
       </c>
       <c r="I14" s="9"/>
       <c r="J14" s="9" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="K14" s="11"/>
       <c r="L14" s="11" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="M14" s="11"/>
     </row>
@@ -36397,33 +36492,33 @@
         <v>14</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>153</v>
+        <v>176</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H15" s="9" t="s">
         <v>155</v>
       </c>
       <c r="I15" s="9"/>
       <c r="J15" s="9" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="K15" s="11"/>
       <c r="L15" s="11" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="M15" s="11"/>
     </row>
@@ -36432,33 +36527,33 @@
         <v>15</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>217</v>
+        <v>176</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="H16" s="9" t="s">
         <v>155</v>
       </c>
       <c r="I16" s="9"/>
       <c r="J16" s="9" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="K16" s="11"/>
       <c r="L16" s="11" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="M16" s="11"/>
     </row>
@@ -36467,33 +36562,33 @@
         <v>16</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>217</v>
+        <v>176</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>174</v>
+        <v>222</v>
       </c>
       <c r="H17" s="9" t="s">
         <v>155</v>
       </c>
       <c r="I17" s="9"/>
       <c r="J17" s="9" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="K17" s="11"/>
       <c r="L17" s="11" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="M17" s="11"/>
     </row>
@@ -36502,33 +36597,33 @@
         <v>17</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>217</v>
+        <v>176</v>
       </c>
       <c r="G18" s="9" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="H18" s="9" t="s">
         <v>155</v>
       </c>
       <c r="I18" s="9"/>
       <c r="J18" s="9" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="K18" s="11"/>
       <c r="L18" s="11" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="M18" s="11"/>
     </row>
@@ -36537,33 +36632,33 @@
         <v>18</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>217</v>
+        <v>176</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>174</v>
+        <v>222</v>
       </c>
       <c r="H19" s="9" t="s">
         <v>155</v>
       </c>
       <c r="I19" s="9"/>
       <c r="J19" s="9" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="K19" s="11"/>
       <c r="L19" s="11" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="M19" s="11"/>
     </row>
@@ -36572,33 +36667,33 @@
         <v>19</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>214</v>
+        <v>233</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>217</v>
+        <v>236</v>
       </c>
       <c r="G20" s="9" t="s">
-        <v>218</v>
+        <v>237</v>
       </c>
       <c r="H20" s="9" t="s">
         <v>155</v>
       </c>
       <c r="I20" s="9"/>
       <c r="J20" s="9" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="K20" s="11"/>
       <c r="L20" s="11" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="M20" s="11"/>
     </row>
@@ -36607,33 +36702,33 @@
         <v>20</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>214</v>
+        <v>233</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>217</v>
+        <v>236</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="H21" s="9" t="s">
         <v>155</v>
       </c>
       <c r="I21" s="9"/>
       <c r="J21" s="9" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="K21" s="11"/>
       <c r="L21" s="11" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="M21" s="11"/>
     </row>
@@ -36642,33 +36737,33 @@
         <v>21</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>214</v>
+        <v>233</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="E22" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="F22" s="9" t="s">
         <v>236</v>
       </c>
-      <c r="F22" s="9" t="s">
-        <v>217</v>
-      </c>
       <c r="G22" s="9" t="s">
-        <v>218</v>
+        <v>237</v>
       </c>
       <c r="H22" s="9" t="s">
         <v>155</v>
       </c>
       <c r="I22" s="9"/>
       <c r="J22" s="9" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="K22" s="11"/>
       <c r="L22" s="11" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="M22" s="11"/>
     </row>
@@ -36677,33 +36772,33 @@
         <v>22</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>214</v>
+        <v>233</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>217</v>
+        <v>236</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="H23" s="9" t="s">
         <v>155</v>
       </c>
       <c r="I23" s="9"/>
       <c r="J23" s="9" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="K23" s="11"/>
       <c r="L23" s="11" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="M23" s="11"/>
     </row>
@@ -36712,33 +36807,33 @@
         <v>23</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>214</v>
+        <v>233</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>217</v>
+        <v>236</v>
       </c>
       <c r="G24" s="9" t="s">
-        <v>218</v>
+        <v>237</v>
       </c>
       <c r="H24" s="9" t="s">
         <v>155</v>
       </c>
       <c r="I24" s="9"/>
       <c r="J24" s="9" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="K24" s="11"/>
       <c r="L24" s="11" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="M24" s="11"/>
     </row>
@@ -36747,33 +36842,33 @@
         <v>24</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>214</v>
+        <v>233</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>217</v>
+        <v>236</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="H25" s="9" t="s">
         <v>155</v>
       </c>
       <c r="I25" s="9"/>
       <c r="J25" s="9" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="K25" s="11"/>
       <c r="L25" s="11" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="M25" s="11"/>
     </row>
@@ -36782,33 +36877,33 @@
         <v>25</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>247</v>
+        <v>233</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>217</v>
+        <v>236</v>
       </c>
       <c r="G26" s="9" t="s">
-        <v>174</v>
+        <v>237</v>
       </c>
       <c r="H26" s="9" t="s">
         <v>155</v>
       </c>
       <c r="I26" s="9"/>
       <c r="J26" s="9" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="K26" s="11"/>
       <c r="L26" s="11" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="M26" s="11"/>
     </row>
@@ -36817,33 +36912,33 @@
         <v>26</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>247</v>
+        <v>233</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>217</v>
+        <v>236</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="H27" s="9" t="s">
         <v>155</v>
       </c>
       <c r="I27" s="9"/>
       <c r="J27" s="9" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="K27" s="11"/>
       <c r="L27" s="11" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="M27" s="11"/>
     </row>
@@ -36852,33 +36947,33 @@
         <v>27</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>247</v>
+        <v>233</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>217</v>
+        <v>236</v>
       </c>
       <c r="G28" s="9" t="s">
-        <v>174</v>
+        <v>237</v>
       </c>
       <c r="H28" s="9" t="s">
         <v>155</v>
       </c>
       <c r="I28" s="9"/>
       <c r="J28" s="9" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="K28" s="11"/>
       <c r="L28" s="11" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="M28" s="11"/>
     </row>
@@ -36887,33 +36982,33 @@
         <v>28</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>247</v>
+        <v>233</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>217</v>
+        <v>236</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="H29" s="9" t="s">
         <v>155</v>
       </c>
       <c r="I29" s="9"/>
       <c r="J29" s="9" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="K29" s="11"/>
       <c r="L29" s="11" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="M29" s="11"/>
     </row>
@@ -36922,33 +37017,33 @@
         <v>29</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>247</v>
+        <v>266</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>217</v>
+        <v>236</v>
       </c>
       <c r="G30" s="9" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="H30" s="9" t="s">
         <v>155</v>
       </c>
       <c r="I30" s="9"/>
       <c r="J30" s="9" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="K30" s="11"/>
       <c r="L30" s="11" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="M30" s="11"/>
     </row>
@@ -36957,33 +37052,33 @@
         <v>30</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>247</v>
+        <v>266</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>217</v>
+        <v>236</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="H31" s="9" t="s">
         <v>155</v>
       </c>
       <c r="I31" s="9"/>
       <c r="J31" s="9" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="K31" s="11"/>
       <c r="L31" s="11" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="M31" s="11"/>
     </row>
@@ -36992,33 +37087,33 @@
         <v>31</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>247</v>
+        <v>266</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>217</v>
+        <v>236</v>
       </c>
       <c r="G32" s="9" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="H32" s="9" t="s">
         <v>155</v>
       </c>
       <c r="I32" s="9"/>
       <c r="J32" s="9" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="K32" s="11"/>
       <c r="L32" s="11" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="M32" s="11"/>
     </row>
@@ -37027,33 +37122,33 @@
         <v>32</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>247</v>
+        <v>266</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>217</v>
+        <v>236</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="H33" s="9" t="s">
         <v>155</v>
       </c>
       <c r="I33" s="9"/>
       <c r="J33" s="9" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="K33" s="11"/>
       <c r="L33" s="11" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="M33" s="11"/>
     </row>
@@ -37062,33 +37157,33 @@
         <v>33</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>247</v>
+        <v>266</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>217</v>
+        <v>236</v>
       </c>
       <c r="G34" s="9" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="H34" s="9" t="s">
         <v>155</v>
       </c>
       <c r="I34" s="9"/>
       <c r="J34" s="9" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="K34" s="11"/>
       <c r="L34" s="11" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="M34" s="11"/>
     </row>
@@ -37097,33 +37192,33 @@
         <v>34</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>247</v>
+        <v>266</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>217</v>
+        <v>236</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="H35" s="9" t="s">
         <v>155</v>
       </c>
       <c r="I35" s="9"/>
       <c r="J35" s="9" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="K35" s="11"/>
       <c r="L35" s="11" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="M35" s="11"/>
     </row>
@@ -37132,33 +37227,33 @@
         <v>35</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>247</v>
+        <v>266</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>217</v>
+        <v>236</v>
       </c>
       <c r="G36" s="9" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="H36" s="9" t="s">
         <v>155</v>
       </c>
       <c r="I36" s="9"/>
       <c r="J36" s="9" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="K36" s="11"/>
       <c r="L36" s="11" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="M36" s="11"/>
     </row>
@@ -37167,33 +37262,33 @@
         <v>36</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>281</v>
+        <v>266</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>282</v>
-      </c>
-      <c r="E37" s="9"/>
+        <v>288</v>
+      </c>
+      <c r="E37" s="9" t="s">
+        <v>289</v>
+      </c>
       <c r="F37" s="9" t="s">
-        <v>283</v>
+        <v>236</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>284</v>
+        <v>183</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="I37" s="9" t="s">
-        <v>285</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="I37" s="9"/>
       <c r="J37" s="9" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="K37" s="11"/>
       <c r="L37" s="11" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="M37" s="11"/>
     </row>
@@ -37202,33 +37297,33 @@
         <v>37</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>281</v>
+        <v>266</v>
       </c>
       <c r="D38" s="10" t="s">
-        <v>287</v>
-      </c>
-      <c r="E38" s="9"/>
+        <v>291</v>
+      </c>
+      <c r="E38" s="9" t="s">
+        <v>292</v>
+      </c>
       <c r="F38" s="9" t="s">
-        <v>283</v>
+        <v>236</v>
       </c>
       <c r="G38" s="9" t="s">
-        <v>284</v>
+        <v>183</v>
       </c>
       <c r="H38" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="I38" s="9" t="s">
-        <v>285</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="I38" s="9"/>
       <c r="J38" s="9" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="K38" s="11"/>
       <c r="L38" s="11" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="M38" s="11"/>
     </row>
@@ -37237,33 +37332,33 @@
         <v>38</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>289</v>
+        <v>266</v>
       </c>
       <c r="D39" s="10" t="s">
-        <v>290</v>
-      </c>
-      <c r="E39" s="9"/>
+        <v>294</v>
+      </c>
+      <c r="E39" s="9" t="s">
+        <v>295</v>
+      </c>
       <c r="F39" s="9" t="s">
-        <v>291</v>
+        <v>236</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="H39" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="I39" s="9" t="s">
-        <v>285</v>
-      </c>
+      <c r="I39" s="9"/>
       <c r="J39" s="9" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="K39" s="11"/>
       <c r="L39" s="11" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="M39" s="11"/>
     </row>
@@ -37272,33 +37367,33 @@
         <v>39</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>289</v>
+        <v>266</v>
       </c>
       <c r="D40" s="10" t="s">
-        <v>293</v>
-      </c>
-      <c r="E40" s="9"/>
+        <v>297</v>
+      </c>
+      <c r="E40" s="9" t="s">
+        <v>298</v>
+      </c>
       <c r="F40" s="9" t="s">
-        <v>291</v>
+        <v>236</v>
       </c>
       <c r="G40" s="9" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="H40" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="I40" s="9" t="s">
-        <v>285</v>
-      </c>
+      <c r="I40" s="9"/>
       <c r="J40" s="9" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="K40" s="11"/>
       <c r="L40" s="11" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="M40" s="11"/>
     </row>
@@ -37307,33 +37402,33 @@
         <v>40</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="D41" s="10" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="E41" s="9"/>
       <c r="F41" s="9" t="s">
-        <v>291</v>
+        <v>302</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>203</v>
+        <v>177</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>155</v>
+        <v>184</v>
       </c>
       <c r="I41" s="9" t="s">
-        <v>285</v>
+        <v>303</v>
       </c>
       <c r="J41" s="9" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="K41" s="11"/>
       <c r="L41" s="11" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="M41" s="11"/>
     </row>
@@ -37342,33 +37437,33 @@
         <v>41</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="D42" s="10" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="E42" s="9"/>
       <c r="F42" s="9" t="s">
-        <v>291</v>
+        <v>302</v>
       </c>
       <c r="G42" s="9" t="s">
-        <v>203</v>
+        <v>177</v>
       </c>
       <c r="H42" s="9" t="s">
-        <v>155</v>
+        <v>184</v>
       </c>
       <c r="I42" s="9" t="s">
-        <v>285</v>
+        <v>303</v>
       </c>
       <c r="J42" s="9" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="K42" s="11"/>
       <c r="L42" s="11" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="M42" s="11"/>
     </row>
@@ -37377,33 +37472,33 @@
         <v>42</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>289</v>
+        <v>307</v>
       </c>
       <c r="D43" s="10" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="E43" s="9"/>
       <c r="F43" s="9" t="s">
-        <v>291</v>
+        <v>171</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>203</v>
+        <v>222</v>
       </c>
       <c r="H43" s="9" t="s">
         <v>155</v>
       </c>
       <c r="I43" s="9" t="s">
-        <v>285</v>
+        <v>303</v>
       </c>
       <c r="J43" s="9" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="K43" s="11"/>
       <c r="L43" s="11" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="M43" s="11"/>
     </row>
@@ -37412,33 +37507,33 @@
         <v>43</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>289</v>
+        <v>307</v>
       </c>
       <c r="D44" s="10" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="E44" s="9"/>
       <c r="F44" s="9" t="s">
-        <v>291</v>
+        <v>171</v>
       </c>
       <c r="G44" s="9" t="s">
-        <v>203</v>
+        <v>222</v>
       </c>
       <c r="H44" s="9" t="s">
         <v>155</v>
       </c>
       <c r="I44" s="9" t="s">
-        <v>285</v>
+        <v>303</v>
       </c>
       <c r="J44" s="9" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="K44" s="11"/>
       <c r="L44" s="11" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="M44" s="11"/>
     </row>
@@ -37447,33 +37542,33 @@
         <v>44</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>289</v>
+        <v>307</v>
       </c>
       <c r="D45" s="10" t="s">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="E45" s="9"/>
       <c r="F45" s="9" t="s">
-        <v>291</v>
+        <v>171</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>203</v>
+        <v>222</v>
       </c>
       <c r="H45" s="9" t="s">
         <v>155</v>
       </c>
       <c r="I45" s="9" t="s">
-        <v>285</v>
+        <v>303</v>
       </c>
       <c r="J45" s="9" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="K45" s="11"/>
       <c r="L45" s="11" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="M45" s="11"/>
     </row>
@@ -37482,33 +37577,33 @@
         <v>45</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>289</v>
+        <v>307</v>
       </c>
       <c r="D46" s="10" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="E46" s="9"/>
       <c r="F46" s="9" t="s">
-        <v>291</v>
+        <v>171</v>
       </c>
       <c r="G46" s="9" t="s">
-        <v>203</v>
+        <v>222</v>
       </c>
       <c r="H46" s="9" t="s">
         <v>155</v>
       </c>
       <c r="I46" s="9" t="s">
-        <v>285</v>
+        <v>303</v>
       </c>
       <c r="J46" s="9" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="K46" s="11"/>
       <c r="L46" s="11" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="M46" s="11"/>
     </row>
@@ -37517,31 +37612,33 @@
         <v>46</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="C47" s="9" t="s">
         <v>307</v>
       </c>
       <c r="D47" s="10" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="E47" s="9"/>
       <c r="F47" s="9" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>284</v>
+        <v>222</v>
       </c>
       <c r="H47" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="I47" s="9"/>
+      <c r="I47" s="9" t="s">
+        <v>303</v>
+      </c>
       <c r="J47" s="9" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="K47" s="11"/>
       <c r="L47" s="11" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="M47" s="11"/>
     </row>
@@ -37550,31 +37647,33 @@
         <v>47</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>163</v>
+        <v>307</v>
       </c>
       <c r="D48" s="10" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="E48" s="9"/>
       <c r="F48" s="9" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="G48" s="9" t="s">
-        <v>166</v>
+        <v>222</v>
       </c>
       <c r="H48" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="I48" s="9"/>
+      <c r="I48" s="9" t="s">
+        <v>303</v>
+      </c>
       <c r="J48" s="9" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="K48" s="11"/>
       <c r="L48" s="11" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="M48" s="11"/>
     </row>
@@ -37583,31 +37682,33 @@
         <v>48</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>163</v>
+        <v>307</v>
       </c>
       <c r="D49" s="10" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="E49" s="9"/>
       <c r="F49" s="9" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>166</v>
+        <v>222</v>
       </c>
       <c r="H49" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="I49" s="9"/>
+      <c r="I49" s="9" t="s">
+        <v>303</v>
+      </c>
       <c r="J49" s="9" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="K49" s="11"/>
       <c r="L49" s="11" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="M49" s="11"/>
     </row>
@@ -37616,31 +37717,33 @@
         <v>49</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>163</v>
+        <v>307</v>
       </c>
       <c r="D50" s="10" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="E50" s="9"/>
       <c r="F50" s="9" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="G50" s="9" t="s">
-        <v>166</v>
+        <v>222</v>
       </c>
       <c r="H50" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="I50" s="9"/>
+      <c r="I50" s="9" t="s">
+        <v>303</v>
+      </c>
       <c r="J50" s="9" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="K50" s="11"/>
       <c r="L50" s="11" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="M50" s="11"/>
     </row>
@@ -37649,31 +37752,31 @@
         <v>50</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>163</v>
+        <v>324</v>
       </c>
       <c r="D51" s="10" t="s">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="E51" s="9"/>
       <c r="F51" s="9" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="H51" s="9" t="s">
         <v>155</v>
       </c>
       <c r="I51" s="9"/>
       <c r="J51" s="9" t="s">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="K51" s="11"/>
       <c r="L51" s="11" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="M51" s="11"/>
     </row>
@@ -37682,56 +37785,223 @@
         <v>51</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>318</v>
+        <v>210</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>196</v>
+        <v>327</v>
       </c>
       <c r="D52" s="10" t="s">
-        <v>319</v>
-      </c>
-      <c r="E52" s="9" t="s">
-        <v>320</v>
-      </c>
+        <v>328</v>
+      </c>
+      <c r="E52" s="9"/>
       <c r="F52" s="9" t="s">
-        <v>192</v>
+        <v>153</v>
       </c>
       <c r="G52" s="9" t="s">
-        <v>193</v>
+        <v>154</v>
       </c>
       <c r="H52" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="I52" s="9" t="s">
-        <v>321</v>
-      </c>
+      <c r="I52" s="9"/>
       <c r="J52" s="9" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="K52" s="11"/>
       <c r="L52" s="11" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="M52" s="11"/>
     </row>
+    <row r="53" customFormat="false" ht="229.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="9" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="C53" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="D53" s="10" t="s">
+        <v>330</v>
+      </c>
+      <c r="E53" s="9"/>
+      <c r="F53" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="G53" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="H53" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="I53" s="9"/>
+      <c r="J53" s="9" t="s">
+        <v>331</v>
+      </c>
+      <c r="K53" s="11"/>
+      <c r="L53" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="M53" s="11"/>
+    </row>
+    <row r="54" customFormat="false" ht="229.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="9" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="C54" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="D54" s="10" t="s">
+        <v>332</v>
+      </c>
+      <c r="E54" s="9"/>
+      <c r="F54" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="G54" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="H54" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="I54" s="9"/>
+      <c r="J54" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="K54" s="11"/>
+      <c r="L54" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="M54" s="11" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="229.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="9" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="C55" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="D55" s="10" t="s">
+        <v>335</v>
+      </c>
+      <c r="E55" s="9"/>
+      <c r="F55" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="G55" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="H55" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="I55" s="9"/>
+      <c r="J55" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="K55" s="11"/>
+      <c r="L55" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="M55" s="11"/>
+    </row>
+    <row r="56" customFormat="false" ht="229.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="9" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="C56" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="D56" s="10" t="s">
+        <v>337</v>
+      </c>
+      <c r="E56" s="9"/>
+      <c r="F56" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="G56" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="H56" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="I56" s="9"/>
+      <c r="J56" s="9" t="s">
+        <v>338</v>
+      </c>
+      <c r="K56" s="11"/>
+      <c r="L56" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="M56" s="11"/>
+    </row>
+    <row r="57" customFormat="false" ht="229.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="9" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="9" t="s">
+        <v>339</v>
+      </c>
+      <c r="C57" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="D57" s="10" t="s">
+        <v>340</v>
+      </c>
+      <c r="E57" s="9" t="s">
+        <v>341</v>
+      </c>
+      <c r="F57" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="G57" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="H57" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="I57" s="9" t="s">
+        <v>342</v>
+      </c>
+      <c r="J57" s="9" t="s">
+        <v>343</v>
+      </c>
+      <c r="K57" s="11"/>
+      <c r="L57" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="M57" s="11"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M52"/>
-  <conditionalFormatting sqref="A2:M52">
-    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+  <autoFilter ref="A1:M57"/>
+  <conditionalFormatting sqref="A2:M57">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
       <formula>$L2="Delivered"</formula>
     </cfRule>
-    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
       <formula>$L2="In game"</formula>
     </cfRule>
-    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>$L2="Needs redo"</formula>
     </cfRule>
-    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>$L2="In progress"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="L2:L52" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="L2:L57" type="list">
       <formula1>"To do,In progress,Delivered,In game,Needs redo"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -37761,7 +38031,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="12" t="s">
-        <v>323</v>
+        <v>344</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37769,7 +38039,7 @@
         <v>147</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>324</v>
+        <v>345</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37777,71 +38047,71 @@
         <v>158</v>
       </c>
       <c r="B4" s="14" t="n">
-        <f aca="false">COUNTIF('Image prompts'!$L$2:$L$52,A4)</f>
-        <v>2</v>
+        <f aca="false">COUNTIF('Image prompts'!$L$2:$L$57,A4)</f>
+        <v>5</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>325</v>
+        <v>346</v>
       </c>
       <c r="B5" s="14" t="n">
-        <f aca="false">COUNTIF('Image prompts'!$L$2:$L$52,A5)</f>
+        <f aca="false">COUNTIF('Image prompts'!$L$2:$L$57,A5)</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>326</v>
+        <v>347</v>
       </c>
       <c r="B6" s="14" t="n">
-        <f aca="false">COUNTIF('Image prompts'!$L$2:$L$52,A6)</f>
+        <f aca="false">COUNTIF('Image prompts'!$L$2:$L$57,A6)</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="B7" s="14" t="n">
-        <f aca="false">COUNTIF('Image prompts'!$L$2:$L$52,A7)</f>
-        <v>48</v>
+        <f aca="false">COUNTIF('Image prompts'!$L$2:$L$57,A7)</f>
+        <v>51</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>168</v>
+        <v>348</v>
       </c>
       <c r="B8" s="14" t="n">
-        <f aca="false">COUNTIF('Image prompts'!$L$2:$L$52,A8)</f>
-        <v>1</v>
+        <f aca="false">COUNTIF('Image prompts'!$L$2:$L$57,A8)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="15" t="s">
-        <v>327</v>
+        <v>349</v>
       </c>
       <c r="B9" s="15" t="n">
         <f aca="false">SUM(B4:B8)</f>
-        <v>51</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="15" t="s">
-        <v>328</v>
+        <v>350</v>
       </c>
       <c r="B10" s="16" t="n">
         <f aca="false">IF(B9=0,0,B7/B9)</f>
-        <v>0.941176470588235</v>
+        <v>0.910714285714286</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>329</v>
+        <v>351</v>
       </c>
       <c r="B12" s="14" t="n">
-        <f aca="false">COUNTBLANK('Image prompts'!$K$2:$K$52)</f>
-        <v>51</v>
+        <f aca="false">COUNTBLANK('Image prompts'!$K$2:$K$57)</f>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -37869,150 +38139,150 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="17" t="s">
-        <v>330</v>
+        <v>352</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="14" t="s">
-        <v>331</v>
+        <v>353</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>332</v>
+        <v>354</v>
       </c>
       <c r="C3" s="18"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>333</v>
+        <v>355</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>334</v>
+        <v>356</v>
       </c>
       <c r="C4" s="19"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>335</v>
+        <v>357</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>336</v>
+        <v>358</v>
       </c>
       <c r="C5" s="20"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>337</v>
+        <v>359</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>338</v>
+        <v>360</v>
       </c>
       <c r="C6" s="21"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>339</v>
+        <v>361</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>340</v>
+        <v>362</v>
       </c>
       <c r="C7" s="22"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>341</v>
+        <v>363</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>342</v>
+        <v>364</v>
       </c>
       <c r="C8" s="23"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>343</v>
+        <v>365</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>344</v>
+        <v>366</v>
       </c>
       <c r="C9" s="24"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>345</v>
+        <v>367</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>346</v>
+        <v>368</v>
       </c>
       <c r="C10" s="25"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>347</v>
+        <v>369</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>348</v>
+        <v>370</v>
       </c>
       <c r="C11" s="26"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>349</v>
+        <v>371</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>350</v>
+        <v>372</v>
       </c>
       <c r="C12" s="27"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>351</v>
+        <v>373</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>352</v>
+        <v>374</v>
       </c>
       <c r="C13" s="28"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="14" t="s">
-        <v>353</v>
+        <v>375</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>354</v>
+        <v>376</v>
       </c>
       <c r="C14" s="29"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="14" t="s">
-        <v>355</v>
+        <v>377</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>356</v>
+        <v>378</v>
       </c>
       <c r="C15" s="30"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="14" t="s">
-        <v>357</v>
+        <v>379</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>358</v>
+        <v>380</v>
       </c>
       <c r="C16" s="31"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="14" t="s">
-        <v>359</v>
+        <v>381</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>360</v>
+        <v>382</v>
       </c>
       <c r="C17" s="32"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="14" t="s">
-        <v>361</v>
+        <v>383</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>362</v>
+        <v>384</v>
       </c>
       <c r="C18" s="33"/>
     </row>

--- a/docs/ideas.xlsx
+++ b/docs/ideas.xlsx
@@ -17,7 +17,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Palette" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Image prompts'!$A$1:$M$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Image prompts'!$A$1:$M$76</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
@@ -34838,7 +34838,7 @@
     <row r="12">
       <c r="A12" s="40" t="inlineStr">
         <is>
-          <t>Batch "Now" (2026-10-16): the street outside the office — the beggar NPC (tanuki on cardboard), street props, cherry-blossom petals. Make street_props and street_petals in the same ChatGPT chat so they match. Everything else is already in the game.</t>
+          <t>Batch "Now" (2026-10-16, office decor v2): more detailed floor and wall tiles (tiles_floor and tiles_wall are REDOS), wall decorations, island desks facing every direction, chairs, wall furniture (front + side), lobby extras, floor clutter, animated props, 4 sitting colleagues and 2 walking colleagues. Do all tile sheets in one chat, all props_* sheets in one chat, and the 6 colleagues in one chat. Everything else is already in the game.</t>
         </is>
       </c>
     </row>
@@ -34929,7 +34929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M60"/>
+  <dimension ref="A1:M76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" style="35" min="1" max="1"/>
@@ -35025,57 +35025,60 @@
       </c>
       <c r="C2" s="43" t="inlineStr">
         <is>
-          <t>Street outside the office</t>
+          <t>Tiles</t>
         </is>
       </c>
       <c r="D2" s="44" t="inlineStr">
         <is>
-          <t>npc_beggar.png</t>
-        </is>
-      </c>
-      <c r="E2" s="43" t="inlineStr">
-        <is>
-          <t>Street — the happy beggar (NPC)</t>
-        </is>
-      </c>
+          <t>tiles_floor.png</t>
+        </is>
+      </c>
+      <c r="E2" s="43" t="inlineStr"/>
       <c r="F2" s="43" t="inlineStr">
         <is>
-          <t>4 × 1</t>
+          <t>4 × 4</t>
         </is>
       </c>
       <c r="G2" s="43" t="inlineStr">
         <is>
-          <t>48×40</t>
+          <t>16×16</t>
         </is>
       </c>
       <c r="H2" s="43" t="inlineStr">
         <is>
-          <t>Wide landscape image, 1536×1024</t>
+          <t>Square image, 1024×1024</t>
         </is>
       </c>
       <c r="I2" s="43" t="inlineStr">
         <is>
-          <t>Sitting character; the code shows a speech bubble above him.</t>
+          <t>Do all sheets of this group in the same ChatGPT chat.</t>
         </is>
       </c>
       <c r="J2" s="43" t="inlineStr">
         <is>
           <t>Art style: retro 8-bit pixel art, like a Japanese console game from around 1990, set in a 1990s Japanese office. Chunky square pixels with hard edges: no anti-aliasing, no blur, no soft shading, no gradients, no painterly or paper texture. Every character and object has a 1-pixel dark ink outline. Flat colours from one small palette only: ink black, night indigo, slate blue, paper cream, warm grey, vermilion red, deep red, gold, ochre, wood brown, celadon green, moss green, sakura pink, peach. Subtle Japanese touches where they fit (seigaiha wave patterns, shoji paper screens, paper lanterns, hanko stamps, maneki-neko, daruma, bonsai). Satirical anthropomorphic animals. Clean, readable game asset. No text, letters, numbers, watermark, signature or frame.
-Camera: plain side view, like a 2D side-scrolling game; every figure stands on the bottom edge of its cell.
-Subject: A happy, relaxed old tanuki (Japanese raccoon dog) beggar sitting cross-legged on a flattened cardboard box on the pavement, wearing a patched indigo kimono and a worn straw hat, a dented tin cup in front of him, a few cherry petals on his hat. Plain side view, he faces to the LEFT. He looks completely at peace — much happier than any office worker.
-Layout: a sprite sheet on a solid flat magenta background (#FF00FF, one single pure colour, no shading, no checkerboard). An evenly spaced grid of 4 columns and 1 row of equal-sized cells with wide plain magenta gaps between the cells. Every cell shows the exact same character (same design, same colours, same size), centred in its cell, feet on the same baseline. Draw each cell at about 48×40 pixel-art resolution, so each pixel is a big visible square block. No grid lines, borders, labels or numbers. Never use magenta or purple on the subjects themselves.
+Camera: seen from directly above, completely flat.
+Subject: Floor tiles for the different zones of a 1990s Japanese office. Make them detailed and realistic for pixel art: a subtle 2–3 tone texture in every tile (carpet pile flecks, tatami straw weave, tile grout lines, metal panel screws), but still calm and low contrast so characters stand out.
+Layout: a sprite sheet on a solid flat magenta background (#FF00FF, one single pure colour, no shading, no checkerboard). An evenly spaced grid of 4 columns and 4 rows of equal-sized cells with wide plain magenta gaps between the cells. Each cell is one square FLOOR TILE drawn at 16×16 pixel-art resolution (each pixel a big visible block), filling its whole cell, seen from directly above, and tiling seamlessly with itself (left edge continues into right, top into bottom). Tiles in the same row belong together and must also fit next to each other. Low contrast so characters stand out. No grid lines, borders, labels or numbers. Never use magenta or purple on the subjects themselves.
 Cells, left to right, top to bottom:
-- Row 1: idle A, eyes closed, smiling | idle B, wiggling his toes, smiling | talking: one paw raised wisely, mouth open | laughing heartily, eyes closed, head tilted back
-Output: PNG, Wide landscape image, 1536×1024.</t>
+- Row 1: open-plan office carpet, muted celadon green: plain | small seigaiha wave pattern | worn spot | coffee stain
+- Row 2: manager's corner tatami mats: plain tatami | tatami with dark border | tatami turned 90° | tatami with a cushion mark
+- Row 3: kitchen floor: cream-and-indigo checker tiles | plain cream tiles | wet spot | crumbs
+- Row 4: archive and server room: grey metal raised floor panel | grey concrete | floor cable cover | indigo rug with gold border
+Output: PNG, Square image, 1024×1024.</t>
         </is>
       </c>
       <c r="K2" s="45" t="n"/>
       <c r="L2" s="45" t="inlineStr">
         <is>
-          <t>In game</t>
-        </is>
-      </c>
-      <c r="M2" s="45" t="n"/>
+          <t>To do</t>
+        </is>
+      </c>
+      <c r="M2" s="45" t="inlineStr">
+        <is>
+          <t>REDO with more detail (same grid, same cell meanings).</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="230" customHeight="1" s="35">
       <c r="A3" s="43" t="n">
@@ -35088,56 +35091,58 @@
       </c>
       <c r="C3" s="43" t="inlineStr">
         <is>
-          <t>Street outside the office</t>
+          <t>Tiles</t>
         </is>
       </c>
       <c r="D3" s="44" t="inlineStr">
         <is>
-          <t>street_props.png</t>
-        </is>
-      </c>
-      <c r="E3" s="43" t="inlineStr">
-        <is>
-          <t>Street — props</t>
-        </is>
-      </c>
+          <t>tiles_wall.png</t>
+        </is>
+      </c>
+      <c r="E3" s="43" t="inlineStr"/>
       <c r="F3" s="43" t="inlineStr">
         <is>
-          <t>3 × 2</t>
+          <t>4 × 4</t>
         </is>
       </c>
       <c r="G3" s="43" t="inlineStr">
         <is>
-          <t>48×48</t>
+          <t>16×16</t>
         </is>
       </c>
       <c r="H3" s="43" t="inlineStr">
         <is>
-          <t>Wide landscape image, 1536×1024</t>
-        </is>
-      </c>
-      <c r="I3" s="43" t="inlineStr"/>
+          <t>Square image, 1024×1024</t>
+        </is>
+      </c>
+      <c r="I3" s="43" t="inlineStr">
+        <is>
+          <t>Do all sheets of this group in the same ChatGPT chat.</t>
+        </is>
+      </c>
       <c r="J3" s="43" t="inlineStr">
         <is>
           <t>Art style: retro 8-bit pixel art, like a Japanese console game from around 1990, set in a 1990s Japanese office. Chunky square pixels with hard edges: no anti-aliasing, no blur, no soft shading, no gradients, no painterly or paper texture. Every character and object has a 1-pixel dark ink outline. Flat colours from one small palette only: ink black, night indigo, slate blue, paper cream, warm grey, vermilion red, deep red, gold, ochre, wood brown, celadon green, moss green, sakura pink, peach. Subtle Japanese touches where they fit (seigaiha wave patterns, shoji paper screens, paper lanterns, hanko stamps, maneki-neko, daruma, bonsai). Satirical anthropomorphic animals. Clean, readable game asset. No text, letters, numbers, watermark, signature or frame.
-Camera: plain side view, like a 2D side-scrolling game; every figure stands on the bottom edge of its cell.
-Subject: Objects on a Tokyo pavement in front of an office building in spring, plain side view, all at the same scale (a standing person would be about as tall as the street lamp is half).
-Layout: a sprite sheet on a solid flat magenta background (#FF00FF, one single pure colour, no shading, no checkerboard). An evenly spaced grid of 3 columns and 2 rows of equal-sized cells with wide plain magenta gaps between the cells. Each cell shows a different object, all drawn at the same scale as if standing on the same office floor (a person would be about 32 pixels tall), each centred in its cell and resting on the bottom of the cell. Each pixel is a big visible square block. No grid lines, borders, labels or numbers. Never use magenta or purple on the subjects themselves.
+Camera: classic Japanese top-down RPG view (three-quarter view from above and in front): you see the top and the front of things; characters show their face when they face down.
+Subject: Wall and partition tiles for a 1990s Japanese office. Make them detailed and realistic for pixel art: the cream wall has a faint plaster texture, a dark wooden skirting board along its bottom and a thin shadow line under the ceiling; partitions show a grey woven fabric texture with an aluminium top rail. Every wall-face tile uses exactly the same plain wall, skirting board and height, so they line up.
+Layout: a sprite sheet on a solid flat magenta background (#FF00FF, one single pure colour, no shading, no checkerboard). An evenly spaced grid of 4 columns and 4 rows of equal-sized cells with wide plain magenta gaps between the cells. Each cell is one square WALL or PARTITION tile drawn at 16×16 pixel-art resolution (each pixel a big visible block), filling its whole cell, in the three-quarter top-down view. Neighbouring wall tiles must line up edge to edge. No grid lines, borders, labels or numbers. Never use magenta or purple on the subjects themselves.
 Cells, left to right, top to bottom:
-- Row 1: a round red Japanese post box on a short post | a parked city bicycle with a front basket | a tall dark-green street lamp
-- Row 2: a simple stone-and-wood street bench with a few cherry petals on it | a café chalk sandwich board (drawings of a coffee cup and a cake, no text) | a small stone Jizo statue wearing a red knitted bib, with a tiny offering cup
-Output: PNG, Wide landscape image, 1536×1024.</t>
+- Row 1: wall faces: plain cream wall | wall with a night-sky window | wall with a dawn window | wall with a hanging ink-painting scroll (mountains, no writing)
+- Row 2: wall faces: closed wooden door | doorway with an indigo noren curtain | shoji paper screen | cork notice board with pinned papers (no readable text)
+- Row 3: grey fabric cubicle partition: horizontal piece | vertical piece | corner piece | end piece
+- Row 4: wall tops: wall top cap (seen from above) | top inner corner | top outer corner | square pillar
+Output: PNG, Square image, 1024×1024.</t>
         </is>
       </c>
       <c r="K3" s="45" t="n"/>
       <c r="L3" s="45" t="inlineStr">
         <is>
-          <t>In game</t>
+          <t>To do</t>
         </is>
       </c>
       <c r="M3" s="45" t="inlineStr">
         <is>
-          <t>Saved first as streets_props.png, renamed.</t>
+          <t>REDO with more detail (same grid, same cell meanings).</t>
         </is>
       </c>
     </row>
@@ -35152,22 +35157,22 @@
       </c>
       <c r="C4" s="43" t="inlineStr">
         <is>
-          <t>Street outside the office</t>
+          <t>Office decor v2</t>
         </is>
       </c>
       <c r="D4" s="44" t="inlineStr">
         <is>
-          <t>street_petals.png</t>
+          <t>tiles_floor_extra.png</t>
         </is>
       </c>
       <c r="E4" s="43" t="inlineStr">
         <is>
-          <t>Street — cherry petals in the wind</t>
+          <t>Office — extra floor tiles (mixed in at random)</t>
         </is>
       </c>
       <c r="F4" s="43" t="inlineStr">
         <is>
-          <t>4 × 2</t>
+          <t>4 × 4</t>
         </is>
       </c>
       <c r="G4" s="43" t="inlineStr">
@@ -35177,26 +35182,32 @@
       </c>
       <c r="H4" s="43" t="inlineStr">
         <is>
-          <t>Wide landscape image, 1536×1024</t>
-        </is>
-      </c>
-      <c r="I4" s="43" t="inlineStr"/>
+          <t>Square image, 1024×1024</t>
+        </is>
+      </c>
+      <c r="I4" s="43" t="inlineStr">
+        <is>
+          <t>Make in the same chat as tiles_floor.png so the colours match. Do all sheets of this group in the same ChatGPT chat.</t>
+        </is>
+      </c>
       <c r="J4" s="43" t="inlineStr">
         <is>
           <t>Art style: retro 8-bit pixel art, like a Japanese console game from around 1990, set in a 1990s Japanese office. Chunky square pixels with hard edges: no anti-aliasing, no blur, no soft shading, no gradients, no painterly or paper texture. Every character and object has a 1-pixel dark ink outline. Flat colours from one small palette only: ink black, night indigo, slate blue, paper cream, warm grey, vermilion red, deep red, gold, ochre, wood brown, celadon green, moss green, sakura pink, peach. Subtle Japanese touches where they fit (seigaiha wave patterns, shoji paper screens, paper lanterns, hanko stamps, maneki-neko, daruma, bonsai). Satirical anthropomorphic animals. Clean, readable game asset. No text, letters, numbers, watermark, signature or frame.
-Camera: plain side view, like a 2D side-scrolling game; every figure stands on the bottom edge of its cell.
-Subject: Cherry blossom petals blown by the wind, soft sakura pink with a slightly darker pink edge and a tiny notch at the tip.
-Layout: a sprite sheet on a solid flat magenta background (#FF00FF, one single pure colour, no shading, no checkerboard). An evenly spaced grid of 4 columns and 2 rows of equal-sized cells with wide plain magenta gaps between the cells. Each cell shows one small item, centred, drawn at about 16×16 pixel-art resolution so each pixel is a big visible square block. No grid lines, borders, labels or numbers. Never use magenta or purple on the subjects themselves.
+Camera: seen from directly above, completely flat.
+Subject: Extra floor tiles that mix in with the existing office floor tiles (same muted colours, same detail level, attach tiles_floor.png if you have it).
+Layout: a sprite sheet on a solid flat magenta background (#FF00FF, one single pure colour, no shading, no checkerboard). An evenly spaced grid of 4 columns and 4 rows of equal-sized cells with wide plain magenta gaps between the cells. Each cell is one square FLOOR TILE drawn at 16×16 pixel-art resolution (each pixel a big visible block), filling its whole cell, seen from directly above, and tiling seamlessly with itself (left edge continues into right, top into bottom). Tiles in the same row belong together and must also fit next to each other. Low contrast so characters stand out. No grid lines, borders, labels or numbers. Never use magenta or purple on the subjects themselves.
 Cells, left to right, top to bottom:
-- Row 1: one petal seen flat | the same petal tilted | the same petal seen from the side (thin) | the same petal tilted the other way
-- Row 2: a little cluster of three petals | a whole small five-petal blossom | a petal lying flat on the ground | a tiny twig with two blossoms
-Output: PNG, Wide landscape image, 1536×1024.</t>
+- Row 1: open-plan carpet, muted celadon green: carpet tile with the pile turned 90° | carpet tile one shade darker | worn walking path running left to right | worn walking path running top to bottom
+- Row 2: open-plan carpet: with a small floor power-outlet box | with a metal air-vent grille | with a grey cable taped down across it | with a few crumbs and a paper clip
+- Row 3: lobby and meeting room: polished cream stone tile with faint veins | the same stone tile with different veins | warm wooden floorboards | wooden floorboards with a knot
+- Row 4: kitchen, server room, archive: cream linoleum with speckles | kitchen floor drain | server-room raised floor panel with round vent holes | grey concrete with a yellow-and-black safety stripe running left to right
+Output: PNG, Square image, 1024×1024.</t>
         </is>
       </c>
       <c r="K4" s="45" t="n"/>
       <c r="L4" s="45" t="inlineStr">
         <is>
-          <t>In game</t>
+          <t>To do</t>
         </is>
       </c>
       <c r="M4" s="45" t="n"/>
@@ -35207,41 +35218,1001 @@
       </c>
       <c r="B5" s="43" t="inlineStr">
         <is>
+          <t>Now</t>
+        </is>
+      </c>
+      <c r="C5" s="43" t="inlineStr">
+        <is>
+          <t>Office decor v2</t>
+        </is>
+      </c>
+      <c r="D5" s="44" t="inlineStr">
+        <is>
+          <t>wall_decor.png</t>
+        </is>
+      </c>
+      <c r="E5" s="43" t="inlineStr">
+        <is>
+          <t>Office — things hanging on the walls</t>
+        </is>
+      </c>
+      <c r="F5" s="43" t="inlineStr">
+        <is>
+          <t>4 × 3</t>
+        </is>
+      </c>
+      <c r="G5" s="43" t="inlineStr">
+        <is>
+          <t>16×16</t>
+        </is>
+      </c>
+      <c r="H5" s="43" t="inlineStr">
+        <is>
+          <t>Square image, 1024×1024</t>
+        </is>
+      </c>
+      <c r="I5" s="43" t="inlineStr">
+        <is>
+          <t>Make in the same chat as tiles_wall.png so the wall matches.</t>
+        </is>
+      </c>
+      <c r="J5" s="43" t="inlineStr">
+        <is>
+          <t>Art style: retro 8-bit pixel art, like a Japanese console game from around 1990, set in a 1990s Japanese office. Chunky square pixels with hard edges: no anti-aliasing, no blur, no soft shading, no gradients, no painterly or paper texture. Every character and object has a 1-pixel dark ink outline. Flat colours from one small palette only: ink black, night indigo, slate blue, paper cream, warm grey, vermilion red, deep red, gold, ochre, wood brown, celadon green, moss green, sakura pink, peach. Subtle Japanese touches where they fit (seigaiha wave patterns, shoji paper screens, paper lanterns, hanko stamps, maneki-neko, daruma, bonsai). Satirical anthropomorphic animals. Clean, readable game asset. No text, letters, numbers, watermark, signature or frame.
+Camera: classic Japanese top-down RPG view (three-quarter view from above and in front): you see the top and the front of things; characters show their face when they face down.
+Subject: Wall-face tiles with things mounted on the wall. Every cell is the SAME plain cream office wall face as tiles_wall.png (same skirting board, same height, same colours), with one object hanging on it, so they slot into a wall row.
+Layout: a sprite sheet on a solid flat magenta background (#FF00FF, one single pure colour, no shading, no checkerboard). An evenly spaced grid of 4 columns and 3 rows of equal-sized cells with wide plain magenta gaps between the cells. Each cell is one square WALL or PARTITION tile drawn at 16×16 pixel-art resolution (each pixel a big visible block), filling its whole cell, in the three-quarter top-down view. Neighbouring wall tiles must line up edge to edge. No grid lines, borders, labels or numbers. Never use magenta or purple on the subjects themselves.
+Cells, left to right, top to bottom:
+- Row 1: round wall clock | paper calendar with a red daruma picture | fire extinguisher in a red wall cabinet | split air-conditioner unit high on the wall
+- Row 2: framed motivational poster of a sunrise over a mountain | framed group photo of animal coworkers | light switch and a beige intercom phone | green emergency-exit pictogram sign with a running figure (no letters)
+- Row 3: wall-mounted TV showing a bar chart | hanging plant in a macramé holder | row of coat hooks with a grey jacket | green-cross safety notice board
+Output: PNG, Square image, 1024×1024.</t>
+        </is>
+      </c>
+      <c r="K5" s="45" t="n"/>
+      <c r="L5" s="45" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+      <c r="M5" s="45" t="n"/>
+    </row>
+    <row r="6" ht="230" customHeight="1" s="35">
+      <c r="A6" s="43" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="43" t="inlineStr">
+        <is>
+          <t>Now</t>
+        </is>
+      </c>
+      <c r="C6" s="43" t="inlineStr">
+        <is>
+          <t>Office decor v2</t>
+        </is>
+      </c>
+      <c r="D6" s="44" t="inlineStr">
+        <is>
+          <t>props_desks_a.png</t>
+        </is>
+      </c>
+      <c r="E6" s="43" t="inlineStr">
+        <is>
+          <t>Office — open island desks (Japanese 'shima' layout), up and down</t>
+        </is>
+      </c>
+      <c r="F6" s="43" t="inlineStr">
+        <is>
+          <t>3 × 2</t>
+        </is>
+      </c>
+      <c r="G6" s="43" t="inlineStr">
+        <is>
+          <t>48×48</t>
+        </is>
+      </c>
+      <c r="H6" s="43" t="inlineStr">
+        <is>
+          <t>Wide landscape image, 1536×1024</t>
+        </is>
+      </c>
+      <c r="I6" s="43" t="inlineStr">
+        <is>
+          <t>Leave the empty floor where the chair would go — no chairs on this sheet. Do all sheets of this group in the same ChatGPT chat.</t>
+        </is>
+      </c>
+      <c r="J6" s="43" t="inlineStr">
+        <is>
+          <t>Art style: retro 8-bit pixel art, like a Japanese console game from around 1990, set in a 1990s Japanese office. Chunky square pixels with hard edges: no anti-aliasing, no blur, no soft shading, no gradients, no painterly or paper texture. Every character and object has a 1-pixel dark ink outline. Flat colours from one small palette only: ink black, night indigo, slate blue, paper cream, warm grey, vermilion red, deep red, gold, ochre, wood brown, celadon green, moss green, sakura pink, peach. Subtle Japanese touches where they fit (seigaiha wave patterns, shoji paper screens, paper lanterns, hanko stamps, maneki-neko, daruma, bonsai). Satirical anthropomorphic animals. Clean, readable game asset. No text, letters, numbers, watermark, signature or frame.
+Camera: classic Japanese top-down RPG view (three-quarter view from above and in front): you see the top and the front of things; characters show their face when they face down.
+Subject: Open office desks WITHOUT partitions and WITHOUT chairs (chairs and people are added separately), for a Japanese island layout where desks are pushed together facing each other. Grey steel desks with a beige CRT monitor, keyboard, papers and a desk phone.
+Layout: a sprite sheet on a solid flat magenta background (#FF00FF, one single pure colour, no shading, no checkerboard). An evenly spaced grid of 3 columns and 2 rows of equal-sized cells with wide plain magenta gaps between the cells. Each cell shows a different object, all drawn at the same scale as if standing on the same office floor (a person would be about 32 pixels tall), each centred in its cell and resting on the bottom of the cell. Each pixel is a big visible square block. No grid lines, borders, labels or numbers. Never use magenta or purple on the subjects themselves.
+Cells, left to right, top to bottom:
+- Row 1: desk where the worker faces UP (sits below the desk): we see the desk top and the monitor SCREEN — tidy desk | messy desk with paper piles | desk with a small cactus and a family photo
+- Row 2: the same three desks seen from the OTHER side, where the worker faces DOWN (sits above the desk, facing the viewer): we see the FRONT PANEL of the desk and the BACK of the monitor — tidy | messy | with a cactus
+Output: PNG, Wide landscape image, 1536×1024.</t>
+        </is>
+      </c>
+      <c r="K6" s="45" t="n"/>
+      <c r="L6" s="45" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+      <c r="M6" s="45" t="n"/>
+    </row>
+    <row r="7" ht="230" customHeight="1" s="35">
+      <c r="A7" s="43" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="43" t="inlineStr">
+        <is>
+          <t>Now</t>
+        </is>
+      </c>
+      <c r="C7" s="43" t="inlineStr">
+        <is>
+          <t>Office decor v2</t>
+        </is>
+      </c>
+      <c r="D7" s="44" t="inlineStr">
+        <is>
+          <t>props_desks_b.png</t>
+        </is>
+      </c>
+      <c r="E7" s="43" t="inlineStr">
+        <is>
+          <t>Office — side-facing desks and island extras</t>
+        </is>
+      </c>
+      <c r="F7" s="43" t="inlineStr">
+        <is>
+          <t>3 × 2</t>
+        </is>
+      </c>
+      <c r="G7" s="43" t="inlineStr">
+        <is>
+          <t>48×48</t>
+        </is>
+      </c>
+      <c r="H7" s="43" t="inlineStr">
+        <is>
+          <t>Wide landscape image, 1536×1024</t>
+        </is>
+      </c>
+      <c r="I7" s="43" t="inlineStr">
+        <is>
+          <t>Do all sheets of this group in the same ChatGPT chat.</t>
+        </is>
+      </c>
+      <c r="J7" s="43" t="inlineStr">
+        <is>
+          <t>Art style: retro 8-bit pixel art, like a Japanese console game from around 1990, set in a 1990s Japanese office. Chunky square pixels with hard edges: no anti-aliasing, no blur, no soft shading, no gradients, no painterly or paper texture. Every character and object has a 1-pixel dark ink outline. Flat colours from one small palette only: ink black, night indigo, slate blue, paper cream, warm grey, vermilion red, deep red, gold, ochre, wood brown, celadon green, moss green, sakura pink, peach. Subtle Japanese touches where they fit (seigaiha wave patterns, shoji paper screens, paper lanterns, hanko stamps, maneki-neko, daruma, bonsai). Satirical anthropomorphic animals. Clean, readable game asset. No text, letters, numbers, watermark, signature or frame.
+Camera: classic Japanese top-down RPG view (three-quarter view from above and in front): you see the top and the front of things; characters show their face when they face down.
+Subject: More office furniture in the same style as props_desks_a.png, WITHOUT chairs.
+Layout: a sprite sheet on a solid flat magenta background (#FF00FF, one single pure colour, no shading, no checkerboard). An evenly spaced grid of 3 columns and 2 rows of equal-sized cells with wide plain magenta gaps between the cells. Each cell shows a different object, all drawn at the same scale as if standing on the same office floor (a person would be about 32 pixels tall), each centred in its cell and resting on the bottom of the cell. Each pixel is a big visible square block. No grid lines, borders, labels or numbers. Never use magenta or purple on the subjects themselves.
+Cells, left to right, top to bottom:
+- Row 1: grey steel desk where the worker faces LEFT (sits to the right of it): monitor seen from the side with its screen pointing right — tidy | messy | with a cactus
+- Row 2: section chief's wider desk at the head of a desk island, worker faces DOWN: back of the monitor, an in-tray and a red hanko stamp | free-standing grey fabric partition screen on two feet | long planter box with green plants used as a room divider
+Output: PNG, Wide landscape image, 1536×1024.</t>
+        </is>
+      </c>
+      <c r="K7" s="45" t="n"/>
+      <c r="L7" s="45" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+      <c r="M7" s="45" t="n"/>
+    </row>
+    <row r="8" ht="230" customHeight="1" s="35">
+      <c r="A8" s="43" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="43" t="inlineStr">
+        <is>
+          <t>Now</t>
+        </is>
+      </c>
+      <c r="C8" s="43" t="inlineStr">
+        <is>
+          <t>Office decor v2</t>
+        </is>
+      </c>
+      <c r="D8" s="44" t="inlineStr">
+        <is>
+          <t>props_chairs.png</t>
+        </is>
+      </c>
+      <c r="E8" s="43" t="inlineStr">
+        <is>
+          <t>Office — chairs in every direction</t>
+        </is>
+      </c>
+      <c r="F8" s="43" t="inlineStr">
+        <is>
+          <t>4 × 2</t>
+        </is>
+      </c>
+      <c r="G8" s="43" t="inlineStr">
+        <is>
+          <t>24×24</t>
+        </is>
+      </c>
+      <c r="H8" s="43" t="inlineStr">
+        <is>
+          <t>Wide landscape image, 1536×1024</t>
+        </is>
+      </c>
+      <c r="I8" s="43" t="inlineStr">
+        <is>
+          <t>Do all sheets of this group in the same ChatGPT chat.</t>
+        </is>
+      </c>
+      <c r="J8" s="43" t="inlineStr">
+        <is>
+          <t>Art style: retro 8-bit pixel art, like a Japanese console game from around 1990, set in a 1990s Japanese office. Chunky square pixels with hard edges: no anti-aliasing, no blur, no soft shading, no gradients, no painterly or paper texture. Every character and object has a 1-pixel dark ink outline. Flat colours from one small palette only: ink black, night indigo, slate blue, paper cream, warm grey, vermilion red, deep red, gold, ochre, wood brown, celadon green, moss green, sakura pink, peach. Subtle Japanese touches where they fit (seigaiha wave patterns, shoji paper screens, paper lanterns, hanko stamps, maneki-neko, daruma, bonsai). Satirical anthropomorphic animals. Clean, readable game asset. No text, letters, numbers, watermark, signature or frame.
+Camera: classic Japanese top-down RPG view (three-quarter view from above and in front): you see the top and the front of things; characters show their face when they face down.
+Subject: Empty office chairs in different directions, same scale as the office props (a person would be about 32 pixels tall).
+Layout: a sprite sheet on a solid flat magenta background (#FF00FF, one single pure colour, no shading, no checkerboard). An evenly spaced grid of 4 columns and 2 rows of equal-sized cells with wide plain magenta gaps between the cells. Each cell shows a different object, all drawn at the same scale as if standing on the same office floor (a person would be about 32 pixels tall), each centred in its cell and resting on the bottom of the cell. Each pixel is a big visible square block. No grid lines, borders, labels or numbers. Never use magenta or purple on the subjects themselves.
+Cells, left to right, top to bottom:
+- Row 1: dark navy rolling office chair seen from BEHIND (facing up) | the same chair seen from the FRONT (facing down) | the same chair facing LEFT | the same chair rolled away and turned at an angle
+- Row 2: steel-and-wood meeting chair seen from BEHIND | from the FRONT | facing LEFT | small round folding stool
+Output: PNG, Wide landscape image, 1536×1024.</t>
+        </is>
+      </c>
+      <c r="K8" s="45" t="n"/>
+      <c r="L8" s="45" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+      <c r="M8" s="45" t="n"/>
+    </row>
+    <row r="9" ht="230" customHeight="1" s="35">
+      <c r="A9" s="43" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="43" t="inlineStr">
+        <is>
+          <t>Now</t>
+        </is>
+      </c>
+      <c r="C9" s="43" t="inlineStr">
+        <is>
+          <t>Office decor v2</t>
+        </is>
+      </c>
+      <c r="D9" s="44" t="inlineStr">
+        <is>
+          <t>props_wall_front.png</t>
+        </is>
+      </c>
+      <c r="E9" s="43" t="inlineStr">
+        <is>
+          <t>Office — furniture that stands against a wall (front view)</t>
+        </is>
+      </c>
+      <c r="F9" s="43" t="inlineStr">
+        <is>
+          <t>3 × 2</t>
+        </is>
+      </c>
+      <c r="G9" s="43" t="inlineStr">
+        <is>
+          <t>48×48</t>
+        </is>
+      </c>
+      <c r="H9" s="43" t="inlineStr">
+        <is>
+          <t>Wide landscape image, 1536×1024</t>
+        </is>
+      </c>
+      <c r="I9" s="43" t="inlineStr">
+        <is>
+          <t>Do all sheets of this group in the same ChatGPT chat.</t>
+        </is>
+      </c>
+      <c r="J9" s="43" t="inlineStr">
+        <is>
+          <t>Art style: retro 8-bit pixel art, like a Japanese console game from around 1990, set in a 1990s Japanese office. Chunky square pixels with hard edges: no anti-aliasing, no blur, no soft shading, no gradients, no painterly or paper texture. Every character and object has a 1-pixel dark ink outline. Flat colours from one small palette only: ink black, night indigo, slate blue, paper cream, warm grey, vermilion red, deep red, gold, ochre, wood brown, celadon green, moss green, sakura pink, peach. Subtle Japanese touches where they fit (seigaiha wave patterns, shoji paper screens, paper lanterns, hanko stamps, maneki-neko, daruma, bonsai). Satirical anthropomorphic animals. Clean, readable game asset. No text, letters, numbers, watermark, signature or frame.
+Camera: classic Japanese top-down RPG view (three-quarter view from above and in front): you see the top and the front of things; characters show their face when they face down.
+Subject: Furniture that stands with its back flat against a wall, seen from the front. The back edge of each object is a straight line at the top so it sits flush against the wall.
+Layout: a sprite sheet on a solid flat magenta background (#FF00FF, one single pure colour, no shading, no checkerboard). An evenly spaced grid of 3 columns and 2 rows of equal-sized cells with wide plain magenta gaps between the cells. Each cell shows a different object, all drawn at the same scale as if standing on the same office floor (a person would be about 32 pixels tall), each centred in its cell and resting on the bottom of the cell. Each pixel is a big visible square block. No grid lines, borders, labels or numbers. Never use magenta or purple on the subjects themselves.
+Cells, left to right, top to bottom:
+- Row 1: tall bookshelf with binders and a small daruma | grey steel employee lockers | Japanese recycling station: three bins in red, blue and green (no text)
+- Row 2: sink counter with a dish rack and a microwave | low cabinet with a potted plant and a desk phone on top | photocopier with paper stacks and a toner box
+Output: PNG, Wide landscape image, 1536×1024.</t>
+        </is>
+      </c>
+      <c r="K9" s="45" t="n"/>
+      <c r="L9" s="45" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+      <c r="M9" s="45" t="n"/>
+    </row>
+    <row r="10" ht="230" customHeight="1" s="35">
+      <c r="A10" s="43" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="43" t="inlineStr">
+        <is>
+          <t>Now</t>
+        </is>
+      </c>
+      <c r="C10" s="43" t="inlineStr">
+        <is>
+          <t>Office decor v2</t>
+        </is>
+      </c>
+      <c r="D10" s="44" t="inlineStr">
+        <is>
+          <t>props_wall_side.png</t>
+        </is>
+      </c>
+      <c r="E10" s="43" t="inlineStr">
+        <is>
+          <t>Office — the same wall furniture seen from the side</t>
+        </is>
+      </c>
+      <c r="F10" s="43" t="inlineStr">
+        <is>
+          <t>3 × 2</t>
+        </is>
+      </c>
+      <c r="G10" s="43" t="inlineStr">
+        <is>
+          <t>48×48</t>
+        </is>
+      </c>
+      <c r="H10" s="43" t="inlineStr">
+        <is>
+          <t>Wide landscape image, 1536×1024</t>
+        </is>
+      </c>
+      <c r="I10" s="43" t="inlineStr">
+        <is>
+          <t>Mirrored in code for the left wall. Do all sheets of this group in the same ChatGPT chat.</t>
+        </is>
+      </c>
+      <c r="J10" s="43" t="inlineStr">
+        <is>
+          <t>Art style: retro 8-bit pixel art, like a Japanese console game from around 1990, set in a 1990s Japanese office. Chunky square pixels with hard edges: no anti-aliasing, no blur, no soft shading, no gradients, no painterly or paper texture. Every character and object has a 1-pixel dark ink outline. Flat colours from one small palette only: ink black, night indigo, slate blue, paper cream, warm grey, vermilion red, deep red, gold, ochre, wood brown, celadon green, moss green, sakura pink, peach. Subtle Japanese touches where they fit (seigaiha wave patterns, shoji paper screens, paper lanterns, hanko stamps, maneki-neko, daruma, bonsai). Satirical anthropomorphic animals. Clean, readable game asset. No text, letters, numbers, watermark, signature or frame.
+Camera: classic Japanese top-down RPG view (three-quarter view from above and in front): you see the top and the front of things; characters show their face when they face down.
+Subject: The SAME six objects as props_wall_front.png (attach it), now standing against a wall on the RIGHT side of the room, so their front faces LEFT. Narrow and deep, seen from the side and slightly above. The right edge of each object is straight so it sits flush against the wall.
+Layout: a sprite sheet on a solid flat magenta background (#FF00FF, one single pure colour, no shading, no checkerboard). An evenly spaced grid of 3 columns and 2 rows of equal-sized cells with wide plain magenta gaps between the cells. Each cell shows a different object, all drawn at the same scale as if standing on the same office floor (a person would be about 32 pixels tall), each centred in its cell and resting on the bottom of the cell. Each pixel is a big visible square block. No grid lines, borders, labels or numbers. Never use magenta or purple on the subjects themselves.
+Cells, left to right, top to bottom:
+- Row 1: tall bookshelf facing LEFT | steel lockers facing LEFT | recycling station facing LEFT
+- Row 2: sink counter facing LEFT | low cabinet facing LEFT | photocopier facing LEFT
+Output: PNG, Wide landscape image, 1536×1024.</t>
+        </is>
+      </c>
+      <c r="K10" s="45" t="n"/>
+      <c r="L10" s="45" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+      <c r="M10" s="45" t="n"/>
+    </row>
+    <row r="11" ht="230" customHeight="1" s="35">
+      <c r="A11" s="43" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="43" t="inlineStr">
+        <is>
+          <t>Now</t>
+        </is>
+      </c>
+      <c r="C11" s="43" t="inlineStr">
+        <is>
+          <t>Office decor v2</t>
+        </is>
+      </c>
+      <c r="D11" s="44" t="inlineStr">
+        <is>
+          <t>props_lounge.png</t>
+        </is>
+      </c>
+      <c r="E11" s="43" t="inlineStr">
+        <is>
+          <t>Office — lobby and manager extras</t>
+        </is>
+      </c>
+      <c r="F11" s="43" t="inlineStr">
+        <is>
+          <t>3 × 2</t>
+        </is>
+      </c>
+      <c r="G11" s="43" t="inlineStr">
+        <is>
+          <t>48×48</t>
+        </is>
+      </c>
+      <c r="H11" s="43" t="inlineStr">
+        <is>
+          <t>Wide landscape image, 1536×1024</t>
+        </is>
+      </c>
+      <c r="I11" s="43" t="inlineStr">
+        <is>
+          <t>Do all sheets of this group in the same ChatGPT chat.</t>
+        </is>
+      </c>
+      <c r="J11" s="43" t="inlineStr">
+        <is>
+          <t>Art style: retro 8-bit pixel art, like a Japanese console game from around 1990, set in a 1990s Japanese office. Chunky square pixels with hard edges: no anti-aliasing, no blur, no soft shading, no gradients, no painterly or paper texture. Every character and object has a 1-pixel dark ink outline. Flat colours from one small palette only: ink black, night indigo, slate blue, paper cream, warm grey, vermilion red, deep red, gold, ochre, wood brown, celadon green, moss green, sakura pink, peach. Subtle Japanese touches where they fit (seigaiha wave patterns, shoji paper screens, paper lanterns, hanko stamps, maneki-neko, daruma, bonsai). Satirical anthropomorphic animals. Clean, readable game asset. No text, letters, numbers, watermark, signature or frame.
+Camera: classic Japanese top-down RPG view (three-quarter view from above and in front): you see the top and the front of things; characters show their face when they face down.
+Subject: Furniture for the lift lobby and the manager's corner.
+Layout: a sprite sheet on a solid flat magenta background (#FF00FF, one single pure colour, no shading, no checkerboard). An evenly spaced grid of 3 columns and 2 rows of equal-sized cells with wide plain magenta gaps between the cells. Each cell shows a different object, all drawn at the same scale as if standing on the same office floor (a person would be about 32 pixels tall), each centred in its cell and resting on the bottom of the cell. Each pixel is a big visible square block. No grid lines, borders, labels or numbers. Never use magenta or purple on the subjects themselves.
+Cells, left to right, top to bottom:
+- Row 1: wooden reception counter with a bell and a small ikebana | waiting bench facing DOWN | big potted kentia palm
+- Row 2: green golf putting mat with a ball and a putter | low coffee table with magazines | two-seat leather sofa facing DOWN
+Output: PNG, Wide landscape image, 1536×1024.</t>
+        </is>
+      </c>
+      <c r="K11" s="45" t="n"/>
+      <c r="L11" s="45" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+      <c r="M11" s="45" t="n"/>
+    </row>
+    <row r="12" ht="230" customHeight="1" s="35">
+      <c r="A12" s="43" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="43" t="inlineStr">
+        <is>
+          <t>Now</t>
+        </is>
+      </c>
+      <c r="C12" s="43" t="inlineStr">
+        <is>
+          <t>Office decor v2</t>
+        </is>
+      </c>
+      <c r="D12" s="44" t="inlineStr">
+        <is>
+          <t>props_clutter.png</t>
+        </is>
+      </c>
+      <c r="E12" s="43" t="inlineStr">
+        <is>
+          <t>Office — clutter lying on the floor (walk over it)</t>
+        </is>
+      </c>
+      <c r="F12" s="43" t="inlineStr">
+        <is>
+          <t>4 × 2</t>
+        </is>
+      </c>
+      <c r="G12" s="43" t="inlineStr">
+        <is>
+          <t>24×24</t>
+        </is>
+      </c>
+      <c r="H12" s="43" t="inlineStr">
+        <is>
+          <t>Wide landscape image, 1536×1024</t>
+        </is>
+      </c>
+      <c r="I12" s="43" t="inlineStr">
+        <is>
+          <t>Do all sheets of this group in the same ChatGPT chat.</t>
+        </is>
+      </c>
+      <c r="J12" s="43" t="inlineStr">
+        <is>
+          <t>Art style: retro 8-bit pixel art, like a Japanese console game from around 1990, set in a 1990s Japanese office. Chunky square pixels with hard edges: no anti-aliasing, no blur, no soft shading, no gradients, no painterly or paper texture. Every character and object has a 1-pixel dark ink outline. Flat colours from one small palette only: ink black, night indigo, slate blue, paper cream, warm grey, vermilion red, deep red, gold, ochre, wood brown, celadon green, moss green, sakura pink, peach. Subtle Japanese touches where they fit (seigaiha wave patterns, shoji paper screens, paper lanterns, hanko stamps, maneki-neko, daruma, bonsai). Satirical anthropomorphic animals. Clean, readable game asset. No text, letters, numbers, watermark, signature or frame.
+Camera: classic Japanese top-down RPG view (three-quarter view from above and in front): you see the top and the front of things; characters show their face when they face down.
+Subject: Small flat things lying on an office floor, seen from above. Low and flat, so a character can walk over them.
+Layout: a sprite sheet on a solid flat magenta background (#FF00FF, one single pure colour, no shading, no checkerboard). An evenly spaced grid of 4 columns and 2 rows of equal-sized cells with wide plain magenta gaps between the cells. Each cell shows a different object, all drawn at the same scale as if standing on the same office floor (a person would be about 32 pixels tall), each centred in its cell and resting on the bottom of the cell. Each pixel is a big visible square block. No grid lines, borders, labels or numbers. Never use magenta or purple on the subjects themselves.
+Cells, left to right, top to bottom:
+- Row 1: scattered papers | tangled power cable with a power strip | crumpled paper balls | a dropped tie and a sticky note
+- Row 2: an open cardboard box with stuff | a pair of office slippers | a toppled paper coffee cup with a small brown spill | a stack of magazines tied with string
+Output: PNG, Wide landscape image, 1536×1024.</t>
+        </is>
+      </c>
+      <c r="K12" s="45" t="n"/>
+      <c r="L12" s="45" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+      <c r="M12" s="45" t="n"/>
+    </row>
+    <row r="13" ht="230" customHeight="1" s="35">
+      <c r="A13" s="43" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="43" t="inlineStr">
+        <is>
+          <t>Now</t>
+        </is>
+      </c>
+      <c r="C13" s="43" t="inlineStr">
+        <is>
+          <t>Office decor v2</t>
+        </is>
+      </c>
+      <c r="D13" s="44" t="inlineStr">
+        <is>
+          <t>props_anim.png</t>
+        </is>
+      </c>
+      <c r="E13" s="43" t="inlineStr">
+        <is>
+          <t>Office — animated props (frames of a loop)</t>
+        </is>
+      </c>
+      <c r="F13" s="43" t="inlineStr">
+        <is>
+          <t>4 × 3</t>
+        </is>
+      </c>
+      <c r="G13" s="43" t="inlineStr">
+        <is>
+          <t>48×48</t>
+        </is>
+      </c>
+      <c r="H13" s="43" t="inlineStr">
+        <is>
+          <t>Wide landscape image, 1536×1024</t>
+        </is>
+      </c>
+      <c r="I13" s="43" t="inlineStr">
+        <is>
+          <t>Do all sheets of this group in the same ChatGPT chat.</t>
+        </is>
+      </c>
+      <c r="J13" s="43" t="inlineStr">
+        <is>
+          <t>Art style: retro 8-bit pixel art, like a Japanese console game from around 1990, set in a 1990s Japanese office. Chunky square pixels with hard edges: no anti-aliasing, no blur, no soft shading, no gradients, no painterly or paper texture. Every character and object has a 1-pixel dark ink outline. Flat colours from one small palette only: ink black, night indigo, slate blue, paper cream, warm grey, vermilion red, deep red, gold, ochre, wood brown, celadon green, moss green, sakura pink, peach. Subtle Japanese touches where they fit (seigaiha wave patterns, shoji paper screens, paper lanterns, hanko stamps, maneki-neko, daruma, bonsai). Satirical anthropomorphic animals. Clean, readable game asset. No text, letters, numbers, watermark, signature or frame.
+Camera: classic Japanese top-down RPG view (three-quarter view from above and in front): you see the top and the front of things; characters show their face when they face down.
+Subject: Three animated office props, 4 animation frames each. The object stays EXACTLY the same size and place in every frame of a row; only the moving part changes.
+Layout: a sprite sheet on a solid flat magenta background (#FF00FF, one single pure colour, no shading, no checkerboard). An evenly spaced grid of 4 columns and 3 rows of equal-sized cells with wide plain magenta gaps between the cells. Each cell shows a different object, all drawn at the same scale as if standing on the same office floor (a person would be about 32 pixels tall), each centred in its cell and resting on the bottom of the cell. Each pixel is a big visible square block. No grid lines, borders, labels or numbers. Never use magenta or purple on the subjects themselves.
+Cells, left to right, top to bottom:
+- Row 1: small koi aquarium on a cabinet: frame 1 | frame 2 | frame 3 | frame 4 (the orange koi swim slowly from left to right, bubbles rise)
+- Row 2: water cooler with a big blue bottle: frame 1 | frame 2 | frame 3 | frame 4 (a big air bubble rises up through the bottle)
+- Row 3: big standing electric fan: frame 1 | frame 2 | frame 3 | frame 4 (the blades turn a quarter turn each frame)
+Output: PNG, Wide landscape image, 1536×1024.</t>
+        </is>
+      </c>
+      <c r="K13" s="45" t="n"/>
+      <c r="L13" s="45" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+      <c r="M13" s="45" t="n"/>
+    </row>
+    <row r="14" ht="230" customHeight="1" s="35">
+      <c r="A14" s="43" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="43" t="inlineStr">
+        <is>
+          <t>Now</t>
+        </is>
+      </c>
+      <c r="C14" s="43" t="inlineStr">
+        <is>
+          <t>Office decor v2</t>
+        </is>
+      </c>
+      <c r="D14" s="44" t="inlineStr">
+        <is>
+          <t>npc_worker_mouse.png</t>
+        </is>
+      </c>
+      <c r="E14" s="43" t="inlineStr">
+        <is>
+          <t>Office — background colleague, sitting (cannot be talked to)</t>
+        </is>
+      </c>
+      <c r="F14" s="43" t="inlineStr">
+        <is>
+          <t>4 × 3</t>
+        </is>
+      </c>
+      <c r="G14" s="43" t="inlineStr">
+        <is>
+          <t>32×32</t>
+        </is>
+      </c>
+      <c r="H14" s="43" t="inlineStr">
+        <is>
+          <t>Wide landscape image, 1536×1024</t>
+        </is>
+      </c>
+      <c r="I14" s="43" t="inlineStr">
+        <is>
+          <t>Typing = hands forward at keyboard height, arms move between A and B.</t>
+        </is>
+      </c>
+      <c r="J14" s="43" t="inlineStr">
+        <is>
+          <t>Art style: retro 8-bit pixel art, like a Japanese console game from around 1990, set in a 1990s Japanese office. Chunky square pixels with hard edges: no anti-aliasing, no blur, no soft shading, no gradients, no painterly or paper texture. Every character and object has a 1-pixel dark ink outline. Flat colours from one small palette only: ink black, night indigo, slate blue, paper cream, warm grey, vermilion red, deep red, gold, ochre, wood brown, celadon green, moss green, sakura pink, peach. Subtle Japanese touches where they fit (seigaiha wave patterns, shoji paper screens, paper lanterns, hanko stamps, maneki-neko, daruma, bonsai). Satirical anthropomorphic animals. Clean, readable game asset. No text, letters, numbers, watermark, signature or frame.
+Camera: classic Japanese top-down RPG view (three-quarter view from above and in front): you see the top and the front of things; characters show their face when they face down.
+Subject: a small grey mouse office worker in a white shirt and a thin black tie, SITTING on a dark navy rolling office chair (the chair is part of the picture and identical in every cell). Draw ONLY the person and the chair: NO desk, NO computer.
+Layout: a sprite sheet on a solid flat magenta background (#FF00FF, one single pure colour, no shading, no checkerboard). An evenly spaced grid of 4 columns and 3 rows of equal-sized cells with wide plain magenta gaps between the cells. Every cell shows the exact same character (same design, same colours, same size), centred in its cell, feet on the same baseline. Draw each cell at about 32×32 pixel-art resolution, so each pixel is a big visible square block. No grid lines, borders, labels or numbers. Never use magenta or purple on the subjects themselves.
+Cells, left to right, top to bottom:
+- Row 1: seen from BEHIND (facing UP, working at a desk above them): typing A | typing B | sipping from a teacup | rubbing his tired eyes
+- Row 2: facing DOWN (towards the viewer): typing A | typing B | sipping from a teacup | rubbing his tired eyes
+- Row 3: facing LEFT (side profile): typing A | typing B | sipping from a teacup | rubbing his tired eyes
+Output: PNG, Wide landscape image, 1536×1024.</t>
+        </is>
+      </c>
+      <c r="K14" s="45" t="n"/>
+      <c r="L14" s="45" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+      <c r="M14" s="45" t="n"/>
+    </row>
+    <row r="15" ht="230" customHeight="1" s="35">
+      <c r="A15" s="43" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="43" t="inlineStr">
+        <is>
+          <t>Now</t>
+        </is>
+      </c>
+      <c r="C15" s="43" t="inlineStr">
+        <is>
+          <t>Office decor v2</t>
+        </is>
+      </c>
+      <c r="D15" s="44" t="inlineStr">
+        <is>
+          <t>npc_worker_beaver.png</t>
+        </is>
+      </c>
+      <c r="E15" s="43" t="inlineStr">
+        <is>
+          <t>Office — background colleague, sitting (cannot be talked to)</t>
+        </is>
+      </c>
+      <c r="F15" s="43" t="inlineStr">
+        <is>
+          <t>4 × 3</t>
+        </is>
+      </c>
+      <c r="G15" s="43" t="inlineStr">
+        <is>
+          <t>32×32</t>
+        </is>
+      </c>
+      <c r="H15" s="43" t="inlineStr">
+        <is>
+          <t>Wide landscape image, 1536×1024</t>
+        </is>
+      </c>
+      <c r="I15" s="43" t="inlineStr">
+        <is>
+          <t>Typing = hands forward at keyboard height, arms move between A and B.</t>
+        </is>
+      </c>
+      <c r="J15" s="43" t="inlineStr">
+        <is>
+          <t>Art style: retro 8-bit pixel art, like a Japanese console game from around 1990, set in a 1990s Japanese office. Chunky square pixels with hard edges: no anti-aliasing, no blur, no soft shading, no gradients, no painterly or paper texture. Every character and object has a 1-pixel dark ink outline. Flat colours from one small palette only: ink black, night indigo, slate blue, paper cream, warm grey, vermilion red, deep red, gold, ochre, wood brown, celadon green, moss green, sakura pink, peach. Subtle Japanese touches where they fit (seigaiha wave patterns, shoji paper screens, paper lanterns, hanko stamps, maneki-neko, daruma, bonsai). Satirical anthropomorphic animals. Clean, readable game asset. No text, letters, numbers, watermark, signature or frame.
+Camera: classic Japanese top-down RPG view (three-quarter view from above and in front): you see the top and the front of things; characters show their face when they face down.
+Subject: a stocky beaver office worker in a mustard cardigan and glasses, SITTING on a dark navy rolling office chair (the chair is part of the picture and identical in every cell). Draw ONLY the person and the chair: NO desk, NO computer.
+Layout: a sprite sheet on a solid flat magenta background (#FF00FF, one single pure colour, no shading, no checkerboard). An evenly spaced grid of 4 columns and 3 rows of equal-sized cells with wide plain magenta gaps between the cells. Every cell shows the exact same character (same design, same colours, same size), centred in its cell, feet on the same baseline. Draw each cell at about 32×32 pixel-art resolution, so each pixel is a big visible square block. No grid lines, borders, labels or numbers. Never use magenta or purple on the subjects themselves.
+Cells, left to right, top to bottom:
+- Row 1: seen from BEHIND (facing UP, working at a desk above them): typing A | typing B | talking on a beige desk phone | stretching both arms up
+- Row 2: facing DOWN (towards the viewer): typing A | typing B | talking on a beige desk phone | stretching both arms up
+- Row 3: facing LEFT (side profile): typing A | typing B | talking on a beige desk phone | stretching both arms up
+Output: PNG, Wide landscape image, 1536×1024.</t>
+        </is>
+      </c>
+      <c r="K15" s="45" t="n"/>
+      <c r="L15" s="45" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+      <c r="M15" s="45" t="n"/>
+    </row>
+    <row r="16" ht="230" customHeight="1" s="35">
+      <c r="A16" s="43" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="43" t="inlineStr">
+        <is>
+          <t>Now</t>
+        </is>
+      </c>
+      <c r="C16" s="43" t="inlineStr">
+        <is>
+          <t>Office decor v2</t>
+        </is>
+      </c>
+      <c r="D16" s="44" t="inlineStr">
+        <is>
+          <t>npc_worker_frog.png</t>
+        </is>
+      </c>
+      <c r="E16" s="43" t="inlineStr">
+        <is>
+          <t>Office — background colleague, sitting (cannot be talked to)</t>
+        </is>
+      </c>
+      <c r="F16" s="43" t="inlineStr">
+        <is>
+          <t>4 × 3</t>
+        </is>
+      </c>
+      <c r="G16" s="43" t="inlineStr">
+        <is>
+          <t>32×32</t>
+        </is>
+      </c>
+      <c r="H16" s="43" t="inlineStr">
+        <is>
+          <t>Wide landscape image, 1536×1024</t>
+        </is>
+      </c>
+      <c r="I16" s="43" t="inlineStr">
+        <is>
+          <t>Typing = hands forward at keyboard height, arms move between A and B.</t>
+        </is>
+      </c>
+      <c r="J16" s="43" t="inlineStr">
+        <is>
+          <t>Art style: retro 8-bit pixel art, like a Japanese console game from around 1990, set in a 1990s Japanese office. Chunky square pixels with hard edges: no anti-aliasing, no blur, no soft shading, no gradients, no painterly or paper texture. Every character and object has a 1-pixel dark ink outline. Flat colours from one small palette only: ink black, night indigo, slate blue, paper cream, warm grey, vermilion red, deep red, gold, ochre, wood brown, celadon green, moss green, sakura pink, peach. Subtle Japanese touches where they fit (seigaiha wave patterns, shoji paper screens, paper lanterns, hanko stamps, maneki-neko, daruma, bonsai). Satirical anthropomorphic animals. Clean, readable game asset. No text, letters, numbers, watermark, signature or frame.
+Camera: classic Japanese top-down RPG view (three-quarter view from above and in front): you see the top and the front of things; characters show their face when they face down.
+Subject: a green frog office worker in a short-sleeved shirt with a pocket of pens, SITTING on a dark navy rolling office chair (the chair is part of the picture and identical in every cell). Draw ONLY the person and the chair: NO desk, NO computer.
+Layout: a sprite sheet on a solid flat magenta background (#FF00FF, one single pure colour, no shading, no checkerboard). An evenly spaced grid of 4 columns and 3 rows of equal-sized cells with wide plain magenta gaps between the cells. Every cell shows the exact same character (same design, same colours, same size), centred in its cell, feet on the same baseline. Draw each cell at about 32×32 pixel-art resolution, so each pixel is a big visible square block. No grid lines, borders, labels or numbers. Never use magenta or purple on the subjects themselves.
+Cells, left to right, top to bottom:
+- Row 1: seen from BEHIND (facing UP, working at a desk above them): typing A | typing B | stamping a paper with a red hanko | dozing off, head nodding
+- Row 2: facing DOWN (towards the viewer): typing A | typing B | stamping a paper with a red hanko | dozing off, head nodding
+- Row 3: facing LEFT (side profile): typing A | typing B | stamping a paper with a red hanko | dozing off, head nodding
+Output: PNG, Wide landscape image, 1536×1024.</t>
+        </is>
+      </c>
+      <c r="K16" s="45" t="n"/>
+      <c r="L16" s="45" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+      <c r="M16" s="45" t="n"/>
+    </row>
+    <row r="17" ht="230" customHeight="1" s="35">
+      <c r="A17" s="43" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="43" t="inlineStr">
+        <is>
+          <t>Now</t>
+        </is>
+      </c>
+      <c r="C17" s="43" t="inlineStr">
+        <is>
+          <t>Office decor v2</t>
+        </is>
+      </c>
+      <c r="D17" s="44" t="inlineStr">
+        <is>
+          <t>npc_worker_cat.png</t>
+        </is>
+      </c>
+      <c r="E17" s="43" t="inlineStr">
+        <is>
+          <t>Office — background colleague, sitting (cannot be talked to)</t>
+        </is>
+      </c>
+      <c r="F17" s="43" t="inlineStr">
+        <is>
+          <t>4 × 3</t>
+        </is>
+      </c>
+      <c r="G17" s="43" t="inlineStr">
+        <is>
+          <t>32×32</t>
+        </is>
+      </c>
+      <c r="H17" s="43" t="inlineStr">
+        <is>
+          <t>Wide landscape image, 1536×1024</t>
+        </is>
+      </c>
+      <c r="I17" s="43" t="inlineStr">
+        <is>
+          <t>Typing = hands forward at keyboard height, arms move between A and B.</t>
+        </is>
+      </c>
+      <c r="J17" s="43" t="inlineStr">
+        <is>
+          <t>Art style: retro 8-bit pixel art, like a Japanese console game from around 1990, set in a 1990s Japanese office. Chunky square pixels with hard edges: no anti-aliasing, no blur, no soft shading, no gradients, no painterly or paper texture. Every character and object has a 1-pixel dark ink outline. Flat colours from one small palette only: ink black, night indigo, slate blue, paper cream, warm grey, vermilion red, deep red, gold, ochre, wood brown, celadon green, moss green, sakura pink, peach. Subtle Japanese touches where they fit (seigaiha wave patterns, shoji paper screens, paper lanterns, hanko stamps, maneki-neko, daruma, bonsai). Satirical anthropomorphic animals. Clean, readable game asset. No text, letters, numbers, watermark, signature or frame.
+Camera: classic Japanese top-down RPG view (three-quarter view from above and in front): you see the top and the front of things; characters show their face when they face down.
+Subject: a calico cat office worker in a cream blouse with a hair bun, SITTING on a dark navy rolling office chair (the chair is part of the picture and identical in every cell). Draw ONLY the person and the chair: NO desk, NO computer.
+Layout: a sprite sheet on a solid flat magenta background (#FF00FF, one single pure colour, no shading, no checkerboard). An evenly spaced grid of 4 columns and 3 rows of equal-sized cells with wide plain magenta gaps between the cells. Every cell shows the exact same character (same design, same colours, same size), centred in its cell, feet on the same baseline. Draw each cell at about 32×32 pixel-art resolution, so each pixel is a big visible square block. No grid lines, borders, labels or numbers. Never use magenta or purple on the subjects themselves.
+Cells, left to right, top to bottom:
+- Row 1: seen from BEHIND (facing UP, working at a desk above them): typing A | typing B | writing on a notepad | yawning
+- Row 2: facing DOWN (towards the viewer): typing A | typing B | writing on a notepad | yawning
+- Row 3: facing LEFT (side profile): typing A | typing B | writing on a notepad | yawning
+Output: PNG, Wide landscape image, 1536×1024.</t>
+        </is>
+      </c>
+      <c r="K17" s="45" t="n"/>
+      <c r="L17" s="45" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+      <c r="M17" s="45" t="n"/>
+    </row>
+    <row r="18" ht="230" customHeight="1" s="35">
+      <c r="A18" s="43" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="43" t="inlineStr">
+        <is>
+          <t>Now</t>
+        </is>
+      </c>
+      <c r="C18" s="43" t="inlineStr">
+        <is>
+          <t>Office decor v2</t>
+        </is>
+      </c>
+      <c r="D18" s="44" t="inlineStr">
+        <is>
+          <t>npc_walker_coffee.png</t>
+        </is>
+      </c>
+      <c r="E18" s="43" t="inlineStr">
+        <is>
+          <t>Office — background colleague, walking (cannot be talked to)</t>
+        </is>
+      </c>
+      <c r="F18" s="43" t="inlineStr">
+        <is>
+          <t>3 × 3</t>
+        </is>
+      </c>
+      <c r="G18" s="43" t="inlineStr">
+        <is>
+          <t>32×32</t>
+        </is>
+      </c>
+      <c r="H18" s="43" t="inlineStr">
+        <is>
+          <t>Square image, 1024×1024</t>
+        </is>
+      </c>
+      <c r="I18" s="43" t="inlineStr"/>
+      <c r="J18" s="43" t="inlineStr">
+        <is>
+          <t>Art style: retro 8-bit pixel art, like a Japanese console game from around 1990, set in a 1990s Japanese office. Chunky square pixels with hard edges: no anti-aliasing, no blur, no soft shading, no gradients, no painterly or paper texture. Every character and object has a 1-pixel dark ink outline. Flat colours from one small palette only: ink black, night indigo, slate blue, paper cream, warm grey, vermilion red, deep red, gold, ochre, wood brown, celadon green, moss green, sakura pink, peach. Subtle Japanese touches where they fit (seigaiha wave patterns, shoji paper screens, paper lanterns, hanko stamps, maneki-neko, daruma, bonsai). Satirical anthropomorphic animals. Clean, readable game asset. No text, letters, numbers, watermark, signature or frame.
+Camera: classic Japanese top-down RPG view (three-quarter view from above and in front): you see the top and the front of things; characters show their face when they face down.
+Subject: a hurried weasel office worker in a grey suit, carrying a paper cup of coffee in one hand.
+Layout: a sprite sheet on a solid flat magenta background (#FF00FF, one single pure colour, no shading, no checkerboard). An evenly spaced grid of 3 columns and 3 rows of equal-sized cells with wide plain magenta gaps between the cells. Every cell shows the exact same character (same design, same colours, same size), centred in its cell, feet on the same baseline. Draw each cell at about 32×32 pixel-art resolution, so each pixel is a big visible square block. No grid lines, borders, labels or numbers. Never use magenta or purple on the subjects themselves.
+Cells, left to right, top to bottom:
+- Row 1: facing DOWN (towards the viewer): left foot forward | standing still | right foot forward
+- Row 2: facing LEFT (side profile): left foot forward | standing still | right foot forward
+- Row 3: facing UP (back to the viewer): left foot forward | standing still | right foot forward
+Output: PNG, Square image, 1024×1024.</t>
+        </is>
+      </c>
+      <c r="K18" s="45" t="n"/>
+      <c r="L18" s="45" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+      <c r="M18" s="45" t="n"/>
+    </row>
+    <row r="19" ht="230" customHeight="1" s="35">
+      <c r="A19" s="43" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="43" t="inlineStr">
+        <is>
+          <t>Now</t>
+        </is>
+      </c>
+      <c r="C19" s="43" t="inlineStr">
+        <is>
+          <t>Office decor v2</t>
+        </is>
+      </c>
+      <c r="D19" s="44" t="inlineStr">
+        <is>
+          <t>npc_walker_papers.png</t>
+        </is>
+      </c>
+      <c r="E19" s="43" t="inlineStr">
+        <is>
+          <t>Office — background colleague, walking (cannot be talked to)</t>
+        </is>
+      </c>
+      <c r="F19" s="43" t="inlineStr">
+        <is>
+          <t>3 × 3</t>
+        </is>
+      </c>
+      <c r="G19" s="43" t="inlineStr">
+        <is>
+          <t>32×32</t>
+        </is>
+      </c>
+      <c r="H19" s="43" t="inlineStr">
+        <is>
+          <t>Square image, 1024×1024</t>
+        </is>
+      </c>
+      <c r="I19" s="43" t="inlineStr"/>
+      <c r="J19" s="43" t="inlineStr">
+        <is>
+          <t>Art style: retro 8-bit pixel art, like a Japanese console game from around 1990, set in a 1990s Japanese office. Chunky square pixels with hard edges: no anti-aliasing, no blur, no soft shading, no gradients, no painterly or paper texture. Every character and object has a 1-pixel dark ink outline. Flat colours from one small palette only: ink black, night indigo, slate blue, paper cream, warm grey, vermilion red, deep red, gold, ochre, wood brown, celadon green, moss green, sakura pink, peach. Subtle Japanese touches where they fit (seigaiha wave patterns, shoji paper screens, paper lanterns, hanko stamps, maneki-neko, daruma, bonsai). Satirical anthropomorphic animals. Clean, readable game asset. No text, letters, numbers, watermark, signature or frame.
+Camera: classic Japanese top-down RPG view (three-quarter view from above and in front): you see the top and the front of things; characters show their face when they face down.
+Subject: a slow old tortoise office worker in a brown vest, carrying a tall stack of papers in both arms.
+Layout: a sprite sheet on a solid flat magenta background (#FF00FF, one single pure colour, no shading, no checkerboard). An evenly spaced grid of 3 columns and 3 rows of equal-sized cells with wide plain magenta gaps between the cells. Every cell shows the exact same character (same design, same colours, same size), centred in its cell, feet on the same baseline. Draw each cell at about 32×32 pixel-art resolution, so each pixel is a big visible square block. No grid lines, borders, labels or numbers. Never use magenta or purple on the subjects themselves.
+Cells, left to right, top to bottom:
+- Row 1: facing DOWN (towards the viewer): left foot forward | standing still | right foot forward
+- Row 2: facing LEFT (side profile): left foot forward | standing still | right foot forward
+- Row 3: facing UP (back to the viewer): left foot forward | standing still | right foot forward
+Output: PNG, Square image, 1024×1024.</t>
+        </is>
+      </c>
+      <c r="K19" s="45" t="n"/>
+      <c r="L19" s="45" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+      <c r="M19" s="45" t="n"/>
+    </row>
+    <row r="20" ht="230" customHeight="1" s="35">
+      <c r="A20" s="43" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="43" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C5" s="43" t="inlineStr">
+      <c r="C20" s="43" t="inlineStr">
         <is>
           <t>Player</t>
         </is>
       </c>
-      <c r="D5" s="44" t="inlineStr">
+      <c r="D20" s="44" t="inlineStr">
         <is>
           <t>player_ok.png</t>
         </is>
       </c>
-      <c r="E5" s="43" t="inlineStr"/>
-      <c r="F5" s="43" t="inlineStr">
+      <c r="E20" s="43" t="inlineStr"/>
+      <c r="F20" s="43" t="inlineStr">
         <is>
           <t>3 × 3</t>
         </is>
       </c>
-      <c r="G5" s="43" t="inlineStr">
+      <c r="G20" s="43" t="inlineStr">
         <is>
           <t>32×32</t>
         </is>
       </c>
-      <c r="H5" s="43" t="inlineStr">
+      <c r="H20" s="43" t="inlineStr">
         <is>
           <t>Square image, 1024×1024</t>
         </is>
       </c>
-      <c r="I5" s="43" t="inlineStr">
+      <c r="I20" s="43" t="inlineStr">
         <is>
           <t>Generate this first. It is the reference for every other bunny image.</t>
         </is>
       </c>
-      <c r="J5" s="43" t="inlineStr">
+      <c r="J20" s="43" t="inlineStr">
         <is>
           <t>Art style: retro 8-bit pixel art, like a Japanese console game from around 1990, set in a 1990s Japanese office. Chunky square pixels with hard edges: no anti-aliasing, no blur, no soft shading, no gradients, no painterly or paper texture. Every character and object has a 1-pixel dark ink outline. Flat colours from one small palette only: ink black, night indigo, slate blue, paper cream, warm grey, vermilion red, deep red, gold, ochre, wood brown, celadon green, moss green, sakura pink, peach. Subtle Japanese touches where they fit (seigaiha wave patterns, shoji paper screens, paper lanterns, hanko stamps, maneki-neko, daruma, bonsai). Satirical anthropomorphic animals. Clean, readable game asset. No text, letters, numbers, watermark, signature or frame.
 Camera: classic Japanese top-down RPG view (three-quarter view from above and in front): you see the top and the front of things; characters show their face when they face down.
@@ -35254,55 +36225,55 @@
 Output: PNG, Square image, 1024×1024.</t>
         </is>
       </c>
-      <c r="K5" s="45" t="n"/>
-      <c r="L5" s="45" t="inlineStr">
+      <c r="K20" s="45" t="n"/>
+      <c r="L20" s="45" t="inlineStr">
         <is>
           <t>In game</t>
         </is>
       </c>
-      <c r="M5" s="45" t="n"/>
-    </row>
-    <row r="6" ht="230" customHeight="1" s="35">
-      <c r="A6" s="43" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="43" t="inlineStr">
+      <c r="M20" s="45" t="n"/>
+    </row>
+    <row r="21" ht="230" customHeight="1" s="35">
+      <c r="A21" s="43" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="43" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C6" s="43" t="inlineStr">
+      <c r="C21" s="43" t="inlineStr">
         <is>
           <t>Player</t>
         </is>
       </c>
-      <c r="D6" s="44" t="inlineStr">
+      <c r="D21" s="44" t="inlineStr">
         <is>
           <t>player_tired.png</t>
         </is>
       </c>
-      <c r="E6" s="43" t="inlineStr"/>
-      <c r="F6" s="43" t="inlineStr">
+      <c r="E21" s="43" t="inlineStr"/>
+      <c r="F21" s="43" t="inlineStr">
         <is>
           <t>3 × 3</t>
         </is>
       </c>
-      <c r="G6" s="43" t="inlineStr">
+      <c r="G21" s="43" t="inlineStr">
         <is>
           <t>32×32</t>
         </is>
       </c>
-      <c r="H6" s="43" t="inlineStr">
+      <c r="H21" s="43" t="inlineStr">
         <is>
           <t>Square image, 1024×1024</t>
         </is>
       </c>
-      <c r="I6" s="43" t="inlineStr">
+      <c r="I21" s="43" t="inlineStr">
         <is>
           <t>Attach player_ok.png and add: "Keep the character identical to the attached sprite sheet, only change the posture."</t>
         </is>
       </c>
-      <c r="J6" s="43" t="inlineStr">
+      <c r="J21" s="43" t="inlineStr">
         <is>
           <t>Art style: retro 8-bit pixel art, like a Japanese console game from around 1990, set in a 1990s Japanese office. Chunky square pixels with hard edges: no anti-aliasing, no blur, no soft shading, no gradients, no painterly or paper texture. Every character and object has a 1-pixel dark ink outline. Flat colours from one small palette only: ink black, night indigo, slate blue, paper cream, warm grey, vermilion red, deep red, gold, ochre, wood brown, celadon green, moss green, sakura pink, peach. Subtle Japanese touches where they fit (seigaiha wave patterns, shoji paper screens, paper lanterns, hanko stamps, maneki-neko, daruma, bonsai). Satirical anthropomorphic animals. Clean, readable game asset. No text, letters, numbers, watermark, signature or frame.
 Camera: classic Japanese top-down RPG view (three-quarter view from above and in front): you see the top and the front of things; characters show their face when they face down.
@@ -35315,55 +36286,55 @@
 Output: PNG, Square image, 1024×1024.</t>
         </is>
       </c>
-      <c r="K6" s="45" t="n"/>
-      <c r="L6" s="45" t="inlineStr">
+      <c r="K21" s="45" t="n"/>
+      <c r="L21" s="45" t="inlineStr">
         <is>
           <t>In game</t>
         </is>
       </c>
-      <c r="M6" s="45" t="n"/>
-    </row>
-    <row r="7" ht="230" customHeight="1" s="35">
-      <c r="A7" s="43" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="43" t="inlineStr">
+      <c r="M21" s="45" t="n"/>
+    </row>
+    <row r="22" ht="230" customHeight="1" s="35">
+      <c r="A22" s="43" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="43" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C7" s="43" t="inlineStr">
+      <c r="C22" s="43" t="inlineStr">
         <is>
           <t>Player</t>
         </is>
       </c>
-      <c r="D7" s="44" t="inlineStr">
+      <c r="D22" s="44" t="inlineStr">
         <is>
           <t>player_burnt.png</t>
         </is>
       </c>
-      <c r="E7" s="43" t="inlineStr"/>
-      <c r="F7" s="43" t="inlineStr">
+      <c r="E22" s="43" t="inlineStr"/>
+      <c r="F22" s="43" t="inlineStr">
         <is>
           <t>3 × 3</t>
         </is>
       </c>
-      <c r="G7" s="43" t="inlineStr">
+      <c r="G22" s="43" t="inlineStr">
         <is>
           <t>32×32</t>
         </is>
       </c>
-      <c r="H7" s="43" t="inlineStr">
+      <c r="H22" s="43" t="inlineStr">
         <is>
           <t>Square image, 1024×1024</t>
         </is>
       </c>
-      <c r="I7" s="43" t="inlineStr">
+      <c r="I22" s="43" t="inlineStr">
         <is>
           <t>Attach player_ok.png and add: "Keep the character identical to the attached sprite sheet, only change the posture."</t>
         </is>
       </c>
-      <c r="J7" s="43" t="inlineStr">
+      <c r="J22" s="43" t="inlineStr">
         <is>
           <t>Art style: retro 8-bit pixel art, like a Japanese console game from around 1990, set in a 1990s Japanese office. Chunky square pixels with hard edges: no anti-aliasing, no blur, no soft shading, no gradients, no painterly or paper texture. Every character and object has a 1-pixel dark ink outline. Flat colours from one small palette only: ink black, night indigo, slate blue, paper cream, warm grey, vermilion red, deep red, gold, ochre, wood brown, celadon green, moss green, sakura pink, peach. Subtle Japanese touches where they fit (seigaiha wave patterns, shoji paper screens, paper lanterns, hanko stamps, maneki-neko, daruma, bonsai). Satirical anthropomorphic animals. Clean, readable game asset. No text, letters, numbers, watermark, signature or frame.
 Camera: classic Japanese top-down RPG view (three-quarter view from above and in front): you see the top and the front of things; characters show their face when they face down.
@@ -35376,55 +36347,55 @@
 Output: PNG, Square image, 1024×1024.</t>
         </is>
       </c>
-      <c r="K7" s="45" t="n"/>
-      <c r="L7" s="45" t="inlineStr">
+      <c r="K22" s="45" t="n"/>
+      <c r="L22" s="45" t="inlineStr">
         <is>
           <t>In game</t>
         </is>
       </c>
-      <c r="M7" s="45" t="n"/>
-    </row>
-    <row r="8" ht="230" customHeight="1" s="35">
-      <c r="A8" s="43" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="43" t="inlineStr">
+      <c r="M22" s="45" t="n"/>
+    </row>
+    <row r="23" ht="230" customHeight="1" s="35">
+      <c r="A23" s="43" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="43" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C8" s="43" t="inlineStr">
+      <c r="C23" s="43" t="inlineStr">
         <is>
           <t>Player</t>
         </is>
       </c>
-      <c r="D8" s="44" t="inlineStr">
+      <c r="D23" s="44" t="inlineStr">
         <is>
           <t>player_actions.png</t>
         </is>
       </c>
-      <c r="E8" s="43" t="inlineStr"/>
-      <c r="F8" s="43" t="inlineStr">
+      <c r="E23" s="43" t="inlineStr"/>
+      <c r="F23" s="43" t="inlineStr">
         <is>
           <t>3 × 3</t>
         </is>
       </c>
-      <c r="G8" s="43" t="inlineStr">
+      <c r="G23" s="43" t="inlineStr">
         <is>
           <t>32×32</t>
         </is>
       </c>
-      <c r="H8" s="43" t="inlineStr">
+      <c r="H23" s="43" t="inlineStr">
         <is>
           <t>Square image, 1024×1024</t>
         </is>
       </c>
-      <c r="I8" s="43" t="inlineStr">
+      <c r="I23" s="43" t="inlineStr">
         <is>
           <t>Attach player_ok.png and add: "Keep the character identical to the attached sprite sheet."</t>
         </is>
       </c>
-      <c r="J8" s="43" t="inlineStr">
+      <c r="J23" s="43" t="inlineStr">
         <is>
           <t>Art style: retro 8-bit pixel art, like a Japanese console game from around 1990, set in a 1990s Japanese office. Chunky square pixels with hard edges: no anti-aliasing, no blur, no soft shading, no gradients, no painterly or paper texture. Every character and object has a 1-pixel dark ink outline. Flat colours from one small palette only: ink black, night indigo, slate blue, paper cream, warm grey, vermilion red, deep red, gold, ochre, wood brown, celadon green, moss green, sakura pink, peach. Subtle Japanese touches where they fit (seigaiha wave patterns, shoji paper screens, paper lanterns, hanko stamps, maneki-neko, daruma, bonsai). Satirical anthropomorphic animals. Clean, readable game asset. No text, letters, numbers, watermark, signature or frame.
 Camera: classic Japanese top-down RPG view (three-quarter view from above and in front): you see the top and the front of things; characters show their face when they face down.
@@ -35437,55 +36408,55 @@
 Output: PNG, Square image, 1024×1024.</t>
         </is>
       </c>
-      <c r="K8" s="45" t="n"/>
-      <c r="L8" s="45" t="inlineStr">
+      <c r="K23" s="45" t="n"/>
+      <c r="L23" s="45" t="inlineStr">
         <is>
           <t>In game</t>
         </is>
       </c>
-      <c r="M8" s="45" t="n"/>
-    </row>
-    <row r="9" ht="230" customHeight="1" s="35">
-      <c r="A9" s="43" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="43" t="inlineStr">
+      <c r="M23" s="45" t="n"/>
+    </row>
+    <row r="24" ht="230" customHeight="1" s="35">
+      <c r="A24" s="43" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="43" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C9" s="43" t="inlineStr">
+      <c r="C24" s="43" t="inlineStr">
         <is>
           <t>Player</t>
         </is>
       </c>
-      <c r="D9" s="44" t="inlineStr">
+      <c r="D24" s="44" t="inlineStr">
         <is>
           <t>player_side.png</t>
         </is>
       </c>
-      <c r="E9" s="43" t="inlineStr"/>
-      <c r="F9" s="43" t="inlineStr">
+      <c r="E24" s="43" t="inlineStr"/>
+      <c r="F24" s="43" t="inlineStr">
         <is>
           <t>4 × 2</t>
         </is>
       </c>
-      <c r="G9" s="43" t="inlineStr">
+      <c r="G24" s="43" t="inlineStr">
         <is>
           <t>32×48</t>
         </is>
       </c>
-      <c r="H9" s="43" t="inlineStr">
+      <c r="H24" s="43" t="inlineStr">
         <is>
           <t>Wide landscape image, 1536×1024</t>
         </is>
       </c>
-      <c r="I9" s="43" t="inlineStr">
+      <c r="I24" s="43" t="inlineStr">
         <is>
           <t>Attach player_ok.png and add: "Keep the character identical to the attached sprite sheet."</t>
         </is>
       </c>
-      <c r="J9" s="43" t="inlineStr">
+      <c r="J24" s="43" t="inlineStr">
         <is>
           <t>Art style: retro 8-bit pixel art, like a Japanese console game from around 1990, set in a 1990s Japanese office. Chunky square pixels with hard edges: no anti-aliasing, no blur, no soft shading, no gradients, no painterly or paper texture. Every character and object has a 1-pixel dark ink outline. Flat colours from one small palette only: ink black, night indigo, slate blue, paper cream, warm grey, vermilion red, deep red, gold, ochre, wood brown, celadon green, moss green, sakura pink, peach. Subtle Japanese touches where they fit (seigaiha wave patterns, shoji paper screens, paper lanterns, hanko stamps, maneki-neko, daruma, bonsai). Satirical anthropomorphic animals. Clean, readable game asset. No text, letters, numbers, watermark, signature or frame.
 Camera: plain side view, like a 2D side-scrolling game; every figure stands on the bottom edge of its cell.
@@ -35497,55 +36468,55 @@
 Output: PNG, Wide landscape image, 1536×1024.</t>
         </is>
       </c>
-      <c r="K9" s="45" t="n"/>
-      <c r="L9" s="45" t="inlineStr">
+      <c r="K24" s="45" t="n"/>
+      <c r="L24" s="45" t="inlineStr">
         <is>
           <t>In game</t>
         </is>
       </c>
-      <c r="M9" s="45" t="n"/>
-    </row>
-    <row r="10" ht="230" customHeight="1" s="35">
-      <c r="A10" s="43" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="43" t="inlineStr">
+      <c r="M24" s="45" t="n"/>
+    </row>
+    <row r="25" ht="230" customHeight="1" s="35">
+      <c r="A25" s="43" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="43" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C10" s="43" t="inlineStr">
+      <c r="C25" s="43" t="inlineStr">
         <is>
           <t>Player</t>
         </is>
       </c>
-      <c r="D10" s="44" t="inlineStr">
+      <c r="D25" s="44" t="inlineStr">
         <is>
           <t>player_portrait.png</t>
         </is>
       </c>
-      <c r="E10" s="43" t="inlineStr"/>
-      <c r="F10" s="43" t="inlineStr">
+      <c r="E25" s="43" t="inlineStr"/>
+      <c r="F25" s="43" t="inlineStr">
         <is>
           <t>2 × 1</t>
         </is>
       </c>
-      <c r="G10" s="43" t="inlineStr">
+      <c r="G25" s="43" t="inlineStr">
         <is>
           <t>64×64</t>
         </is>
       </c>
-      <c r="H10" s="43" t="inlineStr">
+      <c r="H25" s="43" t="inlineStr">
         <is>
           <t>Wide landscape image, 1536×1024</t>
         </is>
       </c>
-      <c r="I10" s="43" t="inlineStr">
+      <c r="I25" s="43" t="inlineStr">
         <is>
           <t>Attach player_ok.png and add: "Keep the character identical to the attached sprite sheet."</t>
         </is>
       </c>
-      <c r="J10" s="43" t="inlineStr">
+      <c r="J25" s="43" t="inlineStr">
         <is>
           <t>Art style: retro 8-bit pixel art, like a Japanese console game from around 1990, set in a 1990s Japanese office. Chunky square pixels with hard edges: no anti-aliasing, no blur, no soft shading, no gradients, no painterly or paper texture. Every character and object has a 1-pixel dark ink outline. Flat colours from one small palette only: ink black, night indigo, slate blue, paper cream, warm grey, vermilion red, deep red, gold, ochre, wood brown, celadon green, moss green, sakura pink, peach. Subtle Japanese touches where they fit (seigaiha wave patterns, shoji paper screens, paper lanterns, hanko stamps, maneki-neko, daruma, bonsai). Satirical anthropomorphic animals. Clean, readable game asset. No text, letters, numbers, watermark, signature or frame.
 Camera: chest-up character portrait, three-quarter view, like a dialogue portrait in a Japanese RPG.
@@ -35556,59 +36527,59 @@
 Output: PNG, Wide landscape image, 1536×1024.</t>
         </is>
       </c>
-      <c r="K10" s="45" t="n"/>
-      <c r="L10" s="45" t="inlineStr">
+      <c r="K25" s="45" t="n"/>
+      <c r="L25" s="45" t="inlineStr">
         <is>
           <t>In game</t>
         </is>
       </c>
-      <c r="M10" s="45" t="n"/>
-    </row>
-    <row r="11" ht="230" customHeight="1" s="35">
-      <c r="A11" s="43" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="43" t="inlineStr">
+      <c r="M25" s="45" t="n"/>
+    </row>
+    <row r="26" ht="230" customHeight="1" s="35">
+      <c r="A26" s="43" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="43" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C11" s="43" t="inlineStr">
+      <c r="C26" s="43" t="inlineStr">
         <is>
           <t>Flat</t>
         </is>
       </c>
-      <c r="D11" s="44" t="inlineStr">
+      <c r="D26" s="44" t="inlineStr">
         <is>
           <t>player_wake.png</t>
         </is>
       </c>
-      <c r="E11" s="43" t="inlineStr">
+      <c r="E26" s="43" t="inlineStr">
         <is>
           <t>Intro — wake-up</t>
         </is>
       </c>
-      <c r="F11" s="43" t="inlineStr">
+      <c r="F26" s="43" t="inlineStr">
         <is>
           <t>4 × 2</t>
         </is>
       </c>
-      <c r="G11" s="43" t="inlineStr">
+      <c r="G26" s="43" t="inlineStr">
         <is>
           <t>112×72</t>
         </is>
       </c>
-      <c r="H11" s="43" t="inlineStr">
+      <c r="H26" s="43" t="inlineStr">
         <is>
           <t>Wide landscape image, 1536×1024</t>
         </is>
       </c>
-      <c r="I11" s="43" t="inlineStr">
+      <c r="I26" s="43" t="inlineStr">
         <is>
           <t>Attach player_ok.png and add: "Keep the character identical to the attached sprite sheet." The futon must stay in the same place in every cell.</t>
         </is>
       </c>
-      <c r="J11" s="43" t="inlineStr">
+      <c r="J26" s="43" t="inlineStr">
         <is>
           <t>Art style: retro 8-bit pixel art, like a Japanese console game from around 1990, set in a 1990s Japanese office. Chunky square pixels with hard edges: no anti-aliasing, no blur, no soft shading, no gradients, no painterly or paper texture. Every character and object has a 1-pixel dark ink outline. Flat colours from one small palette only: ink black, night indigo, slate blue, paper cream, warm grey, vermilion red, deep red, gold, ochre, wood brown, celadon green, moss green, sakura pink, peach. Subtle Japanese touches where they fit (seigaiha wave patterns, shoji paper screens, paper lanterns, hanko stamps, maneki-neko, daruma, bonsai). Satirical anthropomorphic animals. Clean, readable game asset. No text, letters, numbers, watermark, signature or frame.
 Camera: plain side view, like a 2D side-scrolling game; every figure stands on the bottom edge of its cell.
@@ -35620,55 +36591,55 @@
 Output: PNG, Wide landscape image, 1536×1024.</t>
         </is>
       </c>
-      <c r="K11" s="45" t="n"/>
-      <c r="L11" s="45" t="inlineStr">
+      <c r="K26" s="45" t="n"/>
+      <c r="L26" s="45" t="inlineStr">
         <is>
           <t>In game</t>
         </is>
       </c>
-      <c r="M11" s="45" t="n"/>
-    </row>
-    <row r="12" ht="230" customHeight="1" s="35">
-      <c r="A12" s="43" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="43" t="inlineStr">
+      <c r="M26" s="45" t="n"/>
+    </row>
+    <row r="27" ht="230" customHeight="1" s="35">
+      <c r="A27" s="43" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="43" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C12" s="43" t="inlineStr">
+      <c r="C27" s="43" t="inlineStr">
         <is>
           <t>Flat</t>
         </is>
       </c>
-      <c r="D12" s="44" t="inlineStr">
+      <c r="D27" s="44" t="inlineStr">
         <is>
           <t>flat_props.png</t>
         </is>
       </c>
-      <c r="E12" s="43" t="inlineStr">
+      <c r="E27" s="43" t="inlineStr">
         <is>
           <t>Intro — interactive props (mirror, plant, cat)</t>
         </is>
       </c>
-      <c r="F12" s="43" t="inlineStr">
+      <c r="F27" s="43" t="inlineStr">
         <is>
           <t>4 × 2</t>
         </is>
       </c>
-      <c r="G12" s="43" t="inlineStr">
+      <c r="G27" s="43" t="inlineStr">
         <is>
           <t>48×72</t>
         </is>
       </c>
-      <c r="H12" s="43" t="inlineStr">
+      <c r="H27" s="43" t="inlineStr">
         <is>
           <t>Wide landscape image, 1536×1024</t>
         </is>
       </c>
-      <c r="I12" s="43" t="inlineStr"/>
-      <c r="J12" s="43" t="inlineStr">
+      <c r="I27" s="43" t="inlineStr"/>
+      <c r="J27" s="43" t="inlineStr">
         <is>
           <t>Art style: retro 8-bit pixel art, like a Japanese console game from around 1990, set in a 1990s Japanese office. Chunky square pixels with hard edges: no anti-aliasing, no blur, no soft shading, no gradients, no painterly or paper texture. Every character and object has a 1-pixel dark ink outline. Flat colours from one small palette only: ink black, night indigo, slate blue, paper cream, warm grey, vermilion red, deep red, gold, ochre, wood brown, celadon green, moss green, sakura pink, peach. Subtle Japanese touches where they fit (seigaiha wave patterns, shoji paper screens, paper lanterns, hanko stamps, maneki-neko, daruma, bonsai). Satirical anthropomorphic animals. Clean, readable game asset. No text, letters, numbers, watermark, signature or frame.
 Camera: plain side view, like a 2D side-scrolling game; every figure stands on the bottom edge of its cell.
@@ -35680,55 +36651,55 @@
 Output: PNG, Wide landscape image, 1536×1024.</t>
         </is>
       </c>
-      <c r="K12" s="45" t="n"/>
-      <c r="L12" s="45" t="inlineStr">
+      <c r="K27" s="45" t="n"/>
+      <c r="L27" s="45" t="inlineStr">
         <is>
           <t>In game</t>
         </is>
       </c>
-      <c r="M12" s="45" t="n"/>
-    </row>
-    <row r="13" ht="230" customHeight="1" s="35">
-      <c r="A13" s="43" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="43" t="inlineStr">
+      <c r="M27" s="45" t="n"/>
+    </row>
+    <row r="28" ht="230" customHeight="1" s="35">
+      <c r="A28" s="43" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="43" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C13" s="43" t="inlineStr">
+      <c r="C28" s="43" t="inlineStr">
         <is>
           <t>Bosses</t>
         </is>
       </c>
-      <c r="D13" s="44" t="inlineStr">
+      <c r="D28" s="44" t="inlineStr">
         <is>
           <t>boss_ceo.png</t>
         </is>
       </c>
-      <c r="E13" s="43" t="inlineStr">
+      <c r="E28" s="43" t="inlineStr">
         <is>
           <t>Final Boss — CEO "We're a family" (Oni)</t>
         </is>
       </c>
-      <c r="F13" s="43" t="inlineStr">
+      <c r="F28" s="43" t="inlineStr">
         <is>
           <t>4 × 2</t>
         </is>
       </c>
-      <c r="G13" s="43" t="inlineStr">
+      <c r="G28" s="43" t="inlineStr">
         <is>
           <t>64×64</t>
         </is>
       </c>
-      <c r="H13" s="43" t="inlineStr">
+      <c r="H28" s="43" t="inlineStr">
         <is>
           <t>Wide landscape image, 1536×1024</t>
         </is>
       </c>
-      <c r="I13" s="43" t="inlineStr"/>
-      <c r="J13" s="43" t="inlineStr">
+      <c r="I28" s="43" t="inlineStr"/>
+      <c r="J28" s="43" t="inlineStr">
         <is>
           <t>Art style: retro 8-bit pixel art, like a Japanese console game from around 1990, set in a 1990s Japanese office. Chunky square pixels with hard edges: no anti-aliasing, no blur, no soft shading, no gradients, no painterly or paper texture. Every character and object has a 1-pixel dark ink outline. Flat colours from one small palette only: ink black, night indigo, slate blue, paper cream, warm grey, vermilion red, deep red, gold, ochre, wood brown, celadon green, moss green, sakura pink, peach. Subtle Japanese touches where they fit (seigaiha wave patterns, shoji paper screens, paper lanterns, hanko stamps, maneki-neko, daruma, bonsai). Satirical anthropomorphic animals. Clean, readable game asset. No text, letters, numbers, watermark, signature or frame.
 Camera: classic Japanese top-down RPG view (three-quarter view from above and in front): you see the top and the front of things; characters show their face when they face down.
@@ -35740,55 +36711,55 @@
 Output: PNG, Wide landscape image, 1536×1024.</t>
         </is>
       </c>
-      <c r="K13" s="45" t="n"/>
-      <c r="L13" s="45" t="inlineStr">
+      <c r="K28" s="45" t="n"/>
+      <c r="L28" s="45" t="inlineStr">
         <is>
           <t>In game</t>
         </is>
       </c>
-      <c r="M13" s="45" t="n"/>
-    </row>
-    <row r="14" ht="230" customHeight="1" s="35">
-      <c r="A14" s="43" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="43" t="inlineStr">
+      <c r="M28" s="45" t="n"/>
+    </row>
+    <row r="29" ht="230" customHeight="1" s="35">
+      <c r="A29" s="43" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="43" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C14" s="43" t="inlineStr">
+      <c r="C29" s="43" t="inlineStr">
         <is>
           <t>Minibosses</t>
         </is>
       </c>
-      <c r="D14" s="44" t="inlineStr">
+      <c r="D29" s="44" t="inlineStr">
         <is>
           <t>miniboss_client.png</t>
         </is>
       </c>
-      <c r="E14" s="43" t="inlineStr">
+      <c r="E29" s="43" t="inlineStr">
         <is>
           <t>Mini boss — Client</t>
         </is>
       </c>
-      <c r="F14" s="43" t="inlineStr">
+      <c r="F29" s="43" t="inlineStr">
         <is>
           <t>4 × 2</t>
         </is>
       </c>
-      <c r="G14" s="43" t="inlineStr">
+      <c r="G29" s="43" t="inlineStr">
         <is>
           <t>48×48</t>
         </is>
       </c>
-      <c r="H14" s="43" t="inlineStr">
+      <c r="H29" s="43" t="inlineStr">
         <is>
           <t>Wide landscape image, 1536×1024</t>
         </is>
       </c>
-      <c r="I14" s="43" t="inlineStr"/>
-      <c r="J14" s="43" t="inlineStr">
+      <c r="I29" s="43" t="inlineStr"/>
+      <c r="J29" s="43" t="inlineStr">
         <is>
           <t>Art style: retro 8-bit pixel art, like a Japanese console game from around 1990, set in a 1990s Japanese office. Chunky square pixels with hard edges: no anti-aliasing, no blur, no soft shading, no gradients, no painterly or paper texture. Every character and object has a 1-pixel dark ink outline. Flat colours from one small palette only: ink black, night indigo, slate blue, paper cream, warm grey, vermilion red, deep red, gold, ochre, wood brown, celadon green, moss green, sakura pink, peach. Subtle Japanese touches where they fit (seigaiha wave patterns, shoji paper screens, paper lanterns, hanko stamps, maneki-neko, daruma, bonsai). Satirical anthropomorphic animals. Clean, readable game asset. No text, letters, numbers, watermark, signature or frame.
 Camera: classic Japanese top-down RPG view (three-quarter view from above and in front): you see the top and the front of things; characters show their face when they face down.
@@ -35800,55 +36771,55 @@
 Output: PNG, Wide landscape image, 1536×1024.</t>
         </is>
       </c>
-      <c r="K14" s="45" t="n"/>
-      <c r="L14" s="45" t="inlineStr">
+      <c r="K29" s="45" t="n"/>
+      <c r="L29" s="45" t="inlineStr">
         <is>
           <t>In game</t>
         </is>
       </c>
-      <c r="M14" s="45" t="n"/>
-    </row>
-    <row r="15" ht="230" customHeight="1" s="35">
-      <c r="A15" s="43" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="43" t="inlineStr">
+      <c r="M29" s="45" t="n"/>
+    </row>
+    <row r="30" ht="230" customHeight="1" s="35">
+      <c r="A30" s="43" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="43" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C15" s="43" t="inlineStr">
+      <c r="C30" s="43" t="inlineStr">
         <is>
           <t>Minibosses</t>
         </is>
       </c>
-      <c r="D15" s="44" t="inlineStr">
+      <c r="D30" s="44" t="inlineStr">
         <is>
           <t>miniboss_printer.png</t>
         </is>
       </c>
-      <c r="E15" s="43" t="inlineStr">
+      <c r="E30" s="43" t="inlineStr">
         <is>
           <t>Mini boss — Printer</t>
         </is>
       </c>
-      <c r="F15" s="43" t="inlineStr">
+      <c r="F30" s="43" t="inlineStr">
         <is>
           <t>4 × 2</t>
         </is>
       </c>
-      <c r="G15" s="43" t="inlineStr">
+      <c r="G30" s="43" t="inlineStr">
         <is>
           <t>48×48</t>
         </is>
       </c>
-      <c r="H15" s="43" t="inlineStr">
+      <c r="H30" s="43" t="inlineStr">
         <is>
           <t>Wide landscape image, 1536×1024</t>
         </is>
       </c>
-      <c r="I15" s="43" t="inlineStr"/>
-      <c r="J15" s="43" t="inlineStr">
+      <c r="I30" s="43" t="inlineStr"/>
+      <c r="J30" s="43" t="inlineStr">
         <is>
           <t>Art style: retro 8-bit pixel art, like a Japanese console game from around 1990, set in a 1990s Japanese office. Chunky square pixels with hard edges: no anti-aliasing, no blur, no soft shading, no gradients, no painterly or paper texture. Every character and object has a 1-pixel dark ink outline. Flat colours from one small palette only: ink black, night indigo, slate blue, paper cream, warm grey, vermilion red, deep red, gold, ochre, wood brown, celadon green, moss green, sakura pink, peach. Subtle Japanese touches where they fit (seigaiha wave patterns, shoji paper screens, paper lanterns, hanko stamps, maneki-neko, daruma, bonsai). Satirical anthropomorphic animals. Clean, readable game asset. No text, letters, numbers, watermark, signature or frame.
 Camera: classic Japanese top-down RPG view (three-quarter view from above and in front): you see the top and the front of things; characters show their face when they face down.
@@ -35860,55 +36831,55 @@
 Output: PNG, Wide landscape image, 1536×1024.</t>
         </is>
       </c>
-      <c r="K15" s="45" t="n"/>
-      <c r="L15" s="45" t="inlineStr">
+      <c r="K30" s="45" t="n"/>
+      <c r="L30" s="45" t="inlineStr">
         <is>
           <t>In game</t>
         </is>
       </c>
-      <c r="M15" s="45" t="n"/>
-    </row>
-    <row r="16" ht="230" customHeight="1" s="35">
-      <c r="A16" s="43" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="43" t="inlineStr">
+      <c r="M30" s="45" t="n"/>
+    </row>
+    <row r="31" ht="230" customHeight="1" s="35">
+      <c r="A31" s="43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="43" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C16" s="43" t="inlineStr">
+      <c r="C31" s="43" t="inlineStr">
         <is>
           <t>Minibosses</t>
         </is>
       </c>
-      <c r="D16" s="44" t="inlineStr">
+      <c r="D31" s="44" t="inlineStr">
         <is>
           <t>miniboss_coffee.png</t>
         </is>
       </c>
-      <c r="E16" s="43" t="inlineStr">
+      <c r="E31" s="43" t="inlineStr">
         <is>
           <t>Mini boss — Broken coffee machine</t>
         </is>
       </c>
-      <c r="F16" s="43" t="inlineStr">
+      <c r="F31" s="43" t="inlineStr">
         <is>
           <t>4 × 2</t>
         </is>
       </c>
-      <c r="G16" s="43" t="inlineStr">
+      <c r="G31" s="43" t="inlineStr">
         <is>
           <t>48×48</t>
         </is>
       </c>
-      <c r="H16" s="43" t="inlineStr">
+      <c r="H31" s="43" t="inlineStr">
         <is>
           <t>Wide landscape image, 1536×1024</t>
         </is>
       </c>
-      <c r="I16" s="43" t="inlineStr"/>
-      <c r="J16" s="43" t="inlineStr">
+      <c r="I31" s="43" t="inlineStr"/>
+      <c r="J31" s="43" t="inlineStr">
         <is>
           <t>Art style: retro 8-bit pixel art, like a Japanese console game from around 1990, set in a 1990s Japanese office. Chunky square pixels with hard edges: no anti-aliasing, no blur, no soft shading, no gradients, no painterly or paper texture. Every character and object has a 1-pixel dark ink outline. Flat colours from one small palette only: ink black, night indigo, slate blue, paper cream, warm grey, vermilion red, deep red, gold, ochre, wood brown, celadon green, moss green, sakura pink, peach. Subtle Japanese touches where they fit (seigaiha wave patterns, shoji paper screens, paper lanterns, hanko stamps, maneki-neko, daruma, bonsai). Satirical anthropomorphic animals. Clean, readable game asset. No text, letters, numbers, watermark, signature or frame.
 Camera: classic Japanese top-down RPG view (three-quarter view from above and in front): you see the top and the front of things; characters show their face when they face down.
@@ -35920,55 +36891,55 @@
 Output: PNG, Wide landscape image, 1536×1024.</t>
         </is>
       </c>
-      <c r="K16" s="45" t="n"/>
-      <c r="L16" s="45" t="inlineStr">
+      <c r="K31" s="45" t="n"/>
+      <c r="L31" s="45" t="inlineStr">
         <is>
           <t>In game</t>
         </is>
       </c>
-      <c r="M16" s="45" t="n"/>
-    </row>
-    <row r="17" ht="230" customHeight="1" s="35">
-      <c r="A17" s="43" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="43" t="inlineStr">
+      <c r="M31" s="45" t="n"/>
+    </row>
+    <row r="32" ht="230" customHeight="1" s="35">
+      <c r="A32" s="43" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="43" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C17" s="43" t="inlineStr">
+      <c r="C32" s="43" t="inlineStr">
         <is>
           <t>Minibosses</t>
         </is>
       </c>
-      <c r="D17" s="44" t="inlineStr">
+      <c r="D32" s="44" t="inlineStr">
         <is>
           <t>miniboss_ac.png</t>
         </is>
       </c>
-      <c r="E17" s="43" t="inlineStr">
+      <c r="E32" s="43" t="inlineStr">
         <is>
           <t>Mini boss — Air conditioner</t>
         </is>
       </c>
-      <c r="F17" s="43" t="inlineStr">
+      <c r="F32" s="43" t="inlineStr">
         <is>
           <t>4 × 2</t>
         </is>
       </c>
-      <c r="G17" s="43" t="inlineStr">
+      <c r="G32" s="43" t="inlineStr">
         <is>
           <t>48×48</t>
         </is>
       </c>
-      <c r="H17" s="43" t="inlineStr">
+      <c r="H32" s="43" t="inlineStr">
         <is>
           <t>Wide landscape image, 1536×1024</t>
         </is>
       </c>
-      <c r="I17" s="43" t="inlineStr"/>
-      <c r="J17" s="43" t="inlineStr">
+      <c r="I32" s="43" t="inlineStr"/>
+      <c r="J32" s="43" t="inlineStr">
         <is>
           <t>Art style: retro 8-bit pixel art, like a Japanese console game from around 1990, set in a 1990s Japanese office. Chunky square pixels with hard edges: no anti-aliasing, no blur, no soft shading, no gradients, no painterly or paper texture. Every character and object has a 1-pixel dark ink outline. Flat colours from one small palette only: ink black, night indigo, slate blue, paper cream, warm grey, vermilion red, deep red, gold, ochre, wood brown, celadon green, moss green, sakura pink, peach. Subtle Japanese touches where they fit (seigaiha wave patterns, shoji paper screens, paper lanterns, hanko stamps, maneki-neko, daruma, bonsai). Satirical anthropomorphic animals. Clean, readable game asset. No text, letters, numbers, watermark, signature or frame.
 Camera: classic Japanese top-down RPG view (three-quarter view from above and in front): you see the top and the front of things; characters show their face when they face down.
@@ -35980,55 +36951,55 @@
 Output: PNG, Wide landscape image, 1536×1024.</t>
         </is>
       </c>
-      <c r="K17" s="45" t="n"/>
-      <c r="L17" s="45" t="inlineStr">
+      <c r="K32" s="45" t="n"/>
+      <c r="L32" s="45" t="inlineStr">
         <is>
           <t>In game</t>
         </is>
       </c>
-      <c r="M17" s="45" t="n"/>
-    </row>
-    <row r="18" ht="230" customHeight="1" s="35">
-      <c r="A18" s="43" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="43" t="inlineStr">
+      <c r="M32" s="45" t="n"/>
+    </row>
+    <row r="33" ht="230" customHeight="1" s="35">
+      <c r="A33" s="43" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="43" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C18" s="43" t="inlineStr">
+      <c r="C33" s="43" t="inlineStr">
         <is>
           <t>Minions</t>
         </is>
       </c>
-      <c r="D18" s="44" t="inlineStr">
+      <c r="D33" s="44" t="inlineStr">
         <is>
           <t>minion_email_weak.png</t>
         </is>
       </c>
-      <c r="E18" s="43" t="inlineStr">
+      <c r="E33" s="43" t="inlineStr">
         <is>
           <t>Client → email (weak)</t>
         </is>
       </c>
-      <c r="F18" s="43" t="inlineStr">
+      <c r="F33" s="43" t="inlineStr">
         <is>
           <t>4 × 1</t>
         </is>
       </c>
-      <c r="G18" s="43" t="inlineStr">
+      <c r="G33" s="43" t="inlineStr">
         <is>
           <t>24×24</t>
         </is>
       </c>
-      <c r="H18" s="43" t="inlineStr">
+      <c r="H33" s="43" t="inlineStr">
         <is>
           <t>Wide landscape image, 1536×1024</t>
         </is>
       </c>
-      <c r="I18" s="43" t="inlineStr"/>
-      <c r="J18" s="43" t="inlineStr">
+      <c r="I33" s="43" t="inlineStr"/>
+      <c r="J33" s="43" t="inlineStr">
         <is>
           <t>Art style: retro 8-bit pixel art, like a Japanese console game from around 1990, set in a 1990s Japanese office. Chunky square pixels with hard edges: no anti-aliasing, no blur, no soft shading, no gradients, no painterly or paper texture. Every character and object has a 1-pixel dark ink outline. Flat colours from one small palette only: ink black, night indigo, slate blue, paper cream, warm grey, vermilion red, deep red, gold, ochre, wood brown, celadon green, moss green, sakura pink, peach. Subtle Japanese touches where they fit (seigaiha wave patterns, shoji paper screens, paper lanterns, hanko stamps, maneki-neko, daruma, bonsai). Satirical anthropomorphic animals. Clean, readable game asset. No text, letters, numbers, watermark, signature or frame.
 Camera: classic Japanese top-down RPG view (three-quarter view from above and in front): you see the top and the front of things; characters show their face when they face down.
@@ -36039,55 +37010,55 @@
 Output: PNG, Wide landscape image, 1536×1024.</t>
         </is>
       </c>
-      <c r="K18" s="45" t="n"/>
-      <c r="L18" s="45" t="inlineStr">
+      <c r="K33" s="45" t="n"/>
+      <c r="L33" s="45" t="inlineStr">
         <is>
           <t>In game</t>
         </is>
       </c>
-      <c r="M18" s="45" t="n"/>
-    </row>
-    <row r="19" ht="230" customHeight="1" s="35">
-      <c r="A19" s="43" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="43" t="inlineStr">
+      <c r="M33" s="45" t="n"/>
+    </row>
+    <row r="34" ht="230" customHeight="1" s="35">
+      <c r="A34" s="43" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="43" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C19" s="43" t="inlineStr">
+      <c r="C34" s="43" t="inlineStr">
         <is>
           <t>Minions</t>
         </is>
       </c>
-      <c r="D19" s="44" t="inlineStr">
+      <c r="D34" s="44" t="inlineStr">
         <is>
           <t>minion_email_strong.png</t>
         </is>
       </c>
-      <c r="E19" s="43" t="inlineStr">
+      <c r="E34" s="43" t="inlineStr">
         <is>
           <t>Client → email (strong)</t>
         </is>
       </c>
-      <c r="F19" s="43" t="inlineStr">
+      <c r="F34" s="43" t="inlineStr">
         <is>
           <t>4 × 1</t>
         </is>
       </c>
-      <c r="G19" s="43" t="inlineStr">
+      <c r="G34" s="43" t="inlineStr">
         <is>
           <t>32×32</t>
         </is>
       </c>
-      <c r="H19" s="43" t="inlineStr">
+      <c r="H34" s="43" t="inlineStr">
         <is>
           <t>Wide landscape image, 1536×1024</t>
         </is>
       </c>
-      <c r="I19" s="43" t="inlineStr"/>
-      <c r="J19" s="43" t="inlineStr">
+      <c r="I34" s="43" t="inlineStr"/>
+      <c r="J34" s="43" t="inlineStr">
         <is>
           <t>Art style: retro 8-bit pixel art, like a Japanese console game from around 1990, set in a 1990s Japanese office. Chunky square pixels with hard edges: no anti-aliasing, no blur, no soft shading, no gradients, no painterly or paper texture. Every character and object has a 1-pixel dark ink outline. Flat colours from one small palette only: ink black, night indigo, slate blue, paper cream, warm grey, vermilion red, deep red, gold, ochre, wood brown, celadon green, moss green, sakura pink, peach. Subtle Japanese touches where they fit (seigaiha wave patterns, shoji paper screens, paper lanterns, hanko stamps, maneki-neko, daruma, bonsai). Satirical anthropomorphic animals. Clean, readable game asset. No text, letters, numbers, watermark, signature or frame.
 Camera: classic Japanese top-down RPG view (three-quarter view from above and in front): you see the top and the front of things; characters show their face when they face down.
@@ -36098,55 +37069,55 @@
 Output: PNG, Wide landscape image, 1536×1024.</t>
         </is>
       </c>
-      <c r="K19" s="45" t="n"/>
-      <c r="L19" s="45" t="inlineStr">
+      <c r="K34" s="45" t="n"/>
+      <c r="L34" s="45" t="inlineStr">
         <is>
           <t>In game</t>
         </is>
       </c>
-      <c r="M19" s="45" t="n"/>
-    </row>
-    <row r="20" ht="230" customHeight="1" s="35">
-      <c r="A20" s="43" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="43" t="inlineStr">
+      <c r="M34" s="45" t="n"/>
+    </row>
+    <row r="35" ht="230" customHeight="1" s="35">
+      <c r="A35" s="43" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="43" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C20" s="43" t="inlineStr">
+      <c r="C35" s="43" t="inlineStr">
         <is>
           <t>Minions</t>
         </is>
       </c>
-      <c r="D20" s="44" t="inlineStr">
+      <c r="D35" s="44" t="inlineStr">
         <is>
           <t>minion_paper_weak.png</t>
         </is>
       </c>
-      <c r="E20" s="43" t="inlineStr">
+      <c r="E35" s="43" t="inlineStr">
         <is>
           <t>Printer → paper (weak)</t>
         </is>
       </c>
-      <c r="F20" s="43" t="inlineStr">
+      <c r="F35" s="43" t="inlineStr">
         <is>
           <t>4 × 1</t>
         </is>
       </c>
-      <c r="G20" s="43" t="inlineStr">
+      <c r="G35" s="43" t="inlineStr">
         <is>
           <t>24×24</t>
         </is>
       </c>
-      <c r="H20" s="43" t="inlineStr">
+      <c r="H35" s="43" t="inlineStr">
         <is>
           <t>Wide landscape image, 1536×1024</t>
         </is>
       </c>
-      <c r="I20" s="43" t="inlineStr"/>
-      <c r="J20" s="43" t="inlineStr">
+      <c r="I35" s="43" t="inlineStr"/>
+      <c r="J35" s="43" t="inlineStr">
         <is>
           <t>Art style: retro 8-bit pixel art, like a Japanese console game from around 1990, set in a 1990s Japanese office. Chunky square pixels with hard edges: no anti-aliasing, no blur, no soft shading, no gradients, no painterly or paper texture. Every character and object has a 1-pixel dark ink outline. Flat colours from one small palette only: ink black, night indigo, slate blue, paper cream, warm grey, vermilion red, deep red, gold, ochre, wood brown, celadon green, moss green, sakura pink, peach. Subtle Japanese touches where they fit (seigaiha wave patterns, shoji paper screens, paper lanterns, hanko stamps, maneki-neko, daruma, bonsai). Satirical anthropomorphic animals. Clean, readable game asset. No text, letters, numbers, watermark, signature or frame.
 Camera: classic Japanese top-down RPG view (three-quarter view from above and in front): you see the top and the front of things; characters show their face when they face down.
@@ -36157,55 +37128,55 @@
 Output: PNG, Wide landscape image, 1536×1024.</t>
         </is>
       </c>
-      <c r="K20" s="45" t="n"/>
-      <c r="L20" s="45" t="inlineStr">
+      <c r="K35" s="45" t="n"/>
+      <c r="L35" s="45" t="inlineStr">
         <is>
           <t>In game</t>
         </is>
       </c>
-      <c r="M20" s="45" t="n"/>
-    </row>
-    <row r="21" ht="230" customHeight="1" s="35">
-      <c r="A21" s="43" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="43" t="inlineStr">
+      <c r="M35" s="45" t="n"/>
+    </row>
+    <row r="36" ht="230" customHeight="1" s="35">
+      <c r="A36" s="43" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="43" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C21" s="43" t="inlineStr">
+      <c r="C36" s="43" t="inlineStr">
         <is>
           <t>Minions</t>
         </is>
       </c>
-      <c r="D21" s="44" t="inlineStr">
+      <c r="D36" s="44" t="inlineStr">
         <is>
           <t>minion_paper_strong.png</t>
         </is>
       </c>
-      <c r="E21" s="43" t="inlineStr">
+      <c r="E36" s="43" t="inlineStr">
         <is>
           <t>Printer → paper (strong)</t>
         </is>
       </c>
-      <c r="F21" s="43" t="inlineStr">
+      <c r="F36" s="43" t="inlineStr">
         <is>
           <t>4 × 1</t>
         </is>
       </c>
-      <c r="G21" s="43" t="inlineStr">
+      <c r="G36" s="43" t="inlineStr">
         <is>
           <t>32×32</t>
         </is>
       </c>
-      <c r="H21" s="43" t="inlineStr">
+      <c r="H36" s="43" t="inlineStr">
         <is>
           <t>Wide landscape image, 1536×1024</t>
         </is>
       </c>
-      <c r="I21" s="43" t="inlineStr"/>
-      <c r="J21" s="43" t="inlineStr">
+      <c r="I36" s="43" t="inlineStr"/>
+      <c r="J36" s="43" t="inlineStr">
         <is>
           <t>Art style: retro 8-bit pixel art, like a Japanese console game from around 1990, set in a 1990s Japanese office. Chunky square pixels with hard edges: no anti-aliasing, no blur, no soft shading, no gradients, no painterly or paper texture. Every character and object has a 1-pixel dark ink outline. Flat colours from one small palette only: ink black, night indigo, slate blue, paper cream, warm grey, vermilion red, deep red, gold, ochre, wood brown, celadon green, moss green, sakura pink, peach. Subtle Japanese touches where they fit (seigaiha wave patterns, shoji paper screens, paper lanterns, hanko stamps, maneki-neko, daruma, bonsai). Satirical anthropomorphic animals. Clean, readable game asset. No text, letters, numbers, watermark, signature or frame.
 Camera: classic Japanese top-down RPG view (three-quarter view from above and in front): you see the top and the front of things; characters show their face when they face down.
@@ -36216,55 +37187,55 @@
 Output: PNG, Wide landscape image, 1536×1024.</t>
         </is>
       </c>
-      <c r="K21" s="45" t="n"/>
-      <c r="L21" s="45" t="inlineStr">
+      <c r="K36" s="45" t="n"/>
+      <c r="L36" s="45" t="inlineStr">
         <is>
           <t>In game</t>
         </is>
       </c>
-      <c r="M21" s="45" t="n"/>
-    </row>
-    <row r="22" ht="230" customHeight="1" s="35">
-      <c r="A22" s="43" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="43" t="inlineStr">
+      <c r="M36" s="45" t="n"/>
+    </row>
+    <row r="37" ht="230" customHeight="1" s="35">
+      <c r="A37" s="43" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="43" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C22" s="43" t="inlineStr">
+      <c r="C37" s="43" t="inlineStr">
         <is>
           <t>Minions</t>
         </is>
       </c>
-      <c r="D22" s="44" t="inlineStr">
+      <c r="D37" s="44" t="inlineStr">
         <is>
           <t>minion_coffee_weak.png</t>
         </is>
       </c>
-      <c r="E22" s="43" t="inlineStr">
+      <c r="E37" s="43" t="inlineStr">
         <is>
           <t>Coffee machine → coffee / expired milk / broken cup (weak)</t>
         </is>
       </c>
-      <c r="F22" s="43" t="inlineStr">
+      <c r="F37" s="43" t="inlineStr">
         <is>
           <t>4 × 1</t>
         </is>
       </c>
-      <c r="G22" s="43" t="inlineStr">
+      <c r="G37" s="43" t="inlineStr">
         <is>
           <t>24×24</t>
         </is>
       </c>
-      <c r="H22" s="43" t="inlineStr">
+      <c r="H37" s="43" t="inlineStr">
         <is>
           <t>Wide landscape image, 1536×1024</t>
         </is>
       </c>
-      <c r="I22" s="43" t="inlineStr"/>
-      <c r="J22" s="43" t="inlineStr">
+      <c r="I37" s="43" t="inlineStr"/>
+      <c r="J37" s="43" t="inlineStr">
         <is>
           <t>Art style: retro 8-bit pixel art, like a Japanese console game from around 1990, set in a 1990s Japanese office. Chunky square pixels with hard edges: no anti-aliasing, no blur, no soft shading, no gradients, no painterly or paper texture. Every character and object has a 1-pixel dark ink outline. Flat colours from one small palette only: ink black, night indigo, slate blue, paper cream, warm grey, vermilion red, deep red, gold, ochre, wood brown, celadon green, moss green, sakura pink, peach. Subtle Japanese touches where they fit (seigaiha wave patterns, shoji paper screens, paper lanterns, hanko stamps, maneki-neko, daruma, bonsai). Satirical anthropomorphic animals. Clean, readable game asset. No text, letters, numbers, watermark, signature or frame.
 Camera: classic Japanese top-down RPG view (three-quarter view from above and in front): you see the top and the front of things; characters show their face when they face down.
@@ -36275,55 +37246,55 @@
 Output: PNG, Wide landscape image, 1536×1024.</t>
         </is>
       </c>
-      <c r="K22" s="45" t="n"/>
-      <c r="L22" s="45" t="inlineStr">
+      <c r="K37" s="45" t="n"/>
+      <c r="L37" s="45" t="inlineStr">
         <is>
           <t>In game</t>
         </is>
       </c>
-      <c r="M22" s="45" t="n"/>
-    </row>
-    <row r="23" ht="230" customHeight="1" s="35">
-      <c r="A23" s="43" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" s="43" t="inlineStr">
+      <c r="M37" s="45" t="n"/>
+    </row>
+    <row r="38" ht="230" customHeight="1" s="35">
+      <c r="A38" s="43" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="43" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C23" s="43" t="inlineStr">
+      <c r="C38" s="43" t="inlineStr">
         <is>
           <t>Minions</t>
         </is>
       </c>
-      <c r="D23" s="44" t="inlineStr">
+      <c r="D38" s="44" t="inlineStr">
         <is>
           <t>minion_coffee_strong.png</t>
         </is>
       </c>
-      <c r="E23" s="43" t="inlineStr">
+      <c r="E38" s="43" t="inlineStr">
         <is>
           <t>Coffee machine → coffee / expired milk / broken cup (strong)</t>
         </is>
       </c>
-      <c r="F23" s="43" t="inlineStr">
+      <c r="F38" s="43" t="inlineStr">
         <is>
           <t>4 × 1</t>
         </is>
       </c>
-      <c r="G23" s="43" t="inlineStr">
+      <c r="G38" s="43" t="inlineStr">
         <is>
           <t>32×32</t>
         </is>
       </c>
-      <c r="H23" s="43" t="inlineStr">
+      <c r="H38" s="43" t="inlineStr">
         <is>
           <t>Wide landscape image, 1536×1024</t>
         </is>
       </c>
-      <c r="I23" s="43" t="inlineStr"/>
-      <c r="J23" s="43" t="inlineStr">
+      <c r="I38" s="43" t="inlineStr"/>
+      <c r="J38" s="43" t="inlineStr">
         <is>
           <t>Art style: retro 8-bit pixel art, like a Japanese console game from around 1990, set in a 1990s Japanese office. Chunky square pixels with hard edges: no anti-aliasing, no blur, no soft shading, no gradients, no painterly or paper texture. Every character and object has a 1-pixel dark ink outline. Flat colours from one small palette only: ink black, night indigo, slate blue, paper cream, warm grey, vermilion red, deep red, gold, ochre, wood brown, celadon green, moss green, sakura pink, peach. Subtle Japanese touches where they fit (seigaiha wave patterns, shoji paper screens, paper lanterns, hanko stamps, maneki-neko, daruma, bonsai). Satirical anthropomorphic animals. Clean, readable game asset. No text, letters, numbers, watermark, signature or frame.
 Camera: classic Japanese top-down RPG view (three-quarter view from above and in front): you see the top and the front of things; characters show their face when they face down.
@@ -36334,55 +37305,55 @@
 Output: PNG, Wide landscape image, 1536×1024.</t>
         </is>
       </c>
-      <c r="K23" s="45" t="n"/>
-      <c r="L23" s="45" t="inlineStr">
+      <c r="K38" s="45" t="n"/>
+      <c r="L38" s="45" t="inlineStr">
         <is>
           <t>In game</t>
         </is>
       </c>
-      <c r="M23" s="45" t="n"/>
-    </row>
-    <row r="24" ht="230" customHeight="1" s="35">
-      <c r="A24" s="43" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" s="43" t="inlineStr">
+      <c r="M38" s="45" t="n"/>
+    </row>
+    <row r="39" ht="230" customHeight="1" s="35">
+      <c r="A39" s="43" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="43" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C24" s="43" t="inlineStr">
+      <c r="C39" s="43" t="inlineStr">
         <is>
           <t>Minions</t>
         </is>
       </c>
-      <c r="D24" s="44" t="inlineStr">
+      <c r="D39" s="44" t="inlineStr">
         <is>
           <t>minion_ice_weak.png</t>
         </is>
       </c>
-      <c r="E24" s="43" t="inlineStr">
+      <c r="E39" s="43" t="inlineStr">
         <is>
           <t>Air conditioner → ice cubes (weak)</t>
         </is>
       </c>
-      <c r="F24" s="43" t="inlineStr">
+      <c r="F39" s="43" t="inlineStr">
         <is>
           <t>4 × 1</t>
         </is>
       </c>
-      <c r="G24" s="43" t="inlineStr">
+      <c r="G39" s="43" t="inlineStr">
         <is>
           <t>24×24</t>
         </is>
       </c>
-      <c r="H24" s="43" t="inlineStr">
+      <c r="H39" s="43" t="inlineStr">
         <is>
           <t>Wide landscape image, 1536×1024</t>
         </is>
       </c>
-      <c r="I24" s="43" t="inlineStr"/>
-      <c r="J24" s="43" t="inlineStr">
+      <c r="I39" s="43" t="inlineStr"/>
+      <c r="J39" s="43" t="inlineStr">
         <is>
           <t>Art style: retro 8-bit pixel art, like a Japanese console game from around 1990, set in a 1990s Japanese office. Chunky square pixels with hard edges: no anti-aliasing, no blur, no soft shading, no gradients, no painterly or paper texture. Every character and object has a 1-pixel dark ink outline. Flat colours from one small palette only: ink black, night indigo, slate blue, paper cream, warm grey, vermilion red, deep red, gold, ochre, wood brown, celadon green, moss green, sakura pink, peach. Subtle Japanese touches where they fit (seigaiha wave patterns, shoji paper screens, paper lanterns, hanko stamps, maneki-neko, daruma, bonsai). Satirical anthropomorphic animals. Clean, readable game asset. No text, letters, numbers, watermark, signature or frame.
 Camera: classic Japanese top-down RPG view (three-quarter view from above and in front): you see the top and the front of things; characters show their face when they face down.
@@ -36393,55 +37364,55 @@
 Output: PNG, Wide landscape image, 1536×1024.</t>
         </is>
       </c>
-      <c r="K24" s="45" t="n"/>
-      <c r="L24" s="45" t="inlineStr">
+      <c r="K39" s="45" t="n"/>
+      <c r="L39" s="45" t="inlineStr">
         <is>
           <t>In game</t>
         </is>
       </c>
-      <c r="M24" s="45" t="n"/>
-    </row>
-    <row r="25" ht="230" customHeight="1" s="35">
-      <c r="A25" s="43" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" s="43" t="inlineStr">
+      <c r="M39" s="45" t="n"/>
+    </row>
+    <row r="40" ht="230" customHeight="1" s="35">
+      <c r="A40" s="43" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="43" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C25" s="43" t="inlineStr">
+      <c r="C40" s="43" t="inlineStr">
         <is>
           <t>Minions</t>
         </is>
       </c>
-      <c r="D25" s="44" t="inlineStr">
+      <c r="D40" s="44" t="inlineStr">
         <is>
           <t>minion_ice_strong.png</t>
         </is>
       </c>
-      <c r="E25" s="43" t="inlineStr">
+      <c r="E40" s="43" t="inlineStr">
         <is>
           <t>Air conditioner → ice cubes (strong)</t>
         </is>
       </c>
-      <c r="F25" s="43" t="inlineStr">
+      <c r="F40" s="43" t="inlineStr">
         <is>
           <t>4 × 1</t>
         </is>
       </c>
-      <c r="G25" s="43" t="inlineStr">
+      <c r="G40" s="43" t="inlineStr">
         <is>
           <t>32×32</t>
         </is>
       </c>
-      <c r="H25" s="43" t="inlineStr">
+      <c r="H40" s="43" t="inlineStr">
         <is>
           <t>Wide landscape image, 1536×1024</t>
         </is>
       </c>
-      <c r="I25" s="43" t="inlineStr"/>
-      <c r="J25" s="43" t="inlineStr">
+      <c r="I40" s="43" t="inlineStr"/>
+      <c r="J40" s="43" t="inlineStr">
         <is>
           <t>Art style: retro 8-bit pixel art, like a Japanese console game from around 1990, set in a 1990s Japanese office. Chunky square pixels with hard edges: no anti-aliasing, no blur, no soft shading, no gradients, no painterly or paper texture. Every character and object has a 1-pixel dark ink outline. Flat colours from one small palette only: ink black, night indigo, slate blue, paper cream, warm grey, vermilion red, deep red, gold, ochre, wood brown, celadon green, moss green, sakura pink, peach. Subtle Japanese touches where they fit (seigaiha wave patterns, shoji paper screens, paper lanterns, hanko stamps, maneki-neko, daruma, bonsai). Satirical anthropomorphic animals. Clean, readable game asset. No text, letters, numbers, watermark, signature or frame.
 Camera: classic Japanese top-down RPG view (three-quarter view from above and in front): you see the top and the front of things; characters show their face when they face down.
@@ -36452,55 +37423,55 @@
 Output: PNG, Wide landscape image, 1536×1024.</t>
         </is>
       </c>
-      <c r="K25" s="45" t="n"/>
-      <c r="L25" s="45" t="inlineStr">
+      <c r="K40" s="45" t="n"/>
+      <c r="L40" s="45" t="inlineStr">
         <is>
           <t>In game</t>
         </is>
       </c>
-      <c r="M25" s="45" t="n"/>
-    </row>
-    <row r="26" ht="230" customHeight="1" s="35">
-      <c r="A26" s="43" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" s="43" t="inlineStr">
+      <c r="M40" s="45" t="n"/>
+    </row>
+    <row r="41" ht="230" customHeight="1" s="35">
+      <c r="A41" s="43" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="43" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C26" s="43" t="inlineStr">
+      <c r="C41" s="43" t="inlineStr">
         <is>
           <t>Minions</t>
         </is>
       </c>
-      <c r="D26" s="44" t="inlineStr">
+      <c r="D41" s="44" t="inlineStr">
         <is>
           <t>minion_heart_weak.png</t>
         </is>
       </c>
-      <c r="E26" s="43" t="inlineStr">
+      <c r="E41" s="43" t="inlineStr">
         <is>
           <t>Final Boss → pink hearts (weak)</t>
         </is>
       </c>
-      <c r="F26" s="43" t="inlineStr">
+      <c r="F41" s="43" t="inlineStr">
         <is>
           <t>4 × 1</t>
         </is>
       </c>
-      <c r="G26" s="43" t="inlineStr">
+      <c r="G41" s="43" t="inlineStr">
         <is>
           <t>24×24</t>
         </is>
       </c>
-      <c r="H26" s="43" t="inlineStr">
+      <c r="H41" s="43" t="inlineStr">
         <is>
           <t>Wide landscape image, 1536×1024</t>
         </is>
       </c>
-      <c r="I26" s="43" t="inlineStr"/>
-      <c r="J26" s="43" t="inlineStr">
+      <c r="I41" s="43" t="inlineStr"/>
+      <c r="J41" s="43" t="inlineStr">
         <is>
           <t>Art style: retro 8-bit pixel art, like a Japanese console game from around 1990, set in a 1990s Japanese office. Chunky square pixels with hard edges: no anti-aliasing, no blur, no soft shading, no gradients, no painterly or paper texture. Every character and object has a 1-pixel dark ink outline. Flat colours from one small palette only: ink black, night indigo, slate blue, paper cream, warm grey, vermilion red, deep red, gold, ochre, wood brown, celadon green, moss green, sakura pink, peach. Subtle Japanese touches where they fit (seigaiha wave patterns, shoji paper screens, paper lanterns, hanko stamps, maneki-neko, daruma, bonsai). Satirical anthropomorphic animals. Clean, readable game asset. No text, letters, numbers, watermark, signature or frame.
 Camera: classic Japanese top-down RPG view (three-quarter view from above and in front): you see the top and the front of things; characters show their face when they face down.
@@ -36511,55 +37482,55 @@
 Output: PNG, Wide landscape image, 1536×1024.</t>
         </is>
       </c>
-      <c r="K26" s="45" t="n"/>
-      <c r="L26" s="45" t="inlineStr">
+      <c r="K41" s="45" t="n"/>
+      <c r="L41" s="45" t="inlineStr">
         <is>
           <t>In game</t>
         </is>
       </c>
-      <c r="M26" s="45" t="n"/>
-    </row>
-    <row r="27" ht="230" customHeight="1" s="35">
-      <c r="A27" s="43" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" s="43" t="inlineStr">
+      <c r="M41" s="45" t="n"/>
+    </row>
+    <row r="42" ht="230" customHeight="1" s="35">
+      <c r="A42" s="43" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="43" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C27" s="43" t="inlineStr">
+      <c r="C42" s="43" t="inlineStr">
         <is>
           <t>Minions</t>
         </is>
       </c>
-      <c r="D27" s="44" t="inlineStr">
+      <c r="D42" s="44" t="inlineStr">
         <is>
           <t>minion_heart_strong.png</t>
         </is>
       </c>
-      <c r="E27" s="43" t="inlineStr">
+      <c r="E42" s="43" t="inlineStr">
         <is>
           <t>Final Boss → pink hearts (strong)</t>
         </is>
       </c>
-      <c r="F27" s="43" t="inlineStr">
+      <c r="F42" s="43" t="inlineStr">
         <is>
           <t>4 × 1</t>
         </is>
       </c>
-      <c r="G27" s="43" t="inlineStr">
+      <c r="G42" s="43" t="inlineStr">
         <is>
           <t>32×32</t>
         </is>
       </c>
-      <c r="H27" s="43" t="inlineStr">
+      <c r="H42" s="43" t="inlineStr">
         <is>
           <t>Wide landscape image, 1536×1024</t>
         </is>
       </c>
-      <c r="I27" s="43" t="inlineStr"/>
-      <c r="J27" s="43" t="inlineStr">
+      <c r="I42" s="43" t="inlineStr"/>
+      <c r="J42" s="43" t="inlineStr">
         <is>
           <t>Art style: retro 8-bit pixel art, like a Japanese console game from around 1990, set in a 1990s Japanese office. Chunky square pixels with hard edges: no anti-aliasing, no blur, no soft shading, no gradients, no painterly or paper texture. Every character and object has a 1-pixel dark ink outline. Flat colours from one small palette only: ink black, night indigo, slate blue, paper cream, warm grey, vermilion red, deep red, gold, ochre, wood brown, celadon green, moss green, sakura pink, peach. Subtle Japanese touches where they fit (seigaiha wave patterns, shoji paper screens, paper lanterns, hanko stamps, maneki-neko, daruma, bonsai). Satirical anthropomorphic animals. Clean, readable game asset. No text, letters, numbers, watermark, signature or frame.
 Camera: classic Japanese top-down RPG view (three-quarter view from above and in front): you see the top and the front of things; characters show their face when they face down.
@@ -36570,55 +37541,55 @@
 Output: PNG, Wide landscape image, 1536×1024.</t>
         </is>
       </c>
-      <c r="K27" s="45" t="n"/>
-      <c r="L27" s="45" t="inlineStr">
+      <c r="K42" s="45" t="n"/>
+      <c r="L42" s="45" t="inlineStr">
         <is>
           <t>In game</t>
         </is>
       </c>
-      <c r="M27" s="45" t="n"/>
-    </row>
-    <row r="28" ht="230" customHeight="1" s="35">
-      <c r="A28" s="43" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" s="43" t="inlineStr">
+      <c r="M42" s="45" t="n"/>
+    </row>
+    <row r="43" ht="230" customHeight="1" s="35">
+      <c r="A43" s="43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="43" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C28" s="43" t="inlineStr">
+      <c r="C43" s="43" t="inlineStr">
         <is>
           <t>Colleagues</t>
         </is>
       </c>
-      <c r="D28" s="44" t="inlineStr">
+      <c r="D43" s="44" t="inlineStr">
         <is>
           <t>npc_dog.png</t>
         </is>
       </c>
-      <c r="E28" s="43" t="inlineStr">
+      <c r="E43" s="43" t="inlineStr">
         <is>
           <t>NPC - energy boost — Office dog</t>
         </is>
       </c>
-      <c r="F28" s="43" t="inlineStr">
+      <c r="F43" s="43" t="inlineStr">
         <is>
           <t>4 × 1</t>
         </is>
       </c>
-      <c r="G28" s="43" t="inlineStr">
+      <c r="G43" s="43" t="inlineStr">
         <is>
           <t>32×32</t>
         </is>
       </c>
-      <c r="H28" s="43" t="inlineStr">
+      <c r="H43" s="43" t="inlineStr">
         <is>
           <t>Wide landscape image, 1536×1024</t>
         </is>
       </c>
-      <c r="I28" s="43" t="inlineStr"/>
-      <c r="J28" s="43" t="inlineStr">
+      <c r="I43" s="43" t="inlineStr"/>
+      <c r="J43" s="43" t="inlineStr">
         <is>
           <t>Art style: retro 8-bit pixel art, like a Japanese console game from around 1990, set in a 1990s Japanese office. Chunky square pixels with hard edges: no anti-aliasing, no blur, no soft shading, no gradients, no painterly or paper texture. Every character and object has a 1-pixel dark ink outline. Flat colours from one small palette only: ink black, night indigo, slate blue, paper cream, warm grey, vermilion red, deep red, gold, ochre, wood brown, celadon green, moss green, sakura pink, peach. Subtle Japanese touches where they fit (seigaiha wave patterns, shoji paper screens, paper lanterns, hanko stamps, maneki-neko, daruma, bonsai). Satirical anthropomorphic animals. Clean, readable game asset. No text, letters, numbers, watermark, signature or frame.
 Camera: classic Japanese top-down RPG view (three-quarter view from above and in front): you see the top and the front of things; characters show their face when they face down.
@@ -36629,55 +37600,55 @@
 Output: PNG, Wide landscape image, 1536×1024.</t>
         </is>
       </c>
-      <c r="K28" s="45" t="n"/>
-      <c r="L28" s="45" t="inlineStr">
+      <c r="K43" s="45" t="n"/>
+      <c r="L43" s="45" t="inlineStr">
         <is>
           <t>In game</t>
         </is>
       </c>
-      <c r="M28" s="45" t="n"/>
-    </row>
-    <row r="29" ht="230" customHeight="1" s="35">
-      <c r="A29" s="43" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" s="43" t="inlineStr">
+      <c r="M43" s="45" t="n"/>
+    </row>
+    <row r="44" ht="230" customHeight="1" s="35">
+      <c r="A44" s="43" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="43" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C29" s="43" t="inlineStr">
+      <c r="C44" s="43" t="inlineStr">
         <is>
           <t>Colleagues</t>
         </is>
       </c>
-      <c r="D29" s="44" t="inlineStr">
+      <c r="D44" s="44" t="inlineStr">
         <is>
           <t>npc_bestie.png</t>
         </is>
       </c>
-      <c r="E29" s="43" t="inlineStr">
+      <c r="E44" s="43" t="inlineStr">
         <is>
           <t>NPC - energy boost — Work bestie</t>
         </is>
       </c>
-      <c r="F29" s="43" t="inlineStr">
+      <c r="F44" s="43" t="inlineStr">
         <is>
           <t>4 × 1</t>
         </is>
       </c>
-      <c r="G29" s="43" t="inlineStr">
+      <c r="G44" s="43" t="inlineStr">
         <is>
           <t>32×32</t>
         </is>
       </c>
-      <c r="H29" s="43" t="inlineStr">
+      <c r="H44" s="43" t="inlineStr">
         <is>
           <t>Wide landscape image, 1536×1024</t>
         </is>
       </c>
-      <c r="I29" s="43" t="inlineStr"/>
-      <c r="J29" s="43" t="inlineStr">
+      <c r="I44" s="43" t="inlineStr"/>
+      <c r="J44" s="43" t="inlineStr">
         <is>
           <t>Art style: retro 8-bit pixel art, like a Japanese console game from around 1990, set in a 1990s Japanese office. Chunky square pixels with hard edges: no anti-aliasing, no blur, no soft shading, no gradients, no painterly or paper texture. Every character and object has a 1-pixel dark ink outline. Flat colours from one small palette only: ink black, night indigo, slate blue, paper cream, warm grey, vermilion red, deep red, gold, ochre, wood brown, celadon green, moss green, sakura pink, peach. Subtle Japanese touches where they fit (seigaiha wave patterns, shoji paper screens, paper lanterns, hanko stamps, maneki-neko, daruma, bonsai). Satirical anthropomorphic animals. Clean, readable game asset. No text, letters, numbers, watermark, signature or frame.
 Camera: classic Japanese top-down RPG view (three-quarter view from above and in front): you see the top and the front of things; characters show their face when they face down.
@@ -36688,55 +37659,55 @@
 Output: PNG, Wide landscape image, 1536×1024.</t>
         </is>
       </c>
-      <c r="K29" s="45" t="n"/>
-      <c r="L29" s="45" t="inlineStr">
+      <c r="K44" s="45" t="n"/>
+      <c r="L44" s="45" t="inlineStr">
         <is>
           <t>In game</t>
         </is>
       </c>
-      <c r="M29" s="45" t="n"/>
-    </row>
-    <row r="30" ht="230" customHeight="1" s="35">
-      <c r="A30" s="43" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" s="43" t="inlineStr">
+      <c r="M44" s="45" t="n"/>
+    </row>
+    <row r="45" ht="230" customHeight="1" s="35">
+      <c r="A45" s="43" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="43" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C30" s="43" t="inlineStr">
+      <c r="C45" s="43" t="inlineStr">
         <is>
           <t>Colleagues</t>
         </is>
       </c>
-      <c r="D30" s="44" t="inlineStr">
+      <c r="D45" s="44" t="inlineStr">
         <is>
           <t>npc_baker.png</t>
         </is>
       </c>
-      <c r="E30" s="43" t="inlineStr">
+      <c r="E45" s="43" t="inlineStr">
         <is>
           <t>NPC - energy boost — Colleague who brings cookies</t>
         </is>
       </c>
-      <c r="F30" s="43" t="inlineStr">
+      <c r="F45" s="43" t="inlineStr">
         <is>
           <t>4 × 1</t>
         </is>
       </c>
-      <c r="G30" s="43" t="inlineStr">
+      <c r="G45" s="43" t="inlineStr">
         <is>
           <t>32×32</t>
         </is>
       </c>
-      <c r="H30" s="43" t="inlineStr">
+      <c r="H45" s="43" t="inlineStr">
         <is>
           <t>Wide landscape image, 1536×1024</t>
         </is>
       </c>
-      <c r="I30" s="43" t="inlineStr"/>
-      <c r="J30" s="43" t="inlineStr">
+      <c r="I45" s="43" t="inlineStr"/>
+      <c r="J45" s="43" t="inlineStr">
         <is>
           <t>Art style: retro 8-bit pixel art, like a Japanese console game from around 1990, set in a 1990s Japanese office. Chunky square pixels with hard edges: no anti-aliasing, no blur, no soft shading, no gradients, no painterly or paper texture. Every character and object has a 1-pixel dark ink outline. Flat colours from one small palette only: ink black, night indigo, slate blue, paper cream, warm grey, vermilion red, deep red, gold, ochre, wood brown, celadon green, moss green, sakura pink, peach. Subtle Japanese touches where they fit (seigaiha wave patterns, shoji paper screens, paper lanterns, hanko stamps, maneki-neko, daruma, bonsai). Satirical anthropomorphic animals. Clean, readable game asset. No text, letters, numbers, watermark, signature or frame.
 Camera: classic Japanese top-down RPG view (three-quarter view from above and in front): you see the top and the front of things; characters show their face when they face down.
@@ -36747,55 +37718,55 @@
 Output: PNG, Wide landscape image, 1536×1024.</t>
         </is>
       </c>
-      <c r="K30" s="45" t="n"/>
-      <c r="L30" s="45" t="inlineStr">
+      <c r="K45" s="45" t="n"/>
+      <c r="L45" s="45" t="inlineStr">
         <is>
           <t>In game</t>
         </is>
       </c>
-      <c r="M30" s="45" t="n"/>
-    </row>
-    <row r="31" ht="230" customHeight="1" s="35">
-      <c r="A31" s="43" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" s="43" t="inlineStr">
+      <c r="M45" s="45" t="n"/>
+    </row>
+    <row r="46" ht="230" customHeight="1" s="35">
+      <c r="A46" s="43" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="43" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C31" s="43" t="inlineStr">
+      <c r="C46" s="43" t="inlineStr">
         <is>
           <t>Colleagues</t>
         </is>
       </c>
-      <c r="D31" s="44" t="inlineStr">
+      <c r="D46" s="44" t="inlineStr">
         <is>
           <t>npc_expert.png</t>
         </is>
       </c>
-      <c r="E31" s="43" t="inlineStr">
+      <c r="E46" s="43" t="inlineStr">
         <is>
           <t>NPC - energy boost — Kind expert colleague</t>
         </is>
       </c>
-      <c r="F31" s="43" t="inlineStr">
+      <c r="F46" s="43" t="inlineStr">
         <is>
           <t>4 × 1</t>
         </is>
       </c>
-      <c r="G31" s="43" t="inlineStr">
+      <c r="G46" s="43" t="inlineStr">
         <is>
           <t>32×32</t>
         </is>
       </c>
-      <c r="H31" s="43" t="inlineStr">
+      <c r="H46" s="43" t="inlineStr">
         <is>
           <t>Wide landscape image, 1536×1024</t>
         </is>
       </c>
-      <c r="I31" s="43" t="inlineStr"/>
-      <c r="J31" s="43" t="inlineStr">
+      <c r="I46" s="43" t="inlineStr"/>
+      <c r="J46" s="43" t="inlineStr">
         <is>
           <t>Art style: retro 8-bit pixel art, like a Japanese console game from around 1990, set in a 1990s Japanese office. Chunky square pixels with hard edges: no anti-aliasing, no blur, no soft shading, no gradients, no painterly or paper texture. Every character and object has a 1-pixel dark ink outline. Flat colours from one small palette only: ink black, night indigo, slate blue, paper cream, warm grey, vermilion red, deep red, gold, ochre, wood brown, celadon green, moss green, sakura pink, peach. Subtle Japanese touches where they fit (seigaiha wave patterns, shoji paper screens, paper lanterns, hanko stamps, maneki-neko, daruma, bonsai). Satirical anthropomorphic animals. Clean, readable game asset. No text, letters, numbers, watermark, signature or frame.
 Camera: classic Japanese top-down RPG view (three-quarter view from above and in front): you see the top and the front of things; characters show their face when they face down.
@@ -36806,55 +37777,55 @@
 Output: PNG, Wide landscape image, 1536×1024.</t>
         </is>
       </c>
-      <c r="K31" s="45" t="n"/>
-      <c r="L31" s="45" t="inlineStr">
+      <c r="K46" s="45" t="n"/>
+      <c r="L46" s="45" t="inlineStr">
         <is>
           <t>In game</t>
         </is>
       </c>
-      <c r="M31" s="45" t="n"/>
-    </row>
-    <row r="32" ht="230" customHeight="1" s="35">
-      <c r="A32" s="43" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" s="43" t="inlineStr">
+      <c r="M46" s="45" t="n"/>
+    </row>
+    <row r="47" ht="230" customHeight="1" s="35">
+      <c r="A47" s="43" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="43" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C32" s="43" t="inlineStr">
+      <c r="C47" s="43" t="inlineStr">
         <is>
           <t>Colleagues</t>
         </is>
       </c>
-      <c r="D32" s="44" t="inlineStr">
+      <c r="D47" s="44" t="inlineStr">
         <is>
           <t>npc_meeting_saver.png</t>
         </is>
       </c>
-      <c r="E32" s="43" t="inlineStr">
+      <c r="E47" s="43" t="inlineStr">
         <is>
           <t>NPC - energy boost — Meeting saver</t>
         </is>
       </c>
-      <c r="F32" s="43" t="inlineStr">
+      <c r="F47" s="43" t="inlineStr">
         <is>
           <t>4 × 1</t>
         </is>
       </c>
-      <c r="G32" s="43" t="inlineStr">
+      <c r="G47" s="43" t="inlineStr">
         <is>
           <t>32×32</t>
         </is>
       </c>
-      <c r="H32" s="43" t="inlineStr">
+      <c r="H47" s="43" t="inlineStr">
         <is>
           <t>Wide landscape image, 1536×1024</t>
         </is>
       </c>
-      <c r="I32" s="43" t="inlineStr"/>
-      <c r="J32" s="43" t="inlineStr">
+      <c r="I47" s="43" t="inlineStr"/>
+      <c r="J47" s="43" t="inlineStr">
         <is>
           <t>Art style: retro 8-bit pixel art, like a Japanese console game from around 1990, set in a 1990s Japanese office. Chunky square pixels with hard edges: no anti-aliasing, no blur, no soft shading, no gradients, no painterly or paper texture. Every character and object has a 1-pixel dark ink outline. Flat colours from one small palette only: ink black, night indigo, slate blue, paper cream, warm grey, vermilion red, deep red, gold, ochre, wood brown, celadon green, moss green, sakura pink, peach. Subtle Japanese touches where they fit (seigaiha wave patterns, shoji paper screens, paper lanterns, hanko stamps, maneki-neko, daruma, bonsai). Satirical anthropomorphic animals. Clean, readable game asset. No text, letters, numbers, watermark, signature or frame.
 Camera: classic Japanese top-down RPG view (three-quarter view from above and in front): you see the top and the front of things; characters show their face when they face down.
@@ -36865,55 +37836,55 @@
 Output: PNG, Wide landscape image, 1536×1024.</t>
         </is>
       </c>
-      <c r="K32" s="45" t="n"/>
-      <c r="L32" s="45" t="inlineStr">
+      <c r="K47" s="45" t="n"/>
+      <c r="L47" s="45" t="inlineStr">
         <is>
           <t>In game</t>
         </is>
       </c>
-      <c r="M32" s="45" t="n"/>
-    </row>
-    <row r="33" ht="230" customHeight="1" s="35">
-      <c r="A33" s="43" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" s="43" t="inlineStr">
+      <c r="M47" s="45" t="n"/>
+    </row>
+    <row r="48" ht="230" customHeight="1" s="35">
+      <c r="A48" s="43" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="43" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C33" s="43" t="inlineStr">
+      <c r="C48" s="43" t="inlineStr">
         <is>
           <t>Colleagues</t>
         </is>
       </c>
-      <c r="D33" s="44" t="inlineStr">
+      <c r="D48" s="44" t="inlineStr">
         <is>
           <t>npc_shouter.png</t>
         </is>
       </c>
-      <c r="E33" s="43" t="inlineStr">
+      <c r="E48" s="43" t="inlineStr">
         <is>
           <t>NPC - energy vampire — Shouting mid-manager</t>
         </is>
       </c>
-      <c r="F33" s="43" t="inlineStr">
+      <c r="F48" s="43" t="inlineStr">
         <is>
           <t>4 × 1</t>
         </is>
       </c>
-      <c r="G33" s="43" t="inlineStr">
+      <c r="G48" s="43" t="inlineStr">
         <is>
           <t>32×32</t>
         </is>
       </c>
-      <c r="H33" s="43" t="inlineStr">
+      <c r="H48" s="43" t="inlineStr">
         <is>
           <t>Wide landscape image, 1536×1024</t>
         </is>
       </c>
-      <c r="I33" s="43" t="inlineStr"/>
-      <c r="J33" s="43" t="inlineStr">
+      <c r="I48" s="43" t="inlineStr"/>
+      <c r="J48" s="43" t="inlineStr">
         <is>
           <t>Art style: retro 8-bit pixel art, like a Japanese console game from around 1990, set in a 1990s Japanese office. Chunky square pixels with hard edges: no anti-aliasing, no blur, no soft shading, no gradients, no painterly or paper texture. Every character and object has a 1-pixel dark ink outline. Flat colours from one small palette only: ink black, night indigo, slate blue, paper cream, warm grey, vermilion red, deep red, gold, ochre, wood brown, celadon green, moss green, sakura pink, peach. Subtle Japanese touches where they fit (seigaiha wave patterns, shoji paper screens, paper lanterns, hanko stamps, maneki-neko, daruma, bonsai). Satirical anthropomorphic animals. Clean, readable game asset. No text, letters, numbers, watermark, signature or frame.
 Camera: classic Japanese top-down RPG view (three-quarter view from above and in front): you see the top and the front of things; characters show their face when they face down.
@@ -36924,55 +37895,55 @@
 Output: PNG, Wide landscape image, 1536×1024.</t>
         </is>
       </c>
-      <c r="K33" s="45" t="n"/>
-      <c r="L33" s="45" t="inlineStr">
+      <c r="K48" s="45" t="n"/>
+      <c r="L48" s="45" t="inlineStr">
         <is>
           <t>In game</t>
         </is>
       </c>
-      <c r="M33" s="45" t="n"/>
-    </row>
-    <row r="34" ht="230" customHeight="1" s="35">
-      <c r="A34" s="43" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" s="43" t="inlineStr">
+      <c r="M48" s="45" t="n"/>
+    </row>
+    <row r="49" ht="230" customHeight="1" s="35">
+      <c r="A49" s="43" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="43" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C34" s="43" t="inlineStr">
+      <c r="C49" s="43" t="inlineStr">
         <is>
           <t>Colleagues</t>
         </is>
       </c>
-      <c r="D34" s="44" t="inlineStr">
+      <c r="D49" s="44" t="inlineStr">
         <is>
           <t>npc_karen.png</t>
         </is>
       </c>
-      <c r="E34" s="43" t="inlineStr">
+      <c r="E49" s="43" t="inlineStr">
         <is>
           <t>NPC - energy vampire — Know-it-all colleague</t>
         </is>
       </c>
-      <c r="F34" s="43" t="inlineStr">
+      <c r="F49" s="43" t="inlineStr">
         <is>
           <t>4 × 1</t>
         </is>
       </c>
-      <c r="G34" s="43" t="inlineStr">
+      <c r="G49" s="43" t="inlineStr">
         <is>
           <t>32×32</t>
         </is>
       </c>
-      <c r="H34" s="43" t="inlineStr">
+      <c r="H49" s="43" t="inlineStr">
         <is>
           <t>Wide landscape image, 1536×1024</t>
         </is>
       </c>
-      <c r="I34" s="43" t="inlineStr"/>
-      <c r="J34" s="43" t="inlineStr">
+      <c r="I49" s="43" t="inlineStr"/>
+      <c r="J49" s="43" t="inlineStr">
         <is>
           <t>Art style: retro 8-bit pixel art, like a Japanese console game from around 1990, set in a 1990s Japanese office. Chunky square pixels with hard edges: no anti-aliasing, no blur, no soft shading, no gradients, no painterly or paper texture. Every character and object has a 1-pixel dark ink outline. Flat colours from one small palette only: ink black, night indigo, slate blue, paper cream, warm grey, vermilion red, deep red, gold, ochre, wood brown, celadon green, moss green, sakura pink, peach. Subtle Japanese touches where they fit (seigaiha wave patterns, shoji paper screens, paper lanterns, hanko stamps, maneki-neko, daruma, bonsai). Satirical anthropomorphic animals. Clean, readable game asset. No text, letters, numbers, watermark, signature or frame.
 Camera: classic Japanese top-down RPG view (three-quarter view from above and in front): you see the top and the front of things; characters show their face when they face down.
@@ -36983,55 +37954,55 @@
 Output: PNG, Wide landscape image, 1536×1024.</t>
         </is>
       </c>
-      <c r="K34" s="45" t="n"/>
-      <c r="L34" s="45" t="inlineStr">
+      <c r="K49" s="45" t="n"/>
+      <c r="L49" s="45" t="inlineStr">
         <is>
           <t>In game</t>
         </is>
       </c>
-      <c r="M34" s="45" t="n"/>
-    </row>
-    <row r="35" ht="230" customHeight="1" s="35">
-      <c r="A35" s="43" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" s="43" t="inlineStr">
+      <c r="M49" s="45" t="n"/>
+    </row>
+    <row r="50" ht="230" customHeight="1" s="35">
+      <c r="A50" s="43" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="43" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C35" s="43" t="inlineStr">
+      <c r="C50" s="43" t="inlineStr">
         <is>
           <t>Colleagues</t>
         </is>
       </c>
-      <c r="D35" s="44" t="inlineStr">
+      <c r="D50" s="44" t="inlineStr">
         <is>
           <t>npc_lazy.png</t>
         </is>
       </c>
-      <c r="E35" s="43" t="inlineStr">
+      <c r="E50" s="43" t="inlineStr">
         <is>
           <t>NPC - energy vampire — Lazy colleague</t>
         </is>
       </c>
-      <c r="F35" s="43" t="inlineStr">
+      <c r="F50" s="43" t="inlineStr">
         <is>
           <t>4 × 1</t>
         </is>
       </c>
-      <c r="G35" s="43" t="inlineStr">
+      <c r="G50" s="43" t="inlineStr">
         <is>
           <t>32×32</t>
         </is>
       </c>
-      <c r="H35" s="43" t="inlineStr">
+      <c r="H50" s="43" t="inlineStr">
         <is>
           <t>Wide landscape image, 1536×1024</t>
         </is>
       </c>
-      <c r="I35" s="43" t="inlineStr"/>
-      <c r="J35" s="43" t="inlineStr">
+      <c r="I50" s="43" t="inlineStr"/>
+      <c r="J50" s="43" t="inlineStr">
         <is>
           <t>Art style: retro 8-bit pixel art, like a Japanese console game from around 1990, set in a 1990s Japanese office. Chunky square pixels with hard edges: no anti-aliasing, no blur, no soft shading, no gradients, no painterly or paper texture. Every character and object has a 1-pixel dark ink outline. Flat colours from one small palette only: ink black, night indigo, slate blue, paper cream, warm grey, vermilion red, deep red, gold, ochre, wood brown, celadon green, moss green, sakura pink, peach. Subtle Japanese touches where they fit (seigaiha wave patterns, shoji paper screens, paper lanterns, hanko stamps, maneki-neko, daruma, bonsai). Satirical anthropomorphic animals. Clean, readable game asset. No text, letters, numbers, watermark, signature or frame.
 Camera: classic Japanese top-down RPG view (three-quarter view from above and in front): you see the top and the front of things; characters show their face when they face down.
@@ -37042,55 +38013,55 @@
 Output: PNG, Wide landscape image, 1536×1024.</t>
         </is>
       </c>
-      <c r="K35" s="45" t="n"/>
-      <c r="L35" s="45" t="inlineStr">
+      <c r="K50" s="45" t="n"/>
+      <c r="L50" s="45" t="inlineStr">
         <is>
           <t>In game</t>
         </is>
       </c>
-      <c r="M35" s="45" t="n"/>
-    </row>
-    <row r="36" ht="230" customHeight="1" s="35">
-      <c r="A36" s="43" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" s="43" t="inlineStr">
+      <c r="M50" s="45" t="n"/>
+    </row>
+    <row r="51" ht="230" customHeight="1" s="35">
+      <c r="A51" s="43" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="43" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C36" s="43" t="inlineStr">
+      <c r="C51" s="43" t="inlineStr">
         <is>
           <t>Colleagues</t>
         </is>
       </c>
-      <c r="D36" s="44" t="inlineStr">
+      <c r="D51" s="44" t="inlineStr">
         <is>
           <t>npc_photos.png</t>
         </is>
       </c>
-      <c r="E36" s="43" t="inlineStr">
+      <c r="E51" s="43" t="inlineStr">
         <is>
           <t>NPC - energy vampire — Shows pet/family photos</t>
         </is>
       </c>
-      <c r="F36" s="43" t="inlineStr">
+      <c r="F51" s="43" t="inlineStr">
         <is>
           <t>4 × 1</t>
         </is>
       </c>
-      <c r="G36" s="43" t="inlineStr">
+      <c r="G51" s="43" t="inlineStr">
         <is>
           <t>32×32</t>
         </is>
       </c>
-      <c r="H36" s="43" t="inlineStr">
+      <c r="H51" s="43" t="inlineStr">
         <is>
           <t>Wide landscape image, 1536×1024</t>
         </is>
       </c>
-      <c r="I36" s="43" t="inlineStr"/>
-      <c r="J36" s="43" t="inlineStr">
+      <c r="I51" s="43" t="inlineStr"/>
+      <c r="J51" s="43" t="inlineStr">
         <is>
           <t>Art style: retro 8-bit pixel art, like a Japanese console game from around 1990, set in a 1990s Japanese office. Chunky square pixels with hard edges: no anti-aliasing, no blur, no soft shading, no gradients, no painterly or paper texture. Every character and object has a 1-pixel dark ink outline. Flat colours from one small palette only: ink black, night indigo, slate blue, paper cream, warm grey, vermilion red, deep red, gold, ochre, wood brown, celadon green, moss green, sakura pink, peach. Subtle Japanese touches where they fit (seigaiha wave patterns, shoji paper screens, paper lanterns, hanko stamps, maneki-neko, daruma, bonsai). Satirical anthropomorphic animals. Clean, readable game asset. No text, letters, numbers, watermark, signature or frame.
 Camera: classic Japanese top-down RPG view (three-quarter view from above and in front): you see the top and the front of things; characters show their face when they face down.
@@ -37101,55 +38072,55 @@
 Output: PNG, Wide landscape image, 1536×1024.</t>
         </is>
       </c>
-      <c r="K36" s="45" t="n"/>
-      <c r="L36" s="45" t="inlineStr">
+      <c r="K51" s="45" t="n"/>
+      <c r="L51" s="45" t="inlineStr">
         <is>
           <t>In game</t>
         </is>
       </c>
-      <c r="M36" s="45" t="n"/>
-    </row>
-    <row r="37" ht="230" customHeight="1" s="35">
-      <c r="A37" s="43" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" s="43" t="inlineStr">
+      <c r="M51" s="45" t="n"/>
+    </row>
+    <row r="52" ht="230" customHeight="1" s="35">
+      <c r="A52" s="43" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="43" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C37" s="43" t="inlineStr">
+      <c r="C52" s="43" t="inlineStr">
         <is>
           <t>Colleagues</t>
         </is>
       </c>
-      <c r="D37" s="44" t="inlineStr">
+      <c r="D52" s="44" t="inlineStr">
         <is>
           <t>npc_hobby.png</t>
         </is>
       </c>
-      <c r="E37" s="43" t="inlineStr">
+      <c r="E52" s="43" t="inlineStr">
         <is>
           <t>NPC - energy vampire — Boring-hobby colleague</t>
         </is>
       </c>
-      <c r="F37" s="43" t="inlineStr">
+      <c r="F52" s="43" t="inlineStr">
         <is>
           <t>4 × 1</t>
         </is>
       </c>
-      <c r="G37" s="43" t="inlineStr">
+      <c r="G52" s="43" t="inlineStr">
         <is>
           <t>32×32</t>
         </is>
       </c>
-      <c r="H37" s="43" t="inlineStr">
+      <c r="H52" s="43" t="inlineStr">
         <is>
           <t>Wide landscape image, 1536×1024</t>
         </is>
       </c>
-      <c r="I37" s="43" t="inlineStr"/>
-      <c r="J37" s="43" t="inlineStr">
+      <c r="I52" s="43" t="inlineStr"/>
+      <c r="J52" s="43" t="inlineStr">
         <is>
           <t>Art style: retro 8-bit pixel art, like a Japanese console game from around 1990, set in a 1990s Japanese office. Chunky square pixels with hard edges: no anti-aliasing, no blur, no soft shading, no gradients, no painterly or paper texture. Every character and object has a 1-pixel dark ink outline. Flat colours from one small palette only: ink black, night indigo, slate blue, paper cream, warm grey, vermilion red, deep red, gold, ochre, wood brown, celadon green, moss green, sakura pink, peach. Subtle Japanese touches where they fit (seigaiha wave patterns, shoji paper screens, paper lanterns, hanko stamps, maneki-neko, daruma, bonsai). Satirical anthropomorphic animals. Clean, readable game asset. No text, letters, numbers, watermark, signature or frame.
 Camera: classic Japanese top-down RPG view (three-quarter view from above and in front): you see the top and the front of things; characters show their face when they face down.
@@ -37160,55 +38131,55 @@
 Output: PNG, Wide landscape image, 1536×1024.</t>
         </is>
       </c>
-      <c r="K37" s="45" t="n"/>
-      <c r="L37" s="45" t="inlineStr">
+      <c r="K52" s="45" t="n"/>
+      <c r="L52" s="45" t="inlineStr">
         <is>
           <t>In game</t>
         </is>
       </c>
-      <c r="M37" s="45" t="n"/>
-    </row>
-    <row r="38" ht="230" customHeight="1" s="35">
-      <c r="A38" s="43" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" s="43" t="inlineStr">
+      <c r="M52" s="45" t="n"/>
+    </row>
+    <row r="53" ht="230" customHeight="1" s="35">
+      <c r="A53" s="43" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="43" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C38" s="43" t="inlineStr">
+      <c r="C53" s="43" t="inlineStr">
         <is>
           <t>Colleagues</t>
         </is>
       </c>
-      <c r="D38" s="44" t="inlineStr">
+      <c r="D53" s="44" t="inlineStr">
         <is>
           <t>npc_inspector.png</t>
         </is>
       </c>
-      <c r="E38" s="43" t="inlineStr">
+      <c r="E53" s="43" t="inlineStr">
         <is>
           <t>Intro — metro ticket inspector (kept from the earlier plan)</t>
         </is>
       </c>
-      <c r="F38" s="43" t="inlineStr">
+      <c r="F53" s="43" t="inlineStr">
         <is>
           <t>4 × 1</t>
         </is>
       </c>
-      <c r="G38" s="43" t="inlineStr">
+      <c r="G53" s="43" t="inlineStr">
         <is>
           <t>32×48</t>
         </is>
       </c>
-      <c r="H38" s="43" t="inlineStr">
+      <c r="H53" s="43" t="inlineStr">
         <is>
           <t>Wide landscape image, 1536×1024</t>
         </is>
       </c>
-      <c r="I38" s="43" t="inlineStr"/>
-      <c r="J38" s="43" t="inlineStr">
+      <c r="I53" s="43" t="inlineStr"/>
+      <c r="J53" s="43" t="inlineStr">
         <is>
           <t>Art style: retro 8-bit pixel art, like a Japanese console game from around 1990, set in a 1990s Japanese office. Chunky square pixels with hard edges: no anti-aliasing, no blur, no soft shading, no gradients, no painterly or paper texture. Every character and object has a 1-pixel dark ink outline. Flat colours from one small palette only: ink black, night indigo, slate blue, paper cream, warm grey, vermilion red, deep red, gold, ochre, wood brown, celadon green, moss green, sakura pink, peach. Subtle Japanese touches where they fit (seigaiha wave patterns, shoji paper screens, paper lanterns, hanko stamps, maneki-neko, daruma, bonsai). Satirical anthropomorphic animals. Clean, readable game asset. No text, letters, numbers, watermark, signature or frame.
 Camera: plain side view, like a 2D side-scrolling game; every figure stands on the bottom edge of its cell.
@@ -37219,179 +38190,55 @@
 Output: PNG, Wide landscape image, 1536×1024.</t>
         </is>
       </c>
-      <c r="K38" s="45" t="n"/>
-      <c r="L38" s="45" t="inlineStr">
+      <c r="K53" s="45" t="n"/>
+      <c r="L53" s="45" t="inlineStr">
         <is>
           <t>In game</t>
         </is>
       </c>
-      <c r="M38" s="45" t="n"/>
-    </row>
-    <row r="39" ht="230" customHeight="1" s="35">
-      <c r="A39" s="43" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" s="43" t="inlineStr">
+      <c r="M53" s="45" t="n"/>
+    </row>
+    <row r="54" ht="230" customHeight="1" s="35">
+      <c r="A54" s="43" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="43" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C39" s="43" t="inlineStr">
-        <is>
-          <t>Tiles</t>
-        </is>
-      </c>
-      <c r="D39" s="44" t="inlineStr">
-        <is>
-          <t>tiles_floor.png</t>
-        </is>
-      </c>
-      <c r="E39" s="43" t="inlineStr"/>
-      <c r="F39" s="43" t="inlineStr">
-        <is>
-          <t>4 × 4</t>
-        </is>
-      </c>
-      <c r="G39" s="43" t="inlineStr">
-        <is>
-          <t>16×16</t>
-        </is>
-      </c>
-      <c r="H39" s="43" t="inlineStr">
-        <is>
-          <t>Square image, 1024×1024</t>
-        </is>
-      </c>
-      <c r="I39" s="43" t="inlineStr">
+      <c r="C54" s="43" t="inlineStr">
+        <is>
+          <t>Office props</t>
+        </is>
+      </c>
+      <c r="D54" s="44" t="inlineStr">
+        <is>
+          <t>props_cubicles_a.png</t>
+        </is>
+      </c>
+      <c r="E54" s="43" t="inlineStr"/>
+      <c r="F54" s="43" t="inlineStr">
+        <is>
+          <t>3 × 2</t>
+        </is>
+      </c>
+      <c r="G54" s="43" t="inlineStr">
+        <is>
+          <t>48×48</t>
+        </is>
+      </c>
+      <c r="H54" s="43" t="inlineStr">
+        <is>
+          <t>Wide landscape image, 1536×1024</t>
+        </is>
+      </c>
+      <c r="I54" s="43" t="inlineStr">
         <is>
           <t>Do all sheets of this group in the same ChatGPT chat.</t>
         </is>
       </c>
-      <c r="J39" s="43" t="inlineStr">
-        <is>
-          <t>Art style: retro 8-bit pixel art, like a Japanese console game from around 1990, set in a 1990s Japanese office. Chunky square pixels with hard edges: no anti-aliasing, no blur, no soft shading, no gradients, no painterly or paper texture. Every character and object has a 1-pixel dark ink outline. Flat colours from one small palette only: ink black, night indigo, slate blue, paper cream, warm grey, vermilion red, deep red, gold, ochre, wood brown, celadon green, moss green, sakura pink, peach. Subtle Japanese touches where they fit (seigaiha wave patterns, shoji paper screens, paper lanterns, hanko stamps, maneki-neko, daruma, bonsai). Satirical anthropomorphic animals. Clean, readable game asset. No text, letters, numbers, watermark, signature or frame.
-Camera: seen from directly above, completely flat.
-Subject: Floor tiles for the different zones of a 1990s Japanese office.
-Layout: a sprite sheet on a solid flat magenta background (#FF00FF, one single pure colour, no shading, no checkerboard). An evenly spaced grid of 4 columns and 4 rows of equal-sized cells with wide plain magenta gaps between the cells. Each cell is one square FLOOR TILE drawn at 16×16 pixel-art resolution (each pixel a big visible block), filling its whole cell, seen from directly above, and tiling seamlessly with itself (left edge continues into right, top into bottom). Tiles in the same row belong together and must also fit next to each other. Low contrast so characters stand out. No grid lines, borders, labels or numbers. Never use magenta or purple on the subjects themselves.
-Cells, left to right, top to bottom:
-- Row 1: open-plan office carpet, muted celadon green: plain | small seigaiha wave pattern | worn spot | coffee stain
-- Row 2: manager's corner tatami mats: plain tatami | tatami with dark border | tatami turned 90° | tatami with a cushion mark
-- Row 3: kitchen floor: cream-and-indigo checker tiles | plain cream tiles | wet spot | crumbs
-- Row 4: archive and server room: grey metal raised floor panel | grey concrete | floor cable cover | indigo rug with gold border
-Output: PNG, Square image, 1024×1024.</t>
-        </is>
-      </c>
-      <c r="K39" s="45" t="n"/>
-      <c r="L39" s="45" t="inlineStr">
-        <is>
-          <t>In game</t>
-        </is>
-      </c>
-      <c r="M39" s="45" t="n"/>
-    </row>
-    <row r="40" ht="230" customHeight="1" s="35">
-      <c r="A40" s="43" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" s="43" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C40" s="43" t="inlineStr">
-        <is>
-          <t>Tiles</t>
-        </is>
-      </c>
-      <c r="D40" s="44" t="inlineStr">
-        <is>
-          <t>tiles_wall.png</t>
-        </is>
-      </c>
-      <c r="E40" s="43" t="inlineStr"/>
-      <c r="F40" s="43" t="inlineStr">
-        <is>
-          <t>4 × 4</t>
-        </is>
-      </c>
-      <c r="G40" s="43" t="inlineStr">
-        <is>
-          <t>16×16</t>
-        </is>
-      </c>
-      <c r="H40" s="43" t="inlineStr">
-        <is>
-          <t>Square image, 1024×1024</t>
-        </is>
-      </c>
-      <c r="I40" s="43" t="inlineStr">
-        <is>
-          <t>Do all sheets of this group in the same ChatGPT chat.</t>
-        </is>
-      </c>
-      <c r="J40" s="43" t="inlineStr">
-        <is>
-          <t>Art style: retro 8-bit pixel art, like a Japanese console game from around 1990, set in a 1990s Japanese office. Chunky square pixels with hard edges: no anti-aliasing, no blur, no soft shading, no gradients, no painterly or paper texture. Every character and object has a 1-pixel dark ink outline. Flat colours from one small palette only: ink black, night indigo, slate blue, paper cream, warm grey, vermilion red, deep red, gold, ochre, wood brown, celadon green, moss green, sakura pink, peach. Subtle Japanese touches where they fit (seigaiha wave patterns, shoji paper screens, paper lanterns, hanko stamps, maneki-neko, daruma, bonsai). Satirical anthropomorphic animals. Clean, readable game asset. No text, letters, numbers, watermark, signature or frame.
-Camera: classic Japanese top-down RPG view (three-quarter view from above and in front): you see the top and the front of things; characters show their face when they face down.
-Subject: Wall and partition tiles for a 1990s Japanese office.
-Layout: a sprite sheet on a solid flat magenta background (#FF00FF, one single pure colour, no shading, no checkerboard). An evenly spaced grid of 4 columns and 4 rows of equal-sized cells with wide plain magenta gaps between the cells. Each cell is one square WALL or PARTITION tile drawn at 16×16 pixel-art resolution (each pixel a big visible block), filling its whole cell, in the three-quarter top-down view. Neighbouring wall tiles must line up edge to edge. No grid lines, borders, labels or numbers. Never use magenta or purple on the subjects themselves.
-Cells, left to right, top to bottom:
-- Row 1: wall faces: plain cream wall | wall with a night-sky window | wall with a dawn window | wall with a hanging ink-painting scroll (mountains, no writing)
-- Row 2: wall faces: closed wooden door | doorway with an indigo noren curtain | shoji paper screen | cork notice board with pinned papers (no readable text)
-- Row 3: grey fabric cubicle partition: horizontal piece | vertical piece | corner piece | end piece
-- Row 4: wall tops: wall top cap (seen from above) | top inner corner | top outer corner | square pillar
-Output: PNG, Square image, 1024×1024.</t>
-        </is>
-      </c>
-      <c r="K40" s="45" t="n"/>
-      <c r="L40" s="45" t="inlineStr">
-        <is>
-          <t>In game</t>
-        </is>
-      </c>
-      <c r="M40" s="45" t="n"/>
-    </row>
-    <row r="41" ht="230" customHeight="1" s="35">
-      <c r="A41" s="43" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" s="43" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C41" s="43" t="inlineStr">
-        <is>
-          <t>Office props</t>
-        </is>
-      </c>
-      <c r="D41" s="44" t="inlineStr">
-        <is>
-          <t>props_cubicles_a.png</t>
-        </is>
-      </c>
-      <c r="E41" s="43" t="inlineStr"/>
-      <c r="F41" s="43" t="inlineStr">
-        <is>
-          <t>3 × 2</t>
-        </is>
-      </c>
-      <c r="G41" s="43" t="inlineStr">
-        <is>
-          <t>48×48</t>
-        </is>
-      </c>
-      <c r="H41" s="43" t="inlineStr">
-        <is>
-          <t>Wide landscape image, 1536×1024</t>
-        </is>
-      </c>
-      <c r="I41" s="43" t="inlineStr">
-        <is>
-          <t>Do all sheets of this group in the same ChatGPT chat.</t>
-        </is>
-      </c>
-      <c r="J41" s="43" t="inlineStr">
+      <c r="J54" s="43" t="inlineStr">
         <is>
           <t>Art style: retro 8-bit pixel art, like a Japanese console game from around 1990, set in a 1990s Japanese office. Chunky square pixels with hard edges: no anti-aliasing, no blur, no soft shading, no gradients, no painterly or paper texture. Every character and object has a 1-pixel dark ink outline. Flat colours from one small palette only: ink black, night indigo, slate blue, paper cream, warm grey, vermilion red, deep red, gold, ochre, wood brown, celadon green, moss green, sakura pink, peach. Subtle Japanese touches where they fit (seigaiha wave patterns, shoji paper screens, paper lanterns, hanko stamps, maneki-neko, daruma, bonsai). Satirical anthropomorphic animals. Clean, readable game asset. No text, letters, numbers, watermark, signature or frame.
 Camera: classic Japanese top-down RPG view (three-quarter view from above and in front): you see the top and the front of things; characters show their face when they face down.
@@ -37403,55 +38250,55 @@
 Output: PNG, Wide landscape image, 1536×1024.</t>
         </is>
       </c>
-      <c r="K41" s="45" t="n"/>
-      <c r="L41" s="45" t="inlineStr">
+      <c r="K54" s="45" t="n"/>
+      <c r="L54" s="45" t="inlineStr">
         <is>
           <t>In game</t>
         </is>
       </c>
-      <c r="M41" s="45" t="n"/>
-    </row>
-    <row r="42" ht="230" customHeight="1" s="35">
-      <c r="A42" s="43" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" s="43" t="inlineStr">
+      <c r="M54" s="45" t="n"/>
+    </row>
+    <row r="55" ht="230" customHeight="1" s="35">
+      <c r="A55" s="43" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="43" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C42" s="43" t="inlineStr">
+      <c r="C55" s="43" t="inlineStr">
         <is>
           <t>Office props</t>
         </is>
       </c>
-      <c r="D42" s="44" t="inlineStr">
+      <c r="D55" s="44" t="inlineStr">
         <is>
           <t>props_cubicles_b.png</t>
         </is>
       </c>
-      <c r="E42" s="43" t="inlineStr"/>
-      <c r="F42" s="43" t="inlineStr">
+      <c r="E55" s="43" t="inlineStr"/>
+      <c r="F55" s="43" t="inlineStr">
         <is>
           <t>3 × 2</t>
         </is>
       </c>
-      <c r="G42" s="43" t="inlineStr">
+      <c r="G55" s="43" t="inlineStr">
         <is>
           <t>48×48</t>
         </is>
       </c>
-      <c r="H42" s="43" t="inlineStr">
+      <c r="H55" s="43" t="inlineStr">
         <is>
           <t>Wide landscape image, 1536×1024</t>
         </is>
       </c>
-      <c r="I42" s="43" t="inlineStr">
+      <c r="I55" s="43" t="inlineStr">
         <is>
           <t>Do all sheets of this group in the same ChatGPT chat.</t>
         </is>
       </c>
-      <c r="J42" s="43" t="inlineStr">
+      <c r="J55" s="43" t="inlineStr">
         <is>
           <t>Art style: retro 8-bit pixel art, like a Japanese console game from around 1990, set in a 1990s Japanese office. Chunky square pixels with hard edges: no anti-aliasing, no blur, no soft shading, no gradients, no painterly or paper texture. Every character and object has a 1-pixel dark ink outline. Flat colours from one small palette only: ink black, night indigo, slate blue, paper cream, warm grey, vermilion red, deep red, gold, ochre, wood brown, celadon green, moss green, sakura pink, peach. Subtle Japanese touches where they fit (seigaiha wave patterns, shoji paper screens, paper lanterns, hanko stamps, maneki-neko, daruma, bonsai). Satirical anthropomorphic animals. Clean, readable game asset. No text, letters, numbers, watermark, signature or frame.
 Camera: classic Japanese top-down RPG view (three-quarter view from above and in front): you see the top and the front of things; characters show their face when they face down.
@@ -37463,55 +38310,55 @@
 Output: PNG, Wide landscape image, 1536×1024.</t>
         </is>
       </c>
-      <c r="K42" s="45" t="n"/>
-      <c r="L42" s="45" t="inlineStr">
+      <c r="K55" s="45" t="n"/>
+      <c r="L55" s="45" t="inlineStr">
         <is>
           <t>In game</t>
         </is>
       </c>
-      <c r="M42" s="45" t="n"/>
-    </row>
-    <row r="43" ht="230" customHeight="1" s="35">
-      <c r="A43" s="43" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" s="43" t="inlineStr">
+      <c r="M55" s="45" t="n"/>
+    </row>
+    <row r="56" ht="230" customHeight="1" s="35">
+      <c r="A56" s="43" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="43" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C43" s="43" t="inlineStr">
+      <c r="C56" s="43" t="inlineStr">
         <is>
           <t>Office props</t>
         </is>
       </c>
-      <c r="D43" s="44" t="inlineStr">
+      <c r="D56" s="44" t="inlineStr">
         <is>
           <t>props_manager.png</t>
         </is>
       </c>
-      <c r="E43" s="43" t="inlineStr"/>
-      <c r="F43" s="43" t="inlineStr">
+      <c r="E56" s="43" t="inlineStr"/>
+      <c r="F56" s="43" t="inlineStr">
         <is>
           <t>3 × 2</t>
         </is>
       </c>
-      <c r="G43" s="43" t="inlineStr">
+      <c r="G56" s="43" t="inlineStr">
         <is>
           <t>48×48</t>
         </is>
       </c>
-      <c r="H43" s="43" t="inlineStr">
+      <c r="H56" s="43" t="inlineStr">
         <is>
           <t>Wide landscape image, 1536×1024</t>
         </is>
       </c>
-      <c r="I43" s="43" t="inlineStr">
+      <c r="I56" s="43" t="inlineStr">
         <is>
           <t>Do all sheets of this group in the same ChatGPT chat.</t>
         </is>
       </c>
-      <c r="J43" s="43" t="inlineStr">
+      <c r="J56" s="43" t="inlineStr">
         <is>
           <t>Art style: retro 8-bit pixel art, like a Japanese console game from around 1990, set in a 1990s Japanese office. Chunky square pixels with hard edges: no anti-aliasing, no blur, no soft shading, no gradients, no painterly or paper texture. Every character and object has a 1-pixel dark ink outline. Flat colours from one small palette only: ink black, night indigo, slate blue, paper cream, warm grey, vermilion red, deep red, gold, ochre, wood brown, celadon green, moss green, sakura pink, peach. Subtle Japanese touches where they fit (seigaiha wave patterns, shoji paper screens, paper lanterns, hanko stamps, maneki-neko, daruma, bonsai). Satirical anthropomorphic animals. Clean, readable game asset. No text, letters, numbers, watermark, signature or frame.
 Camera: classic Japanese top-down RPG view (three-quarter view from above and in front): you see the top and the front of things; characters show their face when they face down.
@@ -37523,55 +38370,55 @@
 Output: PNG, Wide landscape image, 1536×1024.</t>
         </is>
       </c>
-      <c r="K43" s="45" t="n"/>
-      <c r="L43" s="45" t="inlineStr">
+      <c r="K56" s="45" t="n"/>
+      <c r="L56" s="45" t="inlineStr">
         <is>
           <t>In game</t>
         </is>
       </c>
-      <c r="M43" s="45" t="n"/>
-    </row>
-    <row r="44" ht="230" customHeight="1" s="35">
-      <c r="A44" s="43" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" s="43" t="inlineStr">
+      <c r="M56" s="45" t="n"/>
+    </row>
+    <row r="57" ht="230" customHeight="1" s="35">
+      <c r="A57" s="43" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="43" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C44" s="43" t="inlineStr">
+      <c r="C57" s="43" t="inlineStr">
         <is>
           <t>Office props</t>
         </is>
       </c>
-      <c r="D44" s="44" t="inlineStr">
+      <c r="D57" s="44" t="inlineStr">
         <is>
           <t>props_kitchen.png</t>
         </is>
       </c>
-      <c r="E44" s="43" t="inlineStr"/>
-      <c r="F44" s="43" t="inlineStr">
+      <c r="E57" s="43" t="inlineStr"/>
+      <c r="F57" s="43" t="inlineStr">
         <is>
           <t>3 × 2</t>
         </is>
       </c>
-      <c r="G44" s="43" t="inlineStr">
+      <c r="G57" s="43" t="inlineStr">
         <is>
           <t>48×48</t>
         </is>
       </c>
-      <c r="H44" s="43" t="inlineStr">
+      <c r="H57" s="43" t="inlineStr">
         <is>
           <t>Wide landscape image, 1536×1024</t>
         </is>
       </c>
-      <c r="I44" s="43" t="inlineStr">
+      <c r="I57" s="43" t="inlineStr">
         <is>
           <t>Do all sheets of this group in the same ChatGPT chat.</t>
         </is>
       </c>
-      <c r="J44" s="43" t="inlineStr">
+      <c r="J57" s="43" t="inlineStr">
         <is>
           <t>Art style: retro 8-bit pixel art, like a Japanese console game from around 1990, set in a 1990s Japanese office. Chunky square pixels with hard edges: no anti-aliasing, no blur, no soft shading, no gradients, no painterly or paper texture. Every character and object has a 1-pixel dark ink outline. Flat colours from one small palette only: ink black, night indigo, slate blue, paper cream, warm grey, vermilion red, deep red, gold, ochre, wood brown, celadon green, moss green, sakura pink, peach. Subtle Japanese touches where they fit (seigaiha wave patterns, shoji paper screens, paper lanterns, hanko stamps, maneki-neko, daruma, bonsai). Satirical anthropomorphic animals. Clean, readable game asset. No text, letters, numbers, watermark, signature or frame.
 Camera: classic Japanese top-down RPG view (three-quarter view from above and in front): you see the top and the front of things; characters show their face when they face down.
@@ -37583,55 +38430,55 @@
 Output: PNG, Wide landscape image, 1536×1024.</t>
         </is>
       </c>
-      <c r="K44" s="45" t="n"/>
-      <c r="L44" s="45" t="inlineStr">
+      <c r="K57" s="45" t="n"/>
+      <c r="L57" s="45" t="inlineStr">
         <is>
           <t>In game</t>
         </is>
       </c>
-      <c r="M44" s="45" t="n"/>
-    </row>
-    <row r="45" ht="230" customHeight="1" s="35">
-      <c r="A45" s="43" t="n">
-        <v>44</v>
-      </c>
-      <c r="B45" s="43" t="inlineStr">
+      <c r="M57" s="45" t="n"/>
+    </row>
+    <row r="58" ht="230" customHeight="1" s="35">
+      <c r="A58" s="43" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="43" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C45" s="43" t="inlineStr">
+      <c r="C58" s="43" t="inlineStr">
         <is>
           <t>Office props</t>
         </is>
       </c>
-      <c r="D45" s="44" t="inlineStr">
+      <c r="D58" s="44" t="inlineStr">
         <is>
           <t>props_archive.png</t>
         </is>
       </c>
-      <c r="E45" s="43" t="inlineStr"/>
-      <c r="F45" s="43" t="inlineStr">
+      <c r="E58" s="43" t="inlineStr"/>
+      <c r="F58" s="43" t="inlineStr">
         <is>
           <t>3 × 2</t>
         </is>
       </c>
-      <c r="G45" s="43" t="inlineStr">
+      <c r="G58" s="43" t="inlineStr">
         <is>
           <t>48×48</t>
         </is>
       </c>
-      <c r="H45" s="43" t="inlineStr">
+      <c r="H58" s="43" t="inlineStr">
         <is>
           <t>Wide landscape image, 1536×1024</t>
         </is>
       </c>
-      <c r="I45" s="43" t="inlineStr">
+      <c r="I58" s="43" t="inlineStr">
         <is>
           <t>Do all sheets of this group in the same ChatGPT chat.</t>
         </is>
       </c>
-      <c r="J45" s="43" t="inlineStr">
+      <c r="J58" s="43" t="inlineStr">
         <is>
           <t>Art style: retro 8-bit pixel art, like a Japanese console game from around 1990, set in a 1990s Japanese office. Chunky square pixels with hard edges: no anti-aliasing, no blur, no soft shading, no gradients, no painterly or paper texture. Every character and object has a 1-pixel dark ink outline. Flat colours from one small palette only: ink black, night indigo, slate blue, paper cream, warm grey, vermilion red, deep red, gold, ochre, wood brown, celadon green, moss green, sakura pink, peach. Subtle Japanese touches where they fit (seigaiha wave patterns, shoji paper screens, paper lanterns, hanko stamps, maneki-neko, daruma, bonsai). Satirical anthropomorphic animals. Clean, readable game asset. No text, letters, numbers, watermark, signature or frame.
 Camera: classic Japanese top-down RPG view (three-quarter view from above and in front): you see the top and the front of things; characters show their face when they face down.
@@ -37643,55 +38490,55 @@
 Output: PNG, Wide landscape image, 1536×1024.</t>
         </is>
       </c>
-      <c r="K45" s="45" t="n"/>
-      <c r="L45" s="45" t="inlineStr">
+      <c r="K58" s="45" t="n"/>
+      <c r="L58" s="45" t="inlineStr">
         <is>
           <t>In game</t>
         </is>
       </c>
-      <c r="M45" s="45" t="n"/>
-    </row>
-    <row r="46" ht="230" customHeight="1" s="35">
-      <c r="A46" s="43" t="n">
-        <v>45</v>
-      </c>
-      <c r="B46" s="43" t="inlineStr">
+      <c r="M58" s="45" t="n"/>
+    </row>
+    <row r="59" ht="230" customHeight="1" s="35">
+      <c r="A59" s="43" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="43" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C46" s="43" t="inlineStr">
+      <c r="C59" s="43" t="inlineStr">
         <is>
           <t>Office props</t>
         </is>
       </c>
-      <c r="D46" s="44" t="inlineStr">
+      <c r="D59" s="44" t="inlineStr">
         <is>
           <t>props_meeting.png</t>
         </is>
       </c>
-      <c r="E46" s="43" t="inlineStr"/>
-      <c r="F46" s="43" t="inlineStr">
+      <c r="E59" s="43" t="inlineStr"/>
+      <c r="F59" s="43" t="inlineStr">
         <is>
           <t>3 × 2</t>
         </is>
       </c>
-      <c r="G46" s="43" t="inlineStr">
+      <c r="G59" s="43" t="inlineStr">
         <is>
           <t>48×48</t>
         </is>
       </c>
-      <c r="H46" s="43" t="inlineStr">
+      <c r="H59" s="43" t="inlineStr">
         <is>
           <t>Wide landscape image, 1536×1024</t>
         </is>
       </c>
-      <c r="I46" s="43" t="inlineStr">
+      <c r="I59" s="43" t="inlineStr">
         <is>
           <t>Do all sheets of this group in the same ChatGPT chat.</t>
         </is>
       </c>
-      <c r="J46" s="43" t="inlineStr">
+      <c r="J59" s="43" t="inlineStr">
         <is>
           <t>Art style: retro 8-bit pixel art, like a Japanese console game from around 1990, set in a 1990s Japanese office. Chunky square pixels with hard edges: no anti-aliasing, no blur, no soft shading, no gradients, no painterly or paper texture. Every character and object has a 1-pixel dark ink outline. Flat colours from one small palette only: ink black, night indigo, slate blue, paper cream, warm grey, vermilion red, deep red, gold, ochre, wood brown, celadon green, moss green, sakura pink, peach. Subtle Japanese touches where they fit (seigaiha wave patterns, shoji paper screens, paper lanterns, hanko stamps, maneki-neko, daruma, bonsai). Satirical anthropomorphic animals. Clean, readable game asset. No text, letters, numbers, watermark, signature or frame.
 Camera: classic Japanese top-down RPG view (three-quarter view from above and in front): you see the top and the front of things; characters show their face when they face down.
@@ -37703,55 +38550,55 @@
 Output: PNG, Wide landscape image, 1536×1024.</t>
         </is>
       </c>
-      <c r="K46" s="45" t="n"/>
-      <c r="L46" s="45" t="inlineStr">
+      <c r="K59" s="45" t="n"/>
+      <c r="L59" s="45" t="inlineStr">
         <is>
           <t>In game</t>
         </is>
       </c>
-      <c r="M46" s="45" t="n"/>
-    </row>
-    <row r="47" ht="230" customHeight="1" s="35">
-      <c r="A47" s="43" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" s="43" t="inlineStr">
+      <c r="M59" s="45" t="n"/>
+    </row>
+    <row r="60" ht="230" customHeight="1" s="35">
+      <c r="A60" s="43" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="43" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C47" s="43" t="inlineStr">
+      <c r="C60" s="43" t="inlineStr">
         <is>
           <t>Office props</t>
         </is>
       </c>
-      <c r="D47" s="44" t="inlineStr">
+      <c r="D60" s="44" t="inlineStr">
         <is>
           <t>props_server.png</t>
         </is>
       </c>
-      <c r="E47" s="43" t="inlineStr"/>
-      <c r="F47" s="43" t="inlineStr">
+      <c r="E60" s="43" t="inlineStr"/>
+      <c r="F60" s="43" t="inlineStr">
         <is>
           <t>3 × 2</t>
         </is>
       </c>
-      <c r="G47" s="43" t="inlineStr">
+      <c r="G60" s="43" t="inlineStr">
         <is>
           <t>48×48</t>
         </is>
       </c>
-      <c r="H47" s="43" t="inlineStr">
+      <c r="H60" s="43" t="inlineStr">
         <is>
           <t>Wide landscape image, 1536×1024</t>
         </is>
       </c>
-      <c r="I47" s="43" t="inlineStr">
+      <c r="I60" s="43" t="inlineStr">
         <is>
           <t>Do all sheets of this group in the same ChatGPT chat.</t>
         </is>
       </c>
-      <c r="J47" s="43" t="inlineStr">
+      <c r="J60" s="43" t="inlineStr">
         <is>
           <t>Art style: retro 8-bit pixel art, like a Japanese console game from around 1990, set in a 1990s Japanese office. Chunky square pixels with hard edges: no anti-aliasing, no blur, no soft shading, no gradients, no painterly or paper texture. Every character and object has a 1-pixel dark ink outline. Flat colours from one small palette only: ink black, night indigo, slate blue, paper cream, warm grey, vermilion red, deep red, gold, ochre, wood brown, celadon green, moss green, sakura pink, peach. Subtle Japanese touches where they fit (seigaiha wave patterns, shoji paper screens, paper lanterns, hanko stamps, maneki-neko, daruma, bonsai). Satirical anthropomorphic animals. Clean, readable game asset. No text, letters, numbers, watermark, signature or frame.
 Camera: classic Japanese top-down RPG view (three-quarter view from above and in front): you see the top and the front of things; characters show their face when they face down.
@@ -37763,55 +38610,55 @@
 Output: PNG, Wide landscape image, 1536×1024.</t>
         </is>
       </c>
-      <c r="K47" s="45" t="n"/>
-      <c r="L47" s="45" t="inlineStr">
+      <c r="K60" s="45" t="n"/>
+      <c r="L60" s="45" t="inlineStr">
         <is>
           <t>In game</t>
         </is>
       </c>
-      <c r="M47" s="45" t="n"/>
-    </row>
-    <row r="48" ht="230" customHeight="1" s="35">
-      <c r="A48" s="43" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" s="43" t="inlineStr">
+      <c r="M60" s="45" t="n"/>
+    </row>
+    <row r="61" ht="230" customHeight="1" s="35">
+      <c r="A61" s="43" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="43" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C48" s="43" t="inlineStr">
+      <c r="C61" s="43" t="inlineStr">
         <is>
           <t>Office props</t>
         </is>
       </c>
-      <c r="D48" s="44" t="inlineStr">
+      <c r="D61" s="44" t="inlineStr">
         <is>
           <t>props_misc.png</t>
         </is>
       </c>
-      <c r="E48" s="43" t="inlineStr"/>
-      <c r="F48" s="43" t="inlineStr">
+      <c r="E61" s="43" t="inlineStr"/>
+      <c r="F61" s="43" t="inlineStr">
         <is>
           <t>3 × 2</t>
         </is>
       </c>
-      <c r="G48" s="43" t="inlineStr">
+      <c r="G61" s="43" t="inlineStr">
         <is>
           <t>48×48</t>
         </is>
       </c>
-      <c r="H48" s="43" t="inlineStr">
+      <c r="H61" s="43" t="inlineStr">
         <is>
           <t>Wide landscape image, 1536×1024</t>
         </is>
       </c>
-      <c r="I48" s="43" t="inlineStr">
+      <c r="I61" s="43" t="inlineStr">
         <is>
           <t>Do all sheets of this group in the same ChatGPT chat.</t>
         </is>
       </c>
-      <c r="J48" s="43" t="inlineStr">
+      <c r="J61" s="43" t="inlineStr">
         <is>
           <t>Art style: retro 8-bit pixel art, like a Japanese console game from around 1990, set in a 1990s Japanese office. Chunky square pixels with hard edges: no anti-aliasing, no blur, no soft shading, no gradients, no painterly or paper texture. Every character and object has a 1-pixel dark ink outline. Flat colours from one small palette only: ink black, night indigo, slate blue, paper cream, warm grey, vermilion red, deep red, gold, ochre, wood brown, celadon green, moss green, sakura pink, peach. Subtle Japanese touches where they fit (seigaiha wave patterns, shoji paper screens, paper lanterns, hanko stamps, maneki-neko, daruma, bonsai). Satirical anthropomorphic animals. Clean, readable game asset. No text, letters, numbers, watermark, signature or frame.
 Camera: classic Japanese top-down RPG view (three-quarter view from above and in front): you see the top and the front of things; characters show their face when they face down.
@@ -37823,51 +38670,51 @@
 Output: PNG, Wide landscape image, 1536×1024.</t>
         </is>
       </c>
-      <c r="K48" s="45" t="n"/>
-      <c r="L48" s="45" t="inlineStr">
+      <c r="K61" s="45" t="n"/>
+      <c r="L61" s="45" t="inlineStr">
         <is>
           <t>In game</t>
         </is>
       </c>
-      <c r="M48" s="45" t="n"/>
-    </row>
-    <row r="49" ht="230" customHeight="1" s="35">
-      <c r="A49" s="43" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" s="43" t="inlineStr">
+      <c r="M61" s="45" t="n"/>
+    </row>
+    <row r="62" ht="230" customHeight="1" s="35">
+      <c r="A62" s="43" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="43" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C49" s="43" t="inlineStr">
+      <c r="C62" s="43" t="inlineStr">
         <is>
           <t>Pickups, projectiles and effects</t>
         </is>
       </c>
-      <c r="D49" s="44" t="inlineStr">
+      <c r="D62" s="44" t="inlineStr">
         <is>
           <t>fx_items.png</t>
         </is>
       </c>
-      <c r="E49" s="43" t="inlineStr"/>
-      <c r="F49" s="43" t="inlineStr">
+      <c r="E62" s="43" t="inlineStr"/>
+      <c r="F62" s="43" t="inlineStr">
         <is>
           <t>4 × 2</t>
         </is>
       </c>
-      <c r="G49" s="43" t="inlineStr">
+      <c r="G62" s="43" t="inlineStr">
         <is>
           <t>16×16</t>
         </is>
       </c>
-      <c r="H49" s="43" t="inlineStr">
+      <c r="H62" s="43" t="inlineStr">
         <is>
           <t>Wide landscape image, 1536×1024</t>
         </is>
       </c>
-      <c r="I49" s="43" t="inlineStr"/>
-      <c r="J49" s="43" t="inlineStr">
+      <c r="I62" s="43" t="inlineStr"/>
+      <c r="J62" s="43" t="inlineStr">
         <is>
           <t>Art style: retro 8-bit pixel art, like a Japanese console game from around 1990, set in a 1990s Japanese office. Chunky square pixels with hard edges: no anti-aliasing, no blur, no soft shading, no gradients, no painterly or paper texture. Every character and object has a 1-pixel dark ink outline. Flat colours from one small palette only: ink black, night indigo, slate blue, paper cream, warm grey, vermilion red, deep red, gold, ochre, wood brown, celadon green, moss green, sakura pink, peach. Subtle Japanese touches where they fit (seigaiha wave patterns, shoji paper screens, paper lanterns, hanko stamps, maneki-neko, daruma, bonsai). Satirical anthropomorphic animals. Clean, readable game asset. No text, letters, numbers, watermark, signature or frame.
 Camera: seen from directly above, completely flat.
@@ -37879,59 +38726,59 @@
 Output: PNG, Wide landscape image, 1536×1024.</t>
         </is>
       </c>
-      <c r="K49" s="45" t="n"/>
-      <c r="L49" s="45" t="inlineStr">
+      <c r="K62" s="45" t="n"/>
+      <c r="L62" s="45" t="inlineStr">
         <is>
           <t>In game</t>
         </is>
       </c>
-      <c r="M49" s="45" t="n"/>
-    </row>
-    <row r="50" ht="230" customHeight="1" s="35">
-      <c r="A50" s="43" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" s="43" t="inlineStr">
+      <c r="M62" s="45" t="n"/>
+    </row>
+    <row r="63" ht="230" customHeight="1" s="35">
+      <c r="A63" s="43" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="43" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C50" s="43" t="inlineStr">
+      <c r="C63" s="43" t="inlineStr">
         <is>
           <t>Metro station</t>
         </is>
       </c>
-      <c r="D50" s="44" t="inlineStr">
+      <c r="D63" s="44" t="inlineStr">
         <is>
           <t>metro_back.png</t>
         </is>
       </c>
-      <c r="E50" s="43" t="inlineStr">
+      <c r="E63" s="43" t="inlineStr">
         <is>
           <t>Metro — back layer</t>
         </is>
       </c>
-      <c r="F50" s="43" t="inlineStr">
+      <c r="F63" s="43" t="inlineStr">
         <is>
           <t>full scene</t>
         </is>
       </c>
-      <c r="G50" s="43" t="inlineStr">
+      <c r="G63" s="43" t="inlineStr">
         <is>
           <t>320×180</t>
         </is>
       </c>
-      <c r="H50" s="43" t="inlineStr">
+      <c r="H63" s="43" t="inlineStr">
         <is>
           <t>Wide landscape image, 1536×1024</t>
         </is>
       </c>
-      <c r="I50" s="43" t="inlineStr">
+      <c r="I63" s="43" t="inlineStr">
         <is>
           <t>Back layer: the train drives in front of it.</t>
         </is>
       </c>
-      <c r="J50" s="43" t="inlineStr">
+      <c r="J63" s="43" t="inlineStr">
         <is>
           <t>Art style: retro 8-bit pixel art, like a Japanese console game from around 1990, set in a 1990s Japanese office. Chunky square pixels with hard edges: no anti-aliasing, no blur, no soft shading, no gradients, no painterly or paper texture. Every character and object has a 1-pixel dark ink outline. Flat colours from one small palette only: ink black, night indigo, slate blue, paper cream, warm grey, vermilion red, deep red, gold, ochre, wood brown, celadon green, moss green, sakura pink, peach. Subtle Japanese touches where they fit (seigaiha wave patterns, shoji paper screens, paper lanterns, hanko stamps, maneki-neko, daruma, bonsai). Satirical anthropomorphic animals. Clean, readable game asset. No text, letters, numbers, watermark, signature or frame.
 Camera: plain side view of a 2D side-scrolling game stage, horizon level, no characters in the scene.
@@ -37941,59 +38788,59 @@
 Output: the scene fills the whole image edge to edge, no border, no vignette, no text. Wide landscape image, 1536×1024 (it will be cropped to 16:9, so keep important things away from the top and bottom edges).</t>
         </is>
       </c>
-      <c r="K50" s="45" t="n"/>
-      <c r="L50" s="45" t="inlineStr">
+      <c r="K63" s="45" t="n"/>
+      <c r="L63" s="45" t="inlineStr">
         <is>
           <t>In game</t>
         </is>
       </c>
-      <c r="M50" s="45" t="n"/>
-    </row>
-    <row r="51" ht="230" customHeight="1" s="35">
-      <c r="A51" s="43" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" s="43" t="inlineStr">
+      <c r="M63" s="45" t="n"/>
+    </row>
+    <row r="64" ht="230" customHeight="1" s="35">
+      <c r="A64" s="43" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="43" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C51" s="43" t="inlineStr">
+      <c r="C64" s="43" t="inlineStr">
         <is>
           <t>Metro station</t>
         </is>
       </c>
-      <c r="D51" s="44" t="inlineStr">
+      <c r="D64" s="44" t="inlineStr">
         <is>
           <t>metro_platform.png</t>
         </is>
       </c>
-      <c r="E51" s="43" t="inlineStr">
+      <c r="E64" s="43" t="inlineStr">
         <is>
           <t>Metro — platform front layer</t>
         </is>
       </c>
-      <c r="F51" s="43" t="inlineStr">
+      <c r="F64" s="43" t="inlineStr">
         <is>
           <t>full scene</t>
         </is>
       </c>
-      <c r="G51" s="43" t="inlineStr">
+      <c r="G64" s="43" t="inlineStr">
         <is>
           <t>320×180</t>
         </is>
       </c>
-      <c r="H51" s="43" t="inlineStr">
+      <c r="H64" s="43" t="inlineStr">
         <is>
           <t>Wide landscape image, 1536×1024</t>
         </is>
       </c>
-      <c r="I51" s="43" t="inlineStr">
+      <c r="I64" s="43" t="inlineStr">
         <is>
           <t>Front layer: pillars and platform go in front of the train. Magenta = see-through.</t>
         </is>
       </c>
-      <c r="J51" s="43" t="inlineStr">
+      <c r="J64" s="43" t="inlineStr">
         <is>
           <t>Art style: retro 8-bit pixel art, like a Japanese console game from around 1990, set in a 1990s Japanese office. Chunky square pixels with hard edges: no anti-aliasing, no blur, no soft shading, no gradients, no painterly or paper texture. Every character and object has a 1-pixel dark ink outline. Flat colours from one small palette only: ink black, night indigo, slate blue, paper cream, warm grey, vermilion red, deep red, gold, ochre, wood brown, celadon green, moss green, sakura pink, peach. Subtle Japanese touches where they fit (seigaiha wave patterns, shoji paper screens, paper lanterns, hanko stamps, maneki-neko, daruma, bonsai). Satirical anthropomorphic animals. Clean, readable game asset. No text, letters, numbers, watermark, signature or frame.
 Camera: plain side view of a 2D side-scrolling game stage, horizon level, no characters in the scene.
@@ -38003,59 +38850,59 @@
 Output: PNG, Wide landscape image, 1536×1024 (it will be cropped to 16:9, so keep important things away from the top and bottom edges).</t>
         </is>
       </c>
-      <c r="K51" s="45" t="n"/>
-      <c r="L51" s="45" t="inlineStr">
+      <c r="K64" s="45" t="n"/>
+      <c r="L64" s="45" t="inlineStr">
         <is>
           <t>In game</t>
         </is>
       </c>
-      <c r="M51" s="45" t="n"/>
-    </row>
-    <row r="52" ht="230" customHeight="1" s="35">
-      <c r="A52" s="43" t="n">
-        <v>51</v>
-      </c>
-      <c r="B52" s="43" t="inlineStr">
+      <c r="M64" s="45" t="n"/>
+    </row>
+    <row r="65" ht="230" customHeight="1" s="35">
+      <c r="A65" s="43" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="43" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C52" s="43" t="inlineStr">
+      <c r="C65" s="43" t="inlineStr">
         <is>
           <t>Metro station</t>
         </is>
       </c>
-      <c r="D52" s="44" t="inlineStr">
+      <c r="D65" s="44" t="inlineStr">
         <is>
           <t>metro_train.png</t>
         </is>
       </c>
-      <c r="E52" s="43" t="inlineStr">
+      <c r="E65" s="43" t="inlineStr">
         <is>
           <t>Metro — train cars</t>
         </is>
       </c>
-      <c r="F52" s="43" t="inlineStr">
+      <c r="F65" s="43" t="inlineStr">
         <is>
           <t>1 × 2</t>
         </is>
       </c>
-      <c r="G52" s="43" t="inlineStr">
+      <c r="G65" s="43" t="inlineStr">
         <is>
           <t>400×100</t>
         </is>
       </c>
-      <c r="H52" s="43" t="inlineStr">
+      <c r="H65" s="43" t="inlineStr">
         <is>
           <t>Wide landscape image, 1536×1024</t>
         </is>
       </c>
-      <c r="I52" s="43" t="inlineStr">
+      <c r="I65" s="43" t="inlineStr">
         <is>
           <t>Each car is long and low (about 4 times wider than tall). The code chains them into trains.</t>
         </is>
       </c>
-      <c r="J52" s="43" t="inlineStr">
+      <c r="J65" s="43" t="inlineStr">
         <is>
           <t>Art style: retro 8-bit pixel art, like a Japanese console game from around 1990, set in a 1990s Japanese office. Chunky square pixels with hard edges: no anti-aliasing, no blur, no soft shading, no gradients, no painterly or paper texture. Every character and object has a 1-pixel dark ink outline. Flat colours from one small palette only: ink black, night indigo, slate blue, paper cream, warm grey, vermilion red, deep red, gold, ochre, wood brown, celadon green, moss green, sakura pink, peach. Subtle Japanese touches where they fit (seigaiha wave patterns, shoji paper screens, paper lanterns, hanko stamps, maneki-neko, daruma, bonsai). Satirical anthropomorphic animals. Clean, readable game asset. No text, letters, numbers, watermark, signature or frame.
 Camera: plain side view, like a 2D side-scrolling game; every figure stands on the bottom edge of its cell.
@@ -38067,55 +38914,55 @@
 Output: PNG, Wide landscape image, 1536×1024.</t>
         </is>
       </c>
-      <c r="K52" s="45" t="n"/>
-      <c r="L52" s="45" t="inlineStr">
+      <c r="K65" s="45" t="n"/>
+      <c r="L65" s="45" t="inlineStr">
         <is>
           <t>In game</t>
         </is>
       </c>
-      <c r="M52" s="45" t="n"/>
-    </row>
-    <row r="53" ht="230" customHeight="1" s="35">
-      <c r="A53" s="43" t="n">
-        <v>52</v>
-      </c>
-      <c r="B53" s="43" t="inlineStr">
+      <c r="M65" s="45" t="n"/>
+    </row>
+    <row r="66" ht="230" customHeight="1" s="35">
+      <c r="A66" s="43" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="43" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C53" s="43" t="inlineStr">
+      <c r="C66" s="43" t="inlineStr">
         <is>
           <t>Metro station</t>
         </is>
       </c>
-      <c r="D53" s="44" t="inlineStr">
+      <c r="D66" s="44" t="inlineStr">
         <is>
           <t>metro_props.png</t>
         </is>
       </c>
-      <c r="E53" s="43" t="inlineStr">
+      <c r="E66" s="43" t="inlineStr">
         <is>
           <t>Metro — station props</t>
         </is>
       </c>
-      <c r="F53" s="43" t="inlineStr">
+      <c r="F66" s="43" t="inlineStr">
         <is>
           <t>3 × 2</t>
         </is>
       </c>
-      <c r="G53" s="43" t="inlineStr">
+      <c r="G66" s="43" t="inlineStr">
         <is>
           <t>72×72</t>
         </is>
       </c>
-      <c r="H53" s="43" t="inlineStr">
+      <c r="H66" s="43" t="inlineStr">
         <is>
           <t>Wide landscape image, 1536×1024</t>
         </is>
       </c>
-      <c r="I53" s="43" t="inlineStr"/>
-      <c r="J53" s="43" t="inlineStr">
+      <c r="I66" s="43" t="inlineStr"/>
+      <c r="J66" s="43" t="inlineStr">
         <is>
           <t>Art style: retro 8-bit pixel art, like a Japanese console game from around 1990, set in a 1990s Japanese office. Chunky square pixels with hard edges: no anti-aliasing, no blur, no soft shading, no gradients, no painterly or paper texture. Every character and object has a 1-pixel dark ink outline. Flat colours from one small palette only: ink black, night indigo, slate blue, paper cream, warm grey, vermilion red, deep red, gold, ochre, wood brown, celadon green, moss green, sakura pink, peach. Subtle Japanese touches where they fit (seigaiha wave patterns, shoji paper screens, paper lanterns, hanko stamps, maneki-neko, daruma, bonsai). Satirical anthropomorphic animals. Clean, readable game asset. No text, letters, numbers, watermark, signature or frame.
 Camera: plain side view, like a 2D side-scrolling game; every figure stands on the bottom edge of its cell.
@@ -38127,55 +38974,55 @@
 Output: PNG, Wide landscape image, 1536×1024.</t>
         </is>
       </c>
-      <c r="K53" s="45" t="n"/>
-      <c r="L53" s="45" t="inlineStr">
+      <c r="K66" s="45" t="n"/>
+      <c r="L66" s="45" t="inlineStr">
         <is>
           <t>In game</t>
         </is>
       </c>
-      <c r="M53" s="45" t="n"/>
-    </row>
-    <row r="54" ht="230" customHeight="1" s="35">
-      <c r="A54" s="43" t="n">
-        <v>53</v>
-      </c>
-      <c r="B54" s="43" t="inlineStr">
+      <c r="M66" s="45" t="n"/>
+    </row>
+    <row r="67" ht="230" customHeight="1" s="35">
+      <c r="A67" s="43" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="43" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C54" s="43" t="inlineStr">
+      <c r="C67" s="43" t="inlineStr">
         <is>
           <t>Metro station</t>
         </is>
       </c>
-      <c r="D54" s="44" t="inlineStr">
+      <c r="D67" s="44" t="inlineStr">
         <is>
           <t>metro_debris.png</t>
         </is>
       </c>
-      <c r="E54" s="43" t="inlineStr">
+      <c r="E67" s="43" t="inlineStr">
         <is>
           <t>Metro — debris blown by the draft</t>
         </is>
       </c>
-      <c r="F54" s="43" t="inlineStr">
+      <c r="F67" s="43" t="inlineStr">
         <is>
           <t>4 × 2</t>
         </is>
       </c>
-      <c r="G54" s="43" t="inlineStr">
+      <c r="G67" s="43" t="inlineStr">
         <is>
           <t>16×16</t>
         </is>
       </c>
-      <c r="H54" s="43" t="inlineStr">
+      <c r="H67" s="43" t="inlineStr">
         <is>
           <t>Wide landscape image, 1536×1024</t>
         </is>
       </c>
-      <c r="I54" s="43" t="inlineStr"/>
-      <c r="J54" s="43" t="inlineStr">
+      <c r="I67" s="43" t="inlineStr"/>
+      <c r="J67" s="43" t="inlineStr">
         <is>
           <t>Art style: retro 8-bit pixel art, like a Japanese console game from around 1990, set in a 1990s Japanese office. Chunky square pixels with hard edges: no anti-aliasing, no blur, no soft shading, no gradients, no painterly or paper texture. Every character and object has a 1-pixel dark ink outline. Flat colours from one small palette only: ink black, night indigo, slate blue, paper cream, warm grey, vermilion red, deep red, gold, ochre, wood brown, celadon green, moss green, sakura pink, peach. Subtle Japanese touches where they fit (seigaiha wave patterns, shoji paper screens, paper lanterns, hanko stamps, maneki-neko, daruma, bonsai). Satirical anthropomorphic animals. Clean, readable game asset. No text, letters, numbers, watermark, signature or frame.
 Camera: plain side view, like a 2D side-scrolling game; every figure stands on the bottom edge of its cell.
@@ -38187,51 +39034,238 @@
 Output: PNG, Wide landscape image, 1536×1024.</t>
         </is>
       </c>
-      <c r="K54" s="45" t="n"/>
-      <c r="L54" s="45" t="inlineStr">
+      <c r="K67" s="45" t="n"/>
+      <c r="L67" s="45" t="inlineStr">
         <is>
           <t>In game</t>
         </is>
       </c>
-      <c r="M54" s="45" t="n"/>
-    </row>
-    <row r="55" ht="230" customHeight="1" s="35">
-      <c r="A55" s="43" t="n">
-        <v>54</v>
-      </c>
-      <c r="B55" s="43" t="inlineStr">
+      <c r="M67" s="45" t="n"/>
+    </row>
+    <row r="68" ht="230" customHeight="1" s="35">
+      <c r="A68" s="43" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="43" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C55" s="43" t="inlineStr">
+      <c r="C68" s="43" t="inlineStr">
+        <is>
+          <t>Street outside the office</t>
+        </is>
+      </c>
+      <c r="D68" s="44" t="inlineStr">
+        <is>
+          <t>npc_beggar.png</t>
+        </is>
+      </c>
+      <c r="E68" s="43" t="inlineStr">
+        <is>
+          <t>Street — the happy beggar (NPC)</t>
+        </is>
+      </c>
+      <c r="F68" s="43" t="inlineStr">
+        <is>
+          <t>4 × 1</t>
+        </is>
+      </c>
+      <c r="G68" s="43" t="inlineStr">
+        <is>
+          <t>48×40</t>
+        </is>
+      </c>
+      <c r="H68" s="43" t="inlineStr">
+        <is>
+          <t>Wide landscape image, 1536×1024</t>
+        </is>
+      </c>
+      <c r="I68" s="43" t="inlineStr">
+        <is>
+          <t>Sitting character; the code shows a speech bubble above him.</t>
+        </is>
+      </c>
+      <c r="J68" s="43" t="inlineStr">
+        <is>
+          <t>Art style: retro 8-bit pixel art, like a Japanese console game from around 1990, set in a 1990s Japanese office. Chunky square pixels with hard edges: no anti-aliasing, no blur, no soft shading, no gradients, no painterly or paper texture. Every character and object has a 1-pixel dark ink outline. Flat colours from one small palette only: ink black, night indigo, slate blue, paper cream, warm grey, vermilion red, deep red, gold, ochre, wood brown, celadon green, moss green, sakura pink, peach. Subtle Japanese touches where they fit (seigaiha wave patterns, shoji paper screens, paper lanterns, hanko stamps, maneki-neko, daruma, bonsai). Satirical anthropomorphic animals. Clean, readable game asset. No text, letters, numbers, watermark, signature or frame.
+Camera: plain side view, like a 2D side-scrolling game; every figure stands on the bottom edge of its cell.
+Subject: A happy, relaxed old tanuki (Japanese raccoon dog) beggar sitting cross-legged on a flattened cardboard box on the pavement, wearing a patched indigo kimono and a worn straw hat, a dented tin cup in front of him, a few cherry petals on his hat. Plain side view, he faces to the LEFT. He looks completely at peace — much happier than any office worker.
+Layout: a sprite sheet on a solid flat magenta background (#FF00FF, one single pure colour, no shading, no checkerboard). An evenly spaced grid of 4 columns and 1 row of equal-sized cells with wide plain magenta gaps between the cells. Every cell shows the exact same character (same design, same colours, same size), centred in its cell, feet on the same baseline. Draw each cell at about 48×40 pixel-art resolution, so each pixel is a big visible square block. No grid lines, borders, labels or numbers. Never use magenta or purple on the subjects themselves.
+Cells, left to right, top to bottom:
+- Row 1: idle A, eyes closed, smiling | idle B, wiggling his toes, smiling | talking: one paw raised wisely, mouth open | laughing heartily, eyes closed, head tilted back
+Output: PNG, Wide landscape image, 1536×1024.</t>
+        </is>
+      </c>
+      <c r="K68" s="45" t="n"/>
+      <c r="L68" s="45" t="inlineStr">
+        <is>
+          <t>In game</t>
+        </is>
+      </c>
+      <c r="M68" s="45" t="n"/>
+    </row>
+    <row r="69" ht="230" customHeight="1" s="35">
+      <c r="A69" s="43" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="43" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C69" s="43" t="inlineStr">
+        <is>
+          <t>Street outside the office</t>
+        </is>
+      </c>
+      <c r="D69" s="44" t="inlineStr">
+        <is>
+          <t>street_props.png</t>
+        </is>
+      </c>
+      <c r="E69" s="43" t="inlineStr">
+        <is>
+          <t>Street — props</t>
+        </is>
+      </c>
+      <c r="F69" s="43" t="inlineStr">
+        <is>
+          <t>3 × 2</t>
+        </is>
+      </c>
+      <c r="G69" s="43" t="inlineStr">
+        <is>
+          <t>48×48</t>
+        </is>
+      </c>
+      <c r="H69" s="43" t="inlineStr">
+        <is>
+          <t>Wide landscape image, 1536×1024</t>
+        </is>
+      </c>
+      <c r="I69" s="43" t="inlineStr"/>
+      <c r="J69" s="43" t="inlineStr">
+        <is>
+          <t>Art style: retro 8-bit pixel art, like a Japanese console game from around 1990, set in a 1990s Japanese office. Chunky square pixels with hard edges: no anti-aliasing, no blur, no soft shading, no gradients, no painterly or paper texture. Every character and object has a 1-pixel dark ink outline. Flat colours from one small palette only: ink black, night indigo, slate blue, paper cream, warm grey, vermilion red, deep red, gold, ochre, wood brown, celadon green, moss green, sakura pink, peach. Subtle Japanese touches where they fit (seigaiha wave patterns, shoji paper screens, paper lanterns, hanko stamps, maneki-neko, daruma, bonsai). Satirical anthropomorphic animals. Clean, readable game asset. No text, letters, numbers, watermark, signature or frame.
+Camera: plain side view, like a 2D side-scrolling game; every figure stands on the bottom edge of its cell.
+Subject: Objects on a Tokyo pavement in front of an office building in spring, plain side view, all at the same scale (a standing person would be about as tall as the street lamp is half).
+Layout: a sprite sheet on a solid flat magenta background (#FF00FF, one single pure colour, no shading, no checkerboard). An evenly spaced grid of 3 columns and 2 rows of equal-sized cells with wide plain magenta gaps between the cells. Each cell shows a different object, all drawn at the same scale as if standing on the same office floor (a person would be about 32 pixels tall), each centred in its cell and resting on the bottom of the cell. Each pixel is a big visible square block. No grid lines, borders, labels or numbers. Never use magenta or purple on the subjects themselves.
+Cells, left to right, top to bottom:
+- Row 1: a round red Japanese post box on a short post | a parked city bicycle with a front basket | a tall dark-green street lamp
+- Row 2: a simple stone-and-wood street bench with a few cherry petals on it | a café chalk sandwich board (drawings of a coffee cup and a cake, no text) | a small stone Jizo statue wearing a red knitted bib, with a tiny offering cup
+Output: PNG, Wide landscape image, 1536×1024.</t>
+        </is>
+      </c>
+      <c r="K69" s="45" t="n"/>
+      <c r="L69" s="45" t="inlineStr">
+        <is>
+          <t>In game</t>
+        </is>
+      </c>
+      <c r="M69" s="45" t="inlineStr">
+        <is>
+          <t>Saved first as streets_props.png, renamed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="230" customHeight="1" s="35">
+      <c r="A70" s="43" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="43" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C70" s="43" t="inlineStr">
+        <is>
+          <t>Street outside the office</t>
+        </is>
+      </c>
+      <c r="D70" s="44" t="inlineStr">
+        <is>
+          <t>street_petals.png</t>
+        </is>
+      </c>
+      <c r="E70" s="43" t="inlineStr">
+        <is>
+          <t>Street — cherry petals in the wind</t>
+        </is>
+      </c>
+      <c r="F70" s="43" t="inlineStr">
+        <is>
+          <t>4 × 2</t>
+        </is>
+      </c>
+      <c r="G70" s="43" t="inlineStr">
+        <is>
+          <t>16×16</t>
+        </is>
+      </c>
+      <c r="H70" s="43" t="inlineStr">
+        <is>
+          <t>Wide landscape image, 1536×1024</t>
+        </is>
+      </c>
+      <c r="I70" s="43" t="inlineStr"/>
+      <c r="J70" s="43" t="inlineStr">
+        <is>
+          <t>Art style: retro 8-bit pixel art, like a Japanese console game from around 1990, set in a 1990s Japanese office. Chunky square pixels with hard edges: no anti-aliasing, no blur, no soft shading, no gradients, no painterly or paper texture. Every character and object has a 1-pixel dark ink outline. Flat colours from one small palette only: ink black, night indigo, slate blue, paper cream, warm grey, vermilion red, deep red, gold, ochre, wood brown, celadon green, moss green, sakura pink, peach. Subtle Japanese touches where they fit (seigaiha wave patterns, shoji paper screens, paper lanterns, hanko stamps, maneki-neko, daruma, bonsai). Satirical anthropomorphic animals. Clean, readable game asset. No text, letters, numbers, watermark, signature or frame.
+Camera: plain side view, like a 2D side-scrolling game; every figure stands on the bottom edge of its cell.
+Subject: Cherry blossom petals blown by the wind, soft sakura pink with a slightly darker pink edge and a tiny notch at the tip.
+Layout: a sprite sheet on a solid flat magenta background (#FF00FF, one single pure colour, no shading, no checkerboard). An evenly spaced grid of 4 columns and 2 rows of equal-sized cells with wide plain magenta gaps between the cells. Each cell shows one small item, centred, drawn at about 16×16 pixel-art resolution so each pixel is a big visible square block. No grid lines, borders, labels or numbers. Never use magenta or purple on the subjects themselves.
+Cells, left to right, top to bottom:
+- Row 1: one petal seen flat | the same petal tilted | the same petal seen from the side (thin) | the same petal tilted the other way
+- Row 2: a little cluster of three petals | a whole small five-petal blossom | a petal lying flat on the ground | a tiny twig with two blossoms
+Output: PNG, Wide landscape image, 1536×1024.</t>
+        </is>
+      </c>
+      <c r="K70" s="45" t="n"/>
+      <c r="L70" s="45" t="inlineStr">
+        <is>
+          <t>In game</t>
+        </is>
+      </c>
+      <c r="M70" s="45" t="n"/>
+    </row>
+    <row r="71" ht="230" customHeight="1" s="35">
+      <c r="A71" s="43" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="43" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C71" s="43" t="inlineStr">
         <is>
           <t>Full-screen backgrounds</t>
         </is>
       </c>
-      <c r="D55" s="44" t="inlineStr">
+      <c r="D71" s="44" t="inlineStr">
         <is>
           <t>title_bg.png</t>
         </is>
       </c>
-      <c r="E55" s="43" t="inlineStr"/>
-      <c r="F55" s="43" t="inlineStr">
+      <c r="E71" s="43" t="inlineStr"/>
+      <c r="F71" s="43" t="inlineStr">
         <is>
           <t>full scene</t>
         </is>
       </c>
-      <c r="G55" s="43" t="inlineStr">
+      <c r="G71" s="43" t="inlineStr">
         <is>
           <t>320×180</t>
         </is>
       </c>
-      <c r="H55" s="43" t="inlineStr">
+      <c r="H71" s="43" t="inlineStr">
         <is>
           <t>Wide landscape image, 1536×1024</t>
         </is>
       </c>
-      <c r="I55" s="43" t="inlineStr"/>
-      <c r="J55" s="43" t="inlineStr">
+      <c r="I71" s="43" t="inlineStr"/>
+      <c r="J71" s="43" t="inlineStr">
         <is>
           <t>Art style: retro 8-bit pixel art, like a Japanese console game from around 1990, set in a 1990s Japanese office. Chunky square pixels with hard edges: no anti-aliasing, no blur, no soft shading, no gradients, no painterly or paper texture. Every character and object has a 1-pixel dark ink outline. Flat colours from one small palette only: ink black, night indigo, slate blue, paper cream, warm grey, vermilion red, deep red, gold, ochre, wood brown, celadon green, moss green, sakura pink, peach. Subtle Japanese touches where they fit (seigaiha wave patterns, shoji paper screens, paper lanterns, hanko stamps, maneki-neko, daruma, bonsai). Satirical anthropomorphic animals. Clean, readable game asset. No text, letters, numbers, watermark, signature or frame.
 Camera: plain side view of a 2D side-scrolling game stage, horizon level, no characters in the scene.
@@ -38240,51 +39274,51 @@
 Output: the scene fills the whole image edge to edge, no border, no vignette, no text. Wide landscape image, 1536×1024 (it will be cropped to 16:9, so keep important things away from the top and bottom edges).</t>
         </is>
       </c>
-      <c r="K55" s="45" t="n"/>
-      <c r="L55" s="45" t="inlineStr">
+      <c r="K71" s="45" t="n"/>
+      <c r="L71" s="45" t="inlineStr">
         <is>
           <t>In game</t>
         </is>
       </c>
-      <c r="M55" s="45" t="n"/>
-    </row>
-    <row r="56" ht="230" customHeight="1" s="35">
-      <c r="A56" s="43" t="n">
-        <v>55</v>
-      </c>
-      <c r="B56" s="43" t="inlineStr">
+      <c r="M71" s="45" t="n"/>
+    </row>
+    <row r="72" ht="230" customHeight="1" s="35">
+      <c r="A72" s="43" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="43" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C56" s="43" t="inlineStr">
+      <c r="C72" s="43" t="inlineStr">
         <is>
           <t>Full-screen backgrounds</t>
         </is>
       </c>
-      <c r="D56" s="44" t="inlineStr">
+      <c r="D72" s="44" t="inlineStr">
         <is>
           <t>intro_flat.png</t>
         </is>
       </c>
-      <c r="E56" s="43" t="inlineStr"/>
-      <c r="F56" s="43" t="inlineStr">
+      <c r="E72" s="43" t="inlineStr"/>
+      <c r="F72" s="43" t="inlineStr">
         <is>
           <t>full scene</t>
         </is>
       </c>
-      <c r="G56" s="43" t="inlineStr">
+      <c r="G72" s="43" t="inlineStr">
         <is>
           <t>320×180</t>
         </is>
       </c>
-      <c r="H56" s="43" t="inlineStr">
+      <c r="H72" s="43" t="inlineStr">
         <is>
           <t>Wide landscape image, 1536×1024</t>
         </is>
       </c>
-      <c r="I56" s="43" t="inlineStr"/>
-      <c r="J56" s="43" t="inlineStr">
+      <c r="I72" s="43" t="inlineStr"/>
+      <c r="J72" s="43" t="inlineStr">
         <is>
           <t>Art style: retro 8-bit pixel art, like a Japanese console game from around 1990, set in a 1990s Japanese office. Chunky square pixels with hard edges: no anti-aliasing, no blur, no soft shading, no gradients, no painterly or paper texture. Every character and object has a 1-pixel dark ink outline. Flat colours from one small palette only: ink black, night indigo, slate blue, paper cream, warm grey, vermilion red, deep red, gold, ochre, wood brown, celadon green, moss green, sakura pink, peach. Subtle Japanese touches where they fit (seigaiha wave patterns, shoji paper screens, paper lanterns, hanko stamps, maneki-neko, daruma, bonsai). Satirical anthropomorphic animals. Clean, readable game asset. No text, letters, numbers, watermark, signature or frame.
 Camera: plain side view of a 2D side-scrolling game stage, horizon level, no characters in the scene.
@@ -38293,51 +39327,51 @@
 Output: the scene fills the whole image edge to edge, no border, no vignette, no text. Wide landscape image, 1536×1024 (it will be cropped to 16:9, so keep important things away from the top and bottom edges).</t>
         </is>
       </c>
-      <c r="K56" s="45" t="n"/>
-      <c r="L56" s="45" t="inlineStr">
+      <c r="K72" s="45" t="n"/>
+      <c r="L72" s="45" t="inlineStr">
         <is>
           <t>In game</t>
         </is>
       </c>
-      <c r="M56" s="45" t="n"/>
-    </row>
-    <row r="57" ht="230" customHeight="1" s="35">
-      <c r="A57" s="43" t="n">
-        <v>56</v>
-      </c>
-      <c r="B57" s="43" t="inlineStr">
+      <c r="M72" s="45" t="n"/>
+    </row>
+    <row r="73" ht="230" customHeight="1" s="35">
+      <c r="A73" s="43" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="43" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C57" s="43" t="inlineStr">
+      <c r="C73" s="43" t="inlineStr">
         <is>
           <t>Full-screen backgrounds</t>
         </is>
       </c>
-      <c r="D57" s="44" t="inlineStr">
+      <c r="D73" s="44" t="inlineStr">
         <is>
           <t>intro_metro.png</t>
         </is>
       </c>
-      <c r="E57" s="43" t="inlineStr"/>
-      <c r="F57" s="43" t="inlineStr">
+      <c r="E73" s="43" t="inlineStr"/>
+      <c r="F73" s="43" t="inlineStr">
         <is>
           <t>full scene</t>
         </is>
       </c>
-      <c r="G57" s="43" t="inlineStr">
+      <c r="G73" s="43" t="inlineStr">
         <is>
           <t>320×180</t>
         </is>
       </c>
-      <c r="H57" s="43" t="inlineStr">
+      <c r="H73" s="43" t="inlineStr">
         <is>
           <t>Wide landscape image, 1536×1024</t>
         </is>
       </c>
-      <c r="I57" s="43" t="inlineStr"/>
-      <c r="J57" s="43" t="inlineStr">
+      <c r="I73" s="43" t="inlineStr"/>
+      <c r="J73" s="43" t="inlineStr">
         <is>
           <t>Art style: retro 8-bit pixel art, like a Japanese console game from around 1990, set in a 1990s Japanese office. Chunky square pixels with hard edges: no anti-aliasing, no blur, no soft shading, no gradients, no painterly or paper texture. Every character and object has a 1-pixel dark ink outline. Flat colours from one small palette only: ink black, night indigo, slate blue, paper cream, warm grey, vermilion red, deep red, gold, ochre, wood brown, celadon green, moss green, sakura pink, peach. Subtle Japanese touches where they fit (seigaiha wave patterns, shoji paper screens, paper lanterns, hanko stamps, maneki-neko, daruma, bonsai). Satirical anthropomorphic animals. Clean, readable game asset. No text, letters, numbers, watermark, signature or frame.
 Camera: plain side view of a 2D side-scrolling game stage, horizon level, no characters in the scene.
@@ -38346,55 +39380,55 @@
 Output: the scene fills the whole image edge to edge, no border, no vignette, no text. Wide landscape image, 1536×1024 (it will be cropped to 16:9, so keep important things away from the top and bottom edges).</t>
         </is>
       </c>
-      <c r="K57" s="45" t="n"/>
-      <c r="L57" s="45" t="inlineStr">
+      <c r="K73" s="45" t="n"/>
+      <c r="L73" s="45" t="inlineStr">
         <is>
           <t>In game</t>
         </is>
       </c>
-      <c r="M57" s="45" t="inlineStr">
+      <c r="M73" s="45" t="inlineStr">
         <is>
           <t>Only used until the metro_* layers exist.</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="230" customHeight="1" s="35">
-      <c r="A58" s="43" t="n">
-        <v>57</v>
-      </c>
-      <c r="B58" s="43" t="inlineStr">
+    <row r="74" ht="230" customHeight="1" s="35">
+      <c r="A74" s="43" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="43" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C58" s="43" t="inlineStr">
+      <c r="C74" s="43" t="inlineStr">
         <is>
           <t>Full-screen backgrounds</t>
         </is>
       </c>
-      <c r="D58" s="44" t="inlineStr">
+      <c r="D74" s="44" t="inlineStr">
         <is>
           <t>intro_entrance.png</t>
         </is>
       </c>
-      <c r="E58" s="43" t="inlineStr"/>
-      <c r="F58" s="43" t="inlineStr">
+      <c r="E74" s="43" t="inlineStr"/>
+      <c r="F74" s="43" t="inlineStr">
         <is>
           <t>full scene</t>
         </is>
       </c>
-      <c r="G58" s="43" t="inlineStr">
+      <c r="G74" s="43" t="inlineStr">
         <is>
           <t>320×180</t>
         </is>
       </c>
-      <c r="H58" s="43" t="inlineStr">
+      <c r="H74" s="43" t="inlineStr">
         <is>
           <t>Wide landscape image, 1536×1024</t>
         </is>
       </c>
-      <c r="I58" s="43" t="inlineStr"/>
-      <c r="J58" s="43" t="inlineStr">
+      <c r="I74" s="43" t="inlineStr"/>
+      <c r="J74" s="43" t="inlineStr">
         <is>
           <t>Art style: retro 8-bit pixel art, like a Japanese console game from around 1990, set in a 1990s Japanese office. Chunky square pixels with hard edges: no anti-aliasing, no blur, no soft shading, no gradients, no painterly or paper texture. Every character and object has a 1-pixel dark ink outline. Flat colours from one small palette only: ink black, night indigo, slate blue, paper cream, warm grey, vermilion red, deep red, gold, ochre, wood brown, celadon green, moss green, sakura pink, peach. Subtle Japanese touches where they fit (seigaiha wave patterns, shoji paper screens, paper lanterns, hanko stamps, maneki-neko, daruma, bonsai). Satirical anthropomorphic animals. Clean, readable game asset. No text, letters, numbers, watermark, signature or frame.
 Camera: plain side view of a 2D side-scrolling game stage, horizon level, no characters in the scene.
@@ -38403,51 +39437,51 @@
 Output: the scene fills the whole image edge to edge, no border, no vignette, no text. Wide landscape image, 1536×1024 (it will be cropped to 16:9, so keep important things away from the top and bottom edges).</t>
         </is>
       </c>
-      <c r="K58" s="45" t="n"/>
-      <c r="L58" s="45" t="inlineStr">
+      <c r="K74" s="45" t="n"/>
+      <c r="L74" s="45" t="inlineStr">
         <is>
           <t>In game</t>
         </is>
       </c>
-      <c r="M58" s="45" t="n"/>
-    </row>
-    <row r="59" ht="230" customHeight="1" s="35">
-      <c r="A59" s="43" t="n">
-        <v>58</v>
-      </c>
-      <c r="B59" s="43" t="inlineStr">
+      <c r="M74" s="45" t="n"/>
+    </row>
+    <row r="75" ht="230" customHeight="1" s="35">
+      <c r="A75" s="43" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="43" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C59" s="43" t="inlineStr">
+      <c r="C75" s="43" t="inlineStr">
         <is>
           <t>Full-screen backgrounds</t>
         </is>
       </c>
-      <c r="D59" s="44" t="inlineStr">
+      <c r="D75" s="44" t="inlineStr">
         <is>
           <t>lift_interior.png</t>
         </is>
       </c>
-      <c r="E59" s="43" t="inlineStr"/>
-      <c r="F59" s="43" t="inlineStr">
+      <c r="E75" s="43" t="inlineStr"/>
+      <c r="F75" s="43" t="inlineStr">
         <is>
           <t>full scene</t>
         </is>
       </c>
-      <c r="G59" s="43" t="inlineStr">
+      <c r="G75" s="43" t="inlineStr">
         <is>
           <t>320×180</t>
         </is>
       </c>
-      <c r="H59" s="43" t="inlineStr">
+      <c r="H75" s="43" t="inlineStr">
         <is>
           <t>Wide landscape image, 1536×1024</t>
         </is>
       </c>
-      <c r="I59" s="43" t="inlineStr"/>
-      <c r="J59" s="43" t="inlineStr">
+      <c r="I75" s="43" t="inlineStr"/>
+      <c r="J75" s="43" t="inlineStr">
         <is>
           <t>Art style: retro 8-bit pixel art, like a Japanese console game from around 1990, set in a 1990s Japanese office. Chunky square pixels with hard edges: no anti-aliasing, no blur, no soft shading, no gradients, no painterly or paper texture. Every character and object has a 1-pixel dark ink outline. Flat colours from one small palette only: ink black, night indigo, slate blue, paper cream, warm grey, vermilion red, deep red, gold, ochre, wood brown, celadon green, moss green, sakura pink, peach. Subtle Japanese touches where they fit (seigaiha wave patterns, shoji paper screens, paper lanterns, hanko stamps, maneki-neko, daruma, bonsai). Satirical anthropomorphic animals. Clean, readable game asset. No text, letters, numbers, watermark, signature or frame.
 Camera: straight-on front view, no characters in the scene.
@@ -38456,59 +39490,59 @@
 Output: the scene fills the whole image edge to edge, no border, no vignette, no text. Wide landscape image, 1536×1024 (it will be cropped to 16:9, so keep important things away from the top and bottom edges).</t>
         </is>
       </c>
-      <c r="K59" s="45" t="n"/>
-      <c r="L59" s="45" t="inlineStr">
+      <c r="K75" s="45" t="n"/>
+      <c r="L75" s="45" t="inlineStr">
         <is>
           <t>In game</t>
         </is>
       </c>
-      <c r="M59" s="45" t="n"/>
-    </row>
-    <row r="60" ht="230" customHeight="1" s="35">
-      <c r="A60" s="43" t="n">
-        <v>59</v>
-      </c>
-      <c r="B60" s="43" t="inlineStr">
+      <c r="M75" s="45" t="n"/>
+    </row>
+    <row r="76" ht="230" customHeight="1" s="35">
+      <c r="A76" s="43" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="43" t="inlineStr">
         <is>
           <t>Later</t>
         </is>
       </c>
-      <c r="C60" s="43" t="inlineStr">
+      <c r="C76" s="43" t="inlineStr">
         <is>
           <t>Bosses</t>
         </is>
       </c>
-      <c r="D60" s="44" t="inlineStr">
+      <c r="D76" s="44" t="inlineStr">
         <is>
           <t>boss_portrait.png</t>
         </is>
       </c>
-      <c r="E60" s="43" t="inlineStr">
+      <c r="E76" s="43" t="inlineStr">
         <is>
           <t>Lift boss — not decided yet</t>
         </is>
       </c>
-      <c r="F60" s="43" t="inlineStr">
+      <c r="F76" s="43" t="inlineStr">
         <is>
           <t>2 × 1</t>
         </is>
       </c>
-      <c r="G60" s="43" t="inlineStr">
+      <c r="G76" s="43" t="inlineStr">
         <is>
           <t>64×64</t>
         </is>
       </c>
-      <c r="H60" s="43" t="inlineStr">
+      <c r="H76" s="43" t="inlineStr">
         <is>
           <t>Wide landscape image, 1536×1024</t>
         </is>
       </c>
-      <c r="I60" s="43" t="inlineStr">
+      <c r="I76" s="43" t="inlineStr">
         <is>
           <t>Wait for the team.</t>
         </is>
       </c>
-      <c r="J60" s="43" t="inlineStr">
+      <c r="J76" s="43" t="inlineStr">
         <is>
           <t>Art style: retro 8-bit pixel art, like a Japanese console game from around 1990, set in a 1990s Japanese office. Chunky square pixels with hard edges: no anti-aliasing, no blur, no soft shading, no gradients, no painterly or paper texture. Every character and object has a 1-pixel dark ink outline. Flat colours from one small palette only: ink black, night indigo, slate blue, paper cream, warm grey, vermilion red, deep red, gold, ochre, wood brown, celadon green, moss green, sakura pink, peach. Subtle Japanese touches where they fit (seigaiha wave patterns, shoji paper screens, paper lanterns, hanko stamps, maneki-neko, daruma, bonsai). Satirical anthropomorphic animals. Clean, readable game asset. No text, letters, numbers, watermark, signature or frame.
 Camera: chest-up character portrait, three-quarter view, like a dialogue portrait in a Japanese RPG.
@@ -38519,17 +39553,17 @@
 Output: PNG, Wide landscape image, 1536×1024.</t>
         </is>
       </c>
-      <c r="K60" s="45" t="n"/>
-      <c r="L60" s="45" t="inlineStr">
+      <c r="K76" s="45" t="n"/>
+      <c r="L76" s="45" t="inlineStr">
         <is>
           <t>In game</t>
         </is>
       </c>
-      <c r="M60" s="45" t="n"/>
+      <c r="M76" s="45" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M60"/>
-  <conditionalFormatting sqref="A2:M60">
+  <autoFilter ref="A1:M76"/>
+  <conditionalFormatting sqref="A2:M76">
     <cfRule type="expression" priority="1" dxfId="9">
       <formula>$L2="Delivered"</formula>
     </cfRule>
@@ -38544,7 +39578,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="L2:L60" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L2:L76" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"To do,In progress,Delivered,In game,Needs redo"</formula1>
     </dataValidation>
   </dataValidations>
@@ -38591,7 +39625,7 @@
         </is>
       </c>
       <c r="B4" s="48">
-        <f>COUNTIF('Image prompts'!$L$2:$L$60,A4)</f>
+        <f>COUNTIF('Image prompts'!$L$2:$L$76,A4)</f>
         <v/>
       </c>
     </row>
@@ -38602,7 +39636,7 @@
         </is>
       </c>
       <c r="B5" s="48">
-        <f>COUNTIF('Image prompts'!$L$2:$L$60,A5)</f>
+        <f>COUNTIF('Image prompts'!$L$2:$L$76,A5)</f>
         <v/>
       </c>
     </row>
@@ -38613,7 +39647,7 @@
         </is>
       </c>
       <c r="B6" s="48">
-        <f>COUNTIF('Image prompts'!$L$2:$L$60,A6)</f>
+        <f>COUNTIF('Image prompts'!$L$2:$L$76,A6)</f>
         <v/>
       </c>
     </row>
@@ -38624,7 +39658,7 @@
         </is>
       </c>
       <c r="B7" s="48">
-        <f>COUNTIF('Image prompts'!$L$2:$L$60,A7)</f>
+        <f>COUNTIF('Image prompts'!$L$2:$L$76,A7)</f>
         <v/>
       </c>
     </row>
@@ -38635,7 +39669,7 @@
         </is>
       </c>
       <c r="B8" s="48">
-        <f>COUNTIF('Image prompts'!$L$2:$L$60,A8)</f>
+        <f>COUNTIF('Image prompts'!$L$2:$L$76,A8)</f>
         <v/>
       </c>
     </row>
@@ -38668,7 +39702,7 @@
         </is>
       </c>
       <c r="B12" s="48">
-        <f>COUNTBLANK('Image prompts'!$K$2:$K$60)</f>
+        <f>COUNTBLANK('Image prompts'!$K$2:$K$76)</f>
         <v/>
       </c>
     </row>
